--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_macroeconomia.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_macroeconomia.xlsx
@@ -17,7 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="[$-es-ES]#,##0"/>
+    <numFmt numFmtId="165" formatCode="[$-es-ES]#,##0.00"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -69,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -83,6 +86,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -114,6 +123,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -144,6 +156,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -597,7 +612,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -630,7 +645,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N7" s="4" t="n">
+      <c r="N7" s="8" t="n">
         <v>76.1801254333684</v>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -676,7 +691,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -709,7 +724,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N8" s="4" t="n">
+      <c r="N8" s="8" t="n">
         <v>72.7512581409118</v>
       </c>
       <c r="O8" s="4" t="inlineStr">
@@ -755,7 +770,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -788,7 +803,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N9" s="4" t="n">
+      <c r="N9" s="8" t="n">
         <v>72.9259949195597</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -834,7 +849,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -867,7 +882,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N10" s="4" t="n">
+      <c r="N10" s="8" t="n">
         <v>72.50015534704529</v>
       </c>
       <c r="O10" s="4" t="inlineStr">
@@ -913,7 +928,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -946,7 +961,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N11" s="4" t="n">
+      <c r="N11" s="8" t="n">
         <v>72.0523613098746</v>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -992,7 +1007,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G12" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1025,7 +1040,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N12" s="4" t="n">
+      <c r="N12" s="8" t="n">
         <v>74.761502966381</v>
       </c>
       <c r="O12" s="4" t="inlineStr">
@@ -1071,7 +1086,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G13" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1104,7 +1119,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N13" s="4" t="n">
+      <c r="N13" s="8" t="n">
         <v>75.9143131895941</v>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1150,7 +1165,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G14" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1183,7 +1198,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N14" s="4" t="n">
+      <c r="N14" s="8" t="n">
         <v>75.32276276276269</v>
       </c>
       <c r="O14" s="4" t="inlineStr">
@@ -1229,7 +1244,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G15" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1262,7 +1277,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N15" s="4" t="n">
+      <c r="N15" s="8" t="n">
         <v>74.79193887720081</v>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1308,7 +1323,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G16" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1341,7 +1356,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N16" s="4" t="n">
+      <c r="N16" s="8" t="n">
         <v>76.1052654322321</v>
       </c>
       <c r="O16" s="4" t="inlineStr">
@@ -1387,7 +1402,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G17" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1420,7 +1435,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N17" s="4" t="n">
+      <c r="N17" s="8" t="n">
         <v>70.12359442575681</v>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1466,7 +1481,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="G18" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1499,7 +1514,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N18" s="4" t="n">
+      <c r="N18" s="8" t="n">
         <v>70.1113036173676</v>
       </c>
       <c r="O18" s="4" t="inlineStr">
@@ -1545,7 +1560,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G19" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1578,7 +1593,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N19" s="4" t="n">
+      <c r="N19" s="8" t="n">
         <v>72.84966342557971</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -1624,7 +1639,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="G20" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1657,7 +1672,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N20" s="4" t="n">
+      <c r="N20" s="8" t="n">
         <v>69.35361009105431</v>
       </c>
       <c r="O20" s="4" t="inlineStr">
@@ -1703,7 +1718,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="G21" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1736,7 +1751,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N21" s="4" t="n">
+      <c r="N21" s="8" t="n">
         <v>57.5953810788175</v>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -1782,7 +1797,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="G22" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1815,7 +1830,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N22" s="4" t="n">
+      <c r="N22" s="8" t="n">
         <v>68.7471422039323</v>
       </c>
       <c r="O22" s="4" t="inlineStr">
@@ -1861,7 +1876,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="G23" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1894,7 +1909,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N23" s="4" t="n">
+      <c r="N23" s="8" t="n">
         <v>72.69977202747511</v>
       </c>
       <c r="O23" s="4" t="inlineStr">
@@ -1940,7 +1955,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="G24" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1973,7 +1988,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N24" s="4" t="n">
+      <c r="N24" s="8" t="n">
         <v>74.39167405238079</v>
       </c>
       <c r="O24" s="4" t="inlineStr">
@@ -2019,7 +2034,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="G25" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -2052,7 +2067,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N25" s="4" t="n">
+      <c r="N25" s="8" t="n">
         <v>79.39092629835559</v>
       </c>
       <c r="O25" s="4" t="inlineStr">
@@ -2098,7 +2113,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="G26" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -2131,7 +2146,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N26" s="4" t="n">
+      <c r="N26" s="8" t="n">
         <v>75.4634465694604</v>
       </c>
       <c r="O26" s="4" t="inlineStr">
@@ -2177,7 +2192,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="G27" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -2210,7 +2225,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N27" s="4" t="n">
+      <c r="N27" s="8" t="n">
         <v>75.5646515946043</v>
       </c>
       <c r="O27" s="4" t="inlineStr">
@@ -2256,7 +2271,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="G28" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -2289,7 +2304,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N28" s="4" t="n">
+      <c r="N28" s="8" t="n">
         <v>80.27649995792549</v>
       </c>
       <c r="O28" s="4" t="inlineStr">
@@ -2335,7 +2350,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="G29" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -2368,7 +2383,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N29" s="4" t="n">
+      <c r="N29" s="8" t="n">
         <v>84.6861653185383</v>
       </c>
       <c r="O29" s="4" t="inlineStr">
@@ -2414,7 +2429,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="G30" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -2447,7 +2462,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N30" s="4" t="n">
+      <c r="N30" s="8" t="n">
         <v>92.4076050287099</v>
       </c>
       <c r="O30" s="4" t="inlineStr">
@@ -2493,7 +2508,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="G31" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -2526,7 +2541,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N31" s="4" t="n">
+      <c r="N31" s="8" t="n">
         <v>69.02533375230909</v>
       </c>
       <c r="O31" s="4" t="inlineStr">
@@ -2572,7 +2587,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="G32" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -2605,7 +2620,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N32" s="4" t="n">
+      <c r="N32" s="8" t="n">
         <v>69.93475936059011</v>
       </c>
       <c r="O32" s="4" t="inlineStr">
@@ -2651,7 +2666,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="G33" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -2684,7 +2699,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N33" s="4" t="n">
+      <c r="N33" s="8" t="n">
         <v>77.51007825468341</v>
       </c>
       <c r="O33" s="4" t="inlineStr">
@@ -2730,7 +2745,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="G34" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2763,7 +2778,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N34" s="4" t="n">
+      <c r="N34" s="8" t="n">
         <v>72.45811082664081</v>
       </c>
       <c r="O34" s="4" t="inlineStr">
@@ -2809,7 +2824,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="G35" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -2842,7 +2857,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N35" s="4" t="n">
+      <c r="N35" s="8" t="n">
         <v>76.4239084008277</v>
       </c>
       <c r="O35" s="4" t="inlineStr">
@@ -2888,7 +2903,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="G36" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -2921,7 +2936,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N36" s="4" t="n">
+      <c r="N36" s="8" t="n">
         <v>71.8641636006226</v>
       </c>
       <c r="O36" s="4" t="inlineStr">
@@ -2967,7 +2982,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="G37" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -3000,7 +3015,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N37" s="4" t="n">
+      <c r="N37" s="8" t="n">
         <v>68.2356781430472</v>
       </c>
       <c r="O37" s="4" t="inlineStr">
@@ -3046,7 +3061,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="G38" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -3079,7 +3094,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N38" s="4" t="n">
+      <c r="N38" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O38" s="4" t="inlineStr">
@@ -3125,7 +3140,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G39" s="4" t="n">
+      <c r="G39" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -3158,7 +3173,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N39" s="4" t="n">
+      <c r="N39" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O39" s="4" t="inlineStr">
@@ -3204,7 +3219,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="G40" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -3237,7 +3252,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N40" s="4" t="n">
+      <c r="N40" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O40" s="4" t="inlineStr">
@@ -3283,7 +3298,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="G41" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -3316,7 +3331,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N41" s="4" t="n">
+      <c r="N41" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O41" s="4" t="inlineStr">
@@ -3362,7 +3377,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="G42" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -3395,7 +3410,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N42" s="4" t="n">
+      <c r="N42" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O42" s="4" t="inlineStr">
@@ -3441,7 +3456,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G43" s="4" t="n">
+      <c r="G43" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -3474,7 +3489,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N43" s="4" t="n">
+      <c r="N43" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O43" s="4" t="inlineStr">
@@ -3520,7 +3535,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G44" s="4" t="n">
+      <c r="G44" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -3553,7 +3568,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N44" s="4" t="n">
+      <c r="N44" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O44" s="4" t="inlineStr">
@@ -3599,7 +3614,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G45" s="4" t="n">
+      <c r="G45" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -3632,7 +3647,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N45" s="4" t="n">
+      <c r="N45" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O45" s="4" t="inlineStr">
@@ -3678,7 +3693,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G46" s="4" t="n">
+      <c r="G46" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -3711,7 +3726,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N46" s="4" t="n">
+      <c r="N46" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O46" s="4" t="inlineStr">
@@ -3757,7 +3772,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G47" s="4" t="n">
+      <c r="G47" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -3790,7 +3805,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N47" s="4" t="n">
+      <c r="N47" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O47" s="4" t="inlineStr">
@@ -3836,7 +3851,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G48" s="4" t="n">
+      <c r="G48" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -3869,7 +3884,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N48" s="4" t="n">
+      <c r="N48" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O48" s="4" t="inlineStr">
@@ -3915,7 +3930,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G49" s="4" t="n">
+      <c r="G49" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -3948,7 +3963,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N49" s="4" t="n">
+      <c r="N49" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O49" s="4" t="inlineStr">
@@ -3994,7 +4009,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G50" s="4" t="n">
+      <c r="G50" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -4027,7 +4042,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N50" s="4" t="n">
+      <c r="N50" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O50" s="4" t="inlineStr">
@@ -4073,7 +4088,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G51" s="4" t="n">
+      <c r="G51" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H51" s="4" t="inlineStr">
@@ -4106,7 +4121,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N51" s="4" t="n">
+      <c r="N51" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O51" s="4" t="inlineStr">
@@ -4152,7 +4167,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G52" s="4" t="n">
+      <c r="G52" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -4185,7 +4200,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N52" s="4" t="n">
+      <c r="N52" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O52" s="4" t="inlineStr">
@@ -4231,7 +4246,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G53" s="4" t="n">
+      <c r="G53" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -4264,7 +4279,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N53" s="4" t="n">
+      <c r="N53" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O53" s="4" t="inlineStr">
@@ -4310,7 +4325,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G54" s="4" t="n">
+      <c r="G54" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -4343,7 +4358,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N54" s="4" t="n">
+      <c r="N54" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O54" s="4" t="inlineStr">
@@ -4389,7 +4404,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G55" s="4" t="n">
+      <c r="G55" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -4422,7 +4437,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N55" s="4" t="n">
+      <c r="N55" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O55" s="4" t="inlineStr">
@@ -4468,7 +4483,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G56" s="4" t="n">
+      <c r="G56" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -4501,7 +4516,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N56" s="4" t="n">
+      <c r="N56" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O56" s="4" t="inlineStr">
@@ -4547,7 +4562,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G57" s="4" t="n">
+      <c r="G57" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -4580,7 +4595,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N57" s="4" t="n">
+      <c r="N57" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O57" s="4" t="inlineStr">
@@ -4626,7 +4641,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G58" s="4" t="n">
+      <c r="G58" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -4659,7 +4674,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N58" s="4" t="n">
+      <c r="N58" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O58" s="4" t="inlineStr">
@@ -4705,7 +4720,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G59" s="4" t="n">
+      <c r="G59" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -4738,7 +4753,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N59" s="4" t="n">
+      <c r="N59" s="8" t="n">
         <v>68.2080924855491</v>
       </c>
       <c r="O59" s="4" t="inlineStr">
@@ -4784,7 +4799,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G60" s="4" t="n">
+      <c r="G60" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -4817,7 +4832,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N60" s="4" t="n">
+      <c r="N60" s="8" t="n">
         <v>70.49180327868849</v>
       </c>
       <c r="O60" s="4" t="inlineStr">
@@ -4863,7 +4878,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G61" s="4" t="n">
+      <c r="G61" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -4896,7 +4911,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N61" s="4" t="n">
+      <c r="N61" s="8" t="n">
         <v>57.3804573804574</v>
       </c>
       <c r="O61" s="4" t="inlineStr">
@@ -4942,7 +4957,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G62" s="4" t="n">
+      <c r="G62" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -4975,7 +4990,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N62" s="4" t="n">
+      <c r="N62" s="8" t="n">
         <v>59.4339622641509</v>
       </c>
       <c r="O62" s="4" t="inlineStr">
@@ -5021,7 +5036,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G63" s="4" t="n">
+      <c r="G63" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -5054,7 +5069,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N63" s="4" t="n">
+      <c r="N63" s="8" t="n">
         <v>68.8022284122563</v>
       </c>
       <c r="O63" s="4" t="inlineStr">
@@ -5100,7 +5115,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G64" s="4" t="n">
+      <c r="G64" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -5133,7 +5148,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N64" s="4" t="n">
+      <c r="N64" s="8" t="n">
         <v>70.97701149425291</v>
       </c>
       <c r="O64" s="4" t="inlineStr">
@@ -5179,7 +5194,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G65" s="4" t="n">
+      <c r="G65" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -5212,7 +5227,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N65" s="4" t="n">
+      <c r="N65" s="8" t="n">
         <v>65.2463171233962</v>
       </c>
       <c r="O65" s="4" t="inlineStr">
@@ -5258,7 +5273,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G66" s="4" t="n">
+      <c r="G66" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -5291,7 +5306,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N66" s="4" t="n">
+      <c r="N66" s="8" t="n">
         <v>56.9364331403991</v>
       </c>
       <c r="O66" s="4" t="inlineStr">
@@ -5337,7 +5352,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G67" s="4" t="n">
+      <c r="G67" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -5370,7 +5385,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N67" s="4" t="n">
+      <c r="N67" s="8" t="n">
         <v>90.8732007990026</v>
       </c>
       <c r="O67" s="4" t="inlineStr">
@@ -5416,7 +5431,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G68" s="4" t="n">
+      <c r="G68" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -5449,7 +5464,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N68" s="4" t="n">
+      <c r="N68" s="8" t="n">
         <v>89.6698755348114</v>
       </c>
       <c r="O68" s="4" t="inlineStr">
@@ -5495,7 +5510,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G69" s="4" t="n">
+      <c r="G69" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -5528,7 +5543,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N69" s="4" t="n">
+      <c r="N69" s="8" t="n">
         <v>89.0313259042003</v>
       </c>
       <c r="O69" s="4" t="inlineStr">
@@ -5574,7 +5589,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G70" s="4" t="n">
+      <c r="G70" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H70" s="4" t="inlineStr">
@@ -5607,7 +5622,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N70" s="4" t="n">
+      <c r="N70" s="8" t="n">
         <v>86.635743357465</v>
       </c>
       <c r="O70" s="4" t="inlineStr">
@@ -5653,7 +5668,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G71" s="4" t="n">
+      <c r="G71" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -5686,7 +5701,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N71" s="4" t="n">
+      <c r="N71" s="8" t="n">
         <v>87.9027214650732</v>
       </c>
       <c r="O71" s="4" t="inlineStr">
@@ -5732,7 +5747,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G72" s="4" t="n">
+      <c r="G72" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H72" s="4" t="inlineStr">
@@ -5765,7 +5780,7 @@
           <t>Consumo final como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N72" s="4" t="n">
+      <c r="N72" s="8" t="n">
         <v>89.27797139927191</v>
       </c>
       <c r="O72" s="4" t="inlineStr">
@@ -5811,7 +5826,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G73" s="4" t="n">
+      <c r="G73" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -5892,7 +5907,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G74" s="4" t="n">
+      <c r="G74" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H74" s="4" t="inlineStr">
@@ -5973,7 +5988,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G75" s="4" t="n">
+      <c r="G75" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H75" s="4" t="inlineStr">
@@ -6054,7 +6069,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G76" s="4" t="n">
+      <c r="G76" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H76" s="4" t="inlineStr">
@@ -6135,7 +6150,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G77" s="4" t="n">
+      <c r="G77" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -6216,7 +6231,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G78" s="4" t="n">
+      <c r="G78" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H78" s="4" t="inlineStr">
@@ -6297,7 +6312,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G79" s="4" t="n">
+      <c r="G79" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -6378,7 +6393,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G80" s="4" t="n">
+      <c r="G80" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H80" s="4" t="inlineStr">
@@ -6459,7 +6474,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G81" s="4" t="n">
+      <c r="G81" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H81" s="4" t="inlineStr">
@@ -6540,7 +6555,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G82" s="4" t="n">
+      <c r="G82" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H82" s="4" t="inlineStr">
@@ -6621,7 +6636,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G83" s="4" t="n">
+      <c r="G83" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H83" s="4" t="inlineStr">
@@ -6702,7 +6717,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G84" s="4" t="n">
+      <c r="G84" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H84" s="4" t="inlineStr">
@@ -6783,7 +6798,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G85" s="4" t="n">
+      <c r="G85" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H85" s="4" t="inlineStr">
@@ -6864,7 +6879,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G86" s="4" t="n">
+      <c r="G86" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H86" s="4" t="inlineStr">
@@ -6945,7 +6960,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G87" s="4" t="n">
+      <c r="G87" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H87" s="4" t="inlineStr">
@@ -7026,7 +7041,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G88" s="4" t="n">
+      <c r="G88" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H88" s="4" t="inlineStr">
@@ -7107,7 +7122,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G89" s="4" t="n">
+      <c r="G89" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H89" s="4" t="inlineStr">
@@ -7188,7 +7203,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G90" s="4" t="n">
+      <c r="G90" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H90" s="4" t="inlineStr">
@@ -7269,7 +7284,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G91" s="4" t="n">
+      <c r="G91" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H91" s="4" t="inlineStr">
@@ -7350,7 +7365,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G92" s="4" t="n">
+      <c r="G92" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H92" s="4" t="inlineStr">
@@ -7431,7 +7446,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G93" s="4" t="n">
+      <c r="G93" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -7512,7 +7527,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G94" s="4" t="n">
+      <c r="G94" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H94" s="4" t="inlineStr">
@@ -7593,7 +7608,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G95" s="4" t="n">
+      <c r="G95" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H95" s="4" t="inlineStr">
@@ -7674,7 +7689,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G96" s="4" t="n">
+      <c r="G96" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H96" s="4" t="inlineStr">
@@ -7755,7 +7770,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G97" s="4" t="n">
+      <c r="G97" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H97" s="4" t="inlineStr">
@@ -7836,7 +7851,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G98" s="4" t="n">
+      <c r="G98" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H98" s="4" t="inlineStr">
@@ -7917,7 +7932,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G99" s="4" t="n">
+      <c r="G99" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H99" s="4" t="inlineStr">
@@ -7998,7 +8013,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G100" s="4" t="n">
+      <c r="G100" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H100" s="4" t="inlineStr">
@@ -8079,7 +8094,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G101" s="4" t="n">
+      <c r="G101" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H101" s="4" t="inlineStr">
@@ -8160,7 +8175,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G102" s="4" t="n">
+      <c r="G102" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H102" s="4" t="inlineStr">
@@ -8241,7 +8256,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G103" s="4" t="n">
+      <c r="G103" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H103" s="4" t="inlineStr">
@@ -8322,7 +8337,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G104" s="4" t="n">
+      <c r="G104" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H104" s="4" t="inlineStr">
@@ -8403,7 +8418,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G105" s="4" t="n">
+      <c r="G105" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H105" s="4" t="inlineStr">
@@ -8484,7 +8499,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G106" s="4" t="n">
+      <c r="G106" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H106" s="4" t="inlineStr">
@@ -8565,7 +8580,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G107" s="4" t="n">
+      <c r="G107" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H107" s="4" t="inlineStr">
@@ -8646,7 +8661,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G108" s="4" t="n">
+      <c r="G108" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H108" s="4" t="inlineStr">
@@ -8727,7 +8742,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G109" s="4" t="n">
+      <c r="G109" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H109" s="4" t="inlineStr">
@@ -8808,7 +8823,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G110" s="4" t="n">
+      <c r="G110" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H110" s="4" t="inlineStr">
@@ -8889,7 +8904,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G111" s="4" t="n">
+      <c r="G111" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H111" s="4" t="inlineStr">
@@ -8970,7 +8985,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G112" s="4" t="n">
+      <c r="G112" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H112" s="4" t="inlineStr">
@@ -9051,7 +9066,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G113" s="4" t="n">
+      <c r="G113" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H113" s="4" t="inlineStr">
@@ -9132,7 +9147,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G114" s="4" t="n">
+      <c r="G114" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H114" s="4" t="inlineStr">
@@ -9213,7 +9228,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G115" s="4" t="n">
+      <c r="G115" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H115" s="4" t="inlineStr">
@@ -9294,7 +9309,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G116" s="4" t="n">
+      <c r="G116" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H116" s="4" t="inlineStr">
@@ -9375,7 +9390,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G117" s="4" t="n">
+      <c r="G117" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H117" s="4" t="inlineStr">
@@ -9456,7 +9471,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G118" s="4" t="n">
+      <c r="G118" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H118" s="4" t="inlineStr">
@@ -9537,7 +9552,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G119" s="4" t="n">
+      <c r="G119" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H119" s="4" t="inlineStr">
@@ -9618,7 +9633,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G120" s="4" t="n">
+      <c r="G120" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H120" s="4" t="inlineStr">
@@ -9699,7 +9714,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G121" s="4" t="n">
+      <c r="G121" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H121" s="4" t="inlineStr">
@@ -9780,7 +9795,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G122" s="4" t="n">
+      <c r="G122" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H122" s="4" t="inlineStr">
@@ -9861,7 +9876,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G123" s="4" t="n">
+      <c r="G123" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H123" s="4" t="inlineStr">
@@ -9942,7 +9957,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G124" s="4" t="n">
+      <c r="G124" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H124" s="4" t="inlineStr">
@@ -10023,7 +10038,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G125" s="4" t="n">
+      <c r="G125" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H125" s="4" t="inlineStr">
@@ -10104,7 +10119,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G126" s="4" t="n">
+      <c r="G126" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H126" s="4" t="inlineStr">
@@ -10185,7 +10200,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G127" s="4" t="n">
+      <c r="G127" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H127" s="4" t="inlineStr">
@@ -10266,7 +10281,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G128" s="4" t="n">
+      <c r="G128" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H128" s="4" t="inlineStr">
@@ -10347,7 +10362,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G129" s="4" t="n">
+      <c r="G129" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H129" s="4" t="inlineStr">
@@ -10428,7 +10443,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G130" s="4" t="n">
+      <c r="G130" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H130" s="4" t="inlineStr">
@@ -10509,7 +10524,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G131" s="4" t="n">
+      <c r="G131" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H131" s="4" t="inlineStr">
@@ -10590,7 +10605,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G132" s="4" t="n">
+      <c r="G132" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H132" s="4" t="inlineStr">
@@ -10671,7 +10686,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G133" s="4" t="n">
+      <c r="G133" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H133" s="4" t="inlineStr">
@@ -10752,7 +10767,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G134" s="4" t="n">
+      <c r="G134" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H134" s="4" t="inlineStr">
@@ -10833,7 +10848,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G135" s="4" t="n">
+      <c r="G135" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H135" s="4" t="inlineStr">
@@ -10914,7 +10929,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G136" s="4" t="n">
+      <c r="G136" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H136" s="4" t="inlineStr">
@@ -10995,7 +11010,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G137" s="4" t="n">
+      <c r="G137" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H137" s="4" t="inlineStr">
@@ -11076,7 +11091,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G138" s="4" t="n">
+      <c r="G138" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H138" s="4" t="inlineStr">
@@ -11157,7 +11172,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G139" s="4" t="n">
+      <c r="G139" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="H139" s="4" t="inlineStr">
@@ -11238,7 +11253,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G140" s="4" t="n">
+      <c r="G140" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H140" s="4" t="inlineStr">
@@ -11319,7 +11334,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G141" s="4" t="n">
+      <c r="G141" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H141" s="4" t="inlineStr">
@@ -11400,7 +11415,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G142" s="4" t="n">
+      <c r="G142" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H142" s="4" t="inlineStr">
@@ -11481,7 +11496,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G143" s="4" t="n">
+      <c r="G143" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H143" s="4" t="inlineStr">
@@ -11562,7 +11577,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G144" s="4" t="n">
+      <c r="G144" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H144" s="4" t="inlineStr">
@@ -11643,7 +11658,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G145" s="4" t="n">
+      <c r="G145" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H145" s="4" t="inlineStr">
@@ -11724,7 +11739,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G146" s="4" t="n">
+      <c r="G146" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H146" s="4" t="inlineStr">
@@ -11805,7 +11820,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G147" s="4" t="n">
+      <c r="G147" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H147" s="4" t="inlineStr">
@@ -11886,7 +11901,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G148" s="4" t="n">
+      <c r="G148" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H148" s="4" t="inlineStr">
@@ -11967,7 +11982,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G149" s="4" t="n">
+      <c r="G149" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H149" s="4" t="inlineStr">
@@ -12048,7 +12063,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G150" s="4" t="n">
+      <c r="G150" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H150" s="4" t="inlineStr">
@@ -12129,7 +12144,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G151" s="4" t="n">
+      <c r="G151" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H151" s="4" t="inlineStr">
@@ -12210,7 +12225,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G152" s="4" t="n">
+      <c r="G152" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H152" s="4" t="inlineStr">
@@ -12291,7 +12306,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G153" s="4" t="n">
+      <c r="G153" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H153" s="4" t="inlineStr">
@@ -12372,7 +12387,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G154" s="4" t="n">
+      <c r="G154" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H154" s="4" t="inlineStr">
@@ -12453,7 +12468,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G155" s="4" t="n">
+      <c r="G155" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H155" s="4" t="inlineStr">
@@ -12534,7 +12549,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G156" s="4" t="n">
+      <c r="G156" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H156" s="4" t="inlineStr">
@@ -12615,7 +12630,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G157" s="4" t="n">
+      <c r="G157" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H157" s="4" t="inlineStr">
@@ -12696,7 +12711,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G158" s="4" t="n">
+      <c r="G158" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H158" s="4" t="inlineStr">
@@ -12777,7 +12792,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G159" s="4" t="n">
+      <c r="G159" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H159" s="4" t="inlineStr">
@@ -12858,7 +12873,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G160" s="4" t="n">
+      <c r="G160" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H160" s="4" t="inlineStr">
@@ -12939,7 +12954,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G161" s="4" t="n">
+      <c r="G161" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H161" s="4" t="inlineStr">
@@ -13020,7 +13035,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G162" s="4" t="n">
+      <c r="G162" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H162" s="4" t="inlineStr">
@@ -13101,7 +13116,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G163" s="4" t="n">
+      <c r="G163" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H163" s="4" t="inlineStr">
@@ -13182,7 +13197,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G164" s="4" t="n">
+      <c r="G164" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H164" s="4" t="inlineStr">
@@ -13263,7 +13278,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G165" s="4" t="n">
+      <c r="G165" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H165" s="4" t="inlineStr">
@@ -13344,7 +13359,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G166" s="4" t="n">
+      <c r="G166" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H166" s="4" t="inlineStr">
@@ -13425,7 +13440,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G167" s="4" t="n">
+      <c r="G167" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H167" s="4" t="inlineStr">
@@ -13506,7 +13521,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G168" s="4" t="n">
+      <c r="G168" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H168" s="4" t="inlineStr">
@@ -13587,7 +13602,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G169" s="4" t="n">
+      <c r="G169" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H169" s="4" t="inlineStr">
@@ -13668,7 +13683,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G170" s="4" t="n">
+      <c r="G170" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H170" s="4" t="inlineStr">
@@ -13749,7 +13764,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G171" s="4" t="n">
+      <c r="G171" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H171" s="4" t="inlineStr">
@@ -13830,7 +13845,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G172" s="4" t="n">
+      <c r="G172" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H172" s="4" t="inlineStr">
@@ -13911,7 +13926,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G173" s="4" t="n">
+      <c r="G173" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H173" s="4" t="inlineStr">
@@ -13992,7 +14007,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G174" s="4" t="n">
+      <c r="G174" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H174" s="4" t="inlineStr">
@@ -14073,7 +14088,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G175" s="4" t="n">
+      <c r="G175" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H175" s="4" t="inlineStr">
@@ -14154,7 +14169,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G176" s="4" t="n">
+      <c r="G176" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H176" s="4" t="inlineStr">
@@ -14235,7 +14250,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G177" s="4" t="n">
+      <c r="G177" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H177" s="4" t="inlineStr">
@@ -14316,7 +14331,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G178" s="4" t="n">
+      <c r="G178" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H178" s="4" t="inlineStr">
@@ -14397,7 +14412,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G179" s="4" t="n">
+      <c r="G179" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H179" s="4" t="inlineStr">
@@ -14478,7 +14493,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G180" s="4" t="n">
+      <c r="G180" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H180" s="4" t="inlineStr">
@@ -14559,7 +14574,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G181" s="4" t="n">
+      <c r="G181" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H181" s="4" t="inlineStr">
@@ -14640,7 +14655,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G182" s="4" t="n">
+      <c r="G182" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H182" s="4" t="inlineStr">
@@ -14721,7 +14736,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G183" s="4" t="n">
+      <c r="G183" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H183" s="4" t="inlineStr">
@@ -14802,7 +14817,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G184" s="4" t="n">
+      <c r="G184" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H184" s="4" t="inlineStr">
@@ -14883,7 +14898,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G185" s="4" t="n">
+      <c r="G185" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H185" s="4" t="inlineStr">
@@ -14964,7 +14979,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G186" s="4" t="n">
+      <c r="G186" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H186" s="4" t="inlineStr">
@@ -15045,7 +15060,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G187" s="4" t="n">
+      <c r="G187" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H187" s="4" t="inlineStr">
@@ -15126,7 +15141,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G188" s="4" t="n">
+      <c r="G188" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H188" s="4" t="inlineStr">
@@ -15207,7 +15222,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G189" s="4" t="n">
+      <c r="G189" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H189" s="4" t="inlineStr">
@@ -15288,7 +15303,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G190" s="4" t="n">
+      <c r="G190" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H190" s="4" t="inlineStr">
@@ -15369,7 +15384,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G191" s="4" t="n">
+      <c r="G191" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H191" s="4" t="inlineStr">
@@ -15450,7 +15465,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G192" s="4" t="n">
+      <c r="G192" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H192" s="4" t="inlineStr">
@@ -15531,7 +15546,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G193" s="4" t="n">
+      <c r="G193" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H193" s="4" t="inlineStr">
@@ -15612,7 +15627,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G194" s="4" t="n">
+      <c r="G194" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H194" s="4" t="inlineStr">
@@ -15693,7 +15708,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G195" s="4" t="n">
+      <c r="G195" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H195" s="4" t="inlineStr">
@@ -15774,7 +15789,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G196" s="4" t="n">
+      <c r="G196" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H196" s="4" t="inlineStr">
@@ -15855,7 +15870,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G197" s="4" t="n">
+      <c r="G197" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H197" s="4" t="inlineStr">
@@ -15936,7 +15951,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G198" s="4" t="n">
+      <c r="G198" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H198" s="4" t="inlineStr">
@@ -16017,7 +16032,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G199" s="4" t="n">
+      <c r="G199" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H199" s="4" t="inlineStr">
@@ -16098,7 +16113,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G200" s="4" t="n">
+      <c r="G200" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H200" s="4" t="inlineStr">
@@ -16179,7 +16194,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G201" s="4" t="n">
+      <c r="G201" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H201" s="4" t="inlineStr">
@@ -16260,7 +16275,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G202" s="4" t="n">
+      <c r="G202" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H202" s="4" t="inlineStr">
@@ -16341,7 +16356,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G203" s="4" t="n">
+      <c r="G203" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H203" s="4" t="inlineStr">
@@ -16422,7 +16437,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G204" s="4" t="n">
+      <c r="G204" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H204" s="4" t="inlineStr">
@@ -16503,7 +16518,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G205" s="4" t="n">
+      <c r="G205" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H205" s="4" t="inlineStr">
@@ -16584,7 +16599,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G206" s="4" t="n">
+      <c r="G206" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="H206" s="4" t="inlineStr">
@@ -16665,7 +16680,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G207" s="4" t="n">
+      <c r="G207" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H207" s="4" t="inlineStr">
@@ -16746,7 +16761,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G208" s="4" t="n">
+      <c r="G208" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H208" s="4" t="inlineStr">
@@ -16827,7 +16842,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G209" s="4" t="n">
+      <c r="G209" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H209" s="4" t="inlineStr">
@@ -16908,7 +16923,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G210" s="4" t="n">
+      <c r="G210" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H210" s="4" t="inlineStr">
@@ -16989,7 +17004,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G211" s="4" t="n">
+      <c r="G211" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H211" s="4" t="inlineStr">
@@ -17070,7 +17085,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G212" s="4" t="n">
+      <c r="G212" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H212" s="4" t="inlineStr">
@@ -17151,7 +17166,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G213" s="4" t="n">
+      <c r="G213" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H213" s="4" t="inlineStr">
@@ -17232,7 +17247,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G214" s="4" t="n">
+      <c r="G214" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H214" s="4" t="inlineStr">
@@ -17313,7 +17328,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G215" s="4" t="n">
+      <c r="G215" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H215" s="4" t="inlineStr">
@@ -17394,7 +17409,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G216" s="4" t="n">
+      <c r="G216" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H216" s="4" t="inlineStr">
@@ -17475,7 +17490,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G217" s="4" t="n">
+      <c r="G217" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H217" s="4" t="inlineStr">
@@ -17556,7 +17571,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G218" s="4" t="n">
+      <c r="G218" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H218" s="4" t="inlineStr">
@@ -17637,7 +17652,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G219" s="4" t="n">
+      <c r="G219" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H219" s="4" t="inlineStr">
@@ -17718,7 +17733,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G220" s="4" t="n">
+      <c r="G220" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H220" s="4" t="inlineStr">
@@ -17799,7 +17814,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G221" s="4" t="n">
+      <c r="G221" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H221" s="4" t="inlineStr">
@@ -17880,7 +17895,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G222" s="4" t="n">
+      <c r="G222" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H222" s="4" t="inlineStr">
@@ -17961,7 +17976,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G223" s="4" t="n">
+      <c r="G223" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H223" s="4" t="inlineStr">
@@ -18042,7 +18057,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G224" s="4" t="n">
+      <c r="G224" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H224" s="4" t="inlineStr">
@@ -18123,7 +18138,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G225" s="4" t="n">
+      <c r="G225" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H225" s="4" t="inlineStr">
@@ -18204,7 +18219,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G226" s="4" t="n">
+      <c r="G226" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H226" s="4" t="inlineStr">
@@ -18285,7 +18300,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G227" s="4" t="n">
+      <c r="G227" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H227" s="4" t="inlineStr">
@@ -18366,7 +18381,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G228" s="4" t="n">
+      <c r="G228" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H228" s="4" t="inlineStr">
@@ -18447,7 +18462,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G229" s="4" t="n">
+      <c r="G229" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H229" s="4" t="inlineStr">
@@ -18528,7 +18543,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G230" s="4" t="n">
+      <c r="G230" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H230" s="4" t="inlineStr">
@@ -18609,7 +18624,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G231" s="4" t="n">
+      <c r="G231" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H231" s="4" t="inlineStr">
@@ -18690,7 +18705,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G232" s="4" t="n">
+      <c r="G232" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H232" s="4" t="inlineStr">
@@ -18771,7 +18786,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G233" s="4" t="n">
+      <c r="G233" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H233" s="4" t="inlineStr">
@@ -18852,7 +18867,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G234" s="4" t="n">
+      <c r="G234" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H234" s="4" t="inlineStr">
@@ -18933,7 +18948,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G235" s="4" t="n">
+      <c r="G235" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H235" s="4" t="inlineStr">
@@ -19014,7 +19029,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G236" s="4" t="n">
+      <c r="G236" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H236" s="4" t="inlineStr">
@@ -19095,7 +19110,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G237" s="4" t="n">
+      <c r="G237" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H237" s="4" t="inlineStr">
@@ -19176,7 +19191,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G238" s="4" t="n">
+      <c r="G238" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H238" s="4" t="inlineStr">
@@ -19257,7 +19272,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G239" s="4" t="n">
+      <c r="G239" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H239" s="4" t="inlineStr">
@@ -19338,7 +19353,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G240" s="4" t="n">
+      <c r="G240" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H240" s="4" t="inlineStr">
@@ -19419,7 +19434,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G241" s="4" t="n">
+      <c r="G241" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H241" s="4" t="inlineStr">
@@ -19500,7 +19515,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G242" s="4" t="n">
+      <c r="G242" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H242" s="4" t="inlineStr">
@@ -19581,7 +19596,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G243" s="4" t="n">
+      <c r="G243" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H243" s="4" t="inlineStr">
@@ -19662,7 +19677,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G244" s="4" t="n">
+      <c r="G244" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H244" s="4" t="inlineStr">
@@ -19743,7 +19758,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G245" s="4" t="n">
+      <c r="G245" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H245" s="4" t="inlineStr">
@@ -19824,7 +19839,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G246" s="4" t="n">
+      <c r="G246" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H246" s="4" t="inlineStr">
@@ -19905,7 +19920,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G247" s="4" t="n">
+      <c r="G247" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H247" s="4" t="inlineStr">
@@ -19986,7 +20001,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G248" s="4" t="n">
+      <c r="G248" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H248" s="4" t="inlineStr">
@@ -20067,7 +20082,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G249" s="4" t="n">
+      <c r="G249" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H249" s="4" t="inlineStr">
@@ -20148,7 +20163,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G250" s="4" t="n">
+      <c r="G250" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H250" s="4" t="inlineStr">
@@ -20229,7 +20244,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G251" s="4" t="n">
+      <c r="G251" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H251" s="4" t="inlineStr">
@@ -20310,7 +20325,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G252" s="4" t="n">
+      <c r="G252" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H252" s="4" t="inlineStr">
@@ -20391,7 +20406,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G253" s="4" t="n">
+      <c r="G253" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H253" s="4" t="inlineStr">
@@ -20472,7 +20487,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G254" s="4" t="n">
+      <c r="G254" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H254" s="4" t="inlineStr">
@@ -20553,7 +20568,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G255" s="4" t="n">
+      <c r="G255" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H255" s="4" t="inlineStr">
@@ -20634,7 +20649,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G256" s="4" t="n">
+      <c r="G256" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H256" s="4" t="inlineStr">
@@ -20715,7 +20730,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G257" s="4" t="n">
+      <c r="G257" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H257" s="4" t="inlineStr">
@@ -20796,7 +20811,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G258" s="4" t="n">
+      <c r="G258" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H258" s="4" t="inlineStr">
@@ -20877,7 +20892,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G259" s="4" t="n">
+      <c r="G259" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H259" s="4" t="inlineStr">
@@ -20958,7 +20973,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G260" s="4" t="n">
+      <c r="G260" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H260" s="4" t="inlineStr">
@@ -21039,7 +21054,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G261" s="4" t="n">
+      <c r="G261" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H261" s="4" t="inlineStr">
@@ -21120,7 +21135,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G262" s="4" t="n">
+      <c r="G262" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H262" s="4" t="inlineStr">
@@ -21201,7 +21216,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G263" s="4" t="n">
+      <c r="G263" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H263" s="4" t="inlineStr">
@@ -21282,7 +21297,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G264" s="4" t="n">
+      <c r="G264" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H264" s="4" t="inlineStr">
@@ -21363,7 +21378,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G265" s="4" t="n">
+      <c r="G265" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H265" s="4" t="inlineStr">
@@ -21444,7 +21459,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G266" s="4" t="n">
+      <c r="G266" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H266" s="4" t="inlineStr">
@@ -21525,7 +21540,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G267" s="4" t="n">
+      <c r="G267" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H267" s="4" t="inlineStr">
@@ -21606,7 +21621,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G268" s="4" t="n">
+      <c r="G268" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H268" s="4" t="inlineStr">
@@ -21687,7 +21702,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G269" s="4" t="n">
+      <c r="G269" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H269" s="4" t="inlineStr">
@@ -21768,7 +21783,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G270" s="4" t="n">
+      <c r="G270" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H270" s="4" t="inlineStr">
@@ -21849,7 +21864,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G271" s="4" t="n">
+      <c r="G271" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H271" s="4" t="inlineStr">
@@ -21930,7 +21945,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G272" s="4" t="n">
+      <c r="G272" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H272" s="4" t="inlineStr">
@@ -22011,7 +22026,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G273" s="4" t="n">
+      <c r="G273" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="H273" s="4" t="inlineStr">
@@ -22092,7 +22107,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G274" s="4" t="n">
+      <c r="G274" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H274" s="4" t="inlineStr">
@@ -22169,7 +22184,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G275" s="4" t="n">
+      <c r="G275" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H275" s="4" t="inlineStr">
@@ -22246,7 +22261,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G276" s="4" t="n">
+      <c r="G276" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H276" s="4" t="inlineStr">
@@ -22323,7 +22338,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G277" s="4" t="n">
+      <c r="G277" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H277" s="4" t="inlineStr">
@@ -22400,7 +22415,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G278" s="4" t="n">
+      <c r="G278" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H278" s="4" t="inlineStr">
@@ -22477,7 +22492,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G279" s="4" t="n">
+      <c r="G279" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H279" s="4" t="inlineStr">
@@ -22554,7 +22569,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G280" s="4" t="n">
+      <c r="G280" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H280" s="4" t="inlineStr">
@@ -22631,7 +22646,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G281" s="4" t="n">
+      <c r="G281" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H281" s="4" t="inlineStr">
@@ -22708,7 +22723,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G282" s="4" t="n">
+      <c r="G282" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H282" s="4" t="inlineStr">
@@ -22741,7 +22756,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N282" s="4" t="n">
+      <c r="N282" s="8" t="n">
         <v>56.9223784741446</v>
       </c>
       <c r="O282" s="4" t="inlineStr">
@@ -22787,7 +22802,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G283" s="4" t="n">
+      <c r="G283" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H283" s="4" t="inlineStr">
@@ -22820,7 +22835,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N283" s="4" t="n">
+      <c r="N283" s="8" t="n">
         <v>60.5220059201003</v>
       </c>
       <c r="O283" s="4" t="inlineStr">
@@ -22866,7 +22881,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G284" s="4" t="n">
+      <c r="G284" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H284" s="4" t="inlineStr">
@@ -22899,7 +22914,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N284" s="4" t="n">
+      <c r="N284" s="8" t="n">
         <v>57.7451225372417</v>
       </c>
       <c r="O284" s="4" t="inlineStr">
@@ -22945,7 +22960,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G285" s="4" t="n">
+      <c r="G285" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H285" s="4" t="inlineStr">
@@ -22978,7 +22993,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N285" s="4" t="n">
+      <c r="N285" s="8" t="n">
         <v>58.3076950000875</v>
       </c>
       <c r="O285" s="4" t="inlineStr">
@@ -23024,7 +23039,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G286" s="4" t="n">
+      <c r="G286" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H286" s="4" t="inlineStr">
@@ -23057,7 +23072,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N286" s="4" t="n">
+      <c r="N286" s="8" t="n">
         <v>60.5900621118012</v>
       </c>
       <c r="O286" s="4" t="inlineStr">
@@ -23103,7 +23118,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G287" s="4" t="n">
+      <c r="G287" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H287" s="4" t="inlineStr">
@@ -23136,7 +23151,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N287" s="4" t="n">
+      <c r="N287" s="8" t="n">
         <v>57.0784814273818</v>
       </c>
       <c r="O287" s="4" t="inlineStr">
@@ -23182,7 +23197,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G288" s="4" t="n">
+      <c r="G288" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H288" s="4" t="inlineStr">
@@ -23215,7 +23230,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N288" s="4" t="n">
+      <c r="N288" s="8" t="n">
         <v>44.9942976281697</v>
       </c>
       <c r="O288" s="4" t="inlineStr">
@@ -23261,7 +23276,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G289" s="4" t="n">
+      <c r="G289" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H289" s="4" t="inlineStr">
@@ -23294,7 +23309,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N289" s="4" t="n">
+      <c r="N289" s="8" t="n">
         <v>53.4799911937543</v>
       </c>
       <c r="O289" s="4" t="inlineStr">
@@ -23340,7 +23355,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G290" s="4" t="n">
+      <c r="G290" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H290" s="4" t="inlineStr">
@@ -23373,7 +23388,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N290" s="4" t="n">
+      <c r="N290" s="8" t="n">
         <v>55.4168640454761</v>
       </c>
       <c r="O290" s="4" t="inlineStr">
@@ -23419,7 +23434,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G291" s="4" t="n">
+      <c r="G291" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H291" s="4" t="inlineStr">
@@ -23452,7 +23467,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N291" s="4" t="n">
+      <c r="N291" s="8" t="n">
         <v>57.285332614029</v>
       </c>
       <c r="O291" s="4" t="inlineStr">
@@ -23498,7 +23513,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G292" s="4" t="n">
+      <c r="G292" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H292" s="4" t="inlineStr">
@@ -23531,7 +23546,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N292" s="4" t="n">
+      <c r="N292" s="8" t="n">
         <v>60.160298119011</v>
       </c>
       <c r="O292" s="4" t="inlineStr">
@@ -23577,7 +23592,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G293" s="4" t="n">
+      <c r="G293" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H293" s="4" t="inlineStr">
@@ -23610,7 +23625,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N293" s="4" t="n">
+      <c r="N293" s="8" t="n">
         <v>54.9285394513255</v>
       </c>
       <c r="O293" s="4" t="inlineStr">
@@ -23656,7 +23671,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G294" s="4" t="n">
+      <c r="G294" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H294" s="4" t="inlineStr">
@@ -23689,7 +23704,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N294" s="4" t="n">
+      <c r="N294" s="8" t="n">
         <v>53.863714147466</v>
       </c>
       <c r="O294" s="4" t="inlineStr">
@@ -23735,7 +23750,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G295" s="4" t="n">
+      <c r="G295" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H295" s="4" t="inlineStr">
@@ -23768,7 +23783,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N295" s="4" t="n">
+      <c r="N295" s="8" t="n">
         <v>56.1667625031556</v>
       </c>
       <c r="O295" s="4" t="inlineStr">
@@ -23814,7 +23829,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G296" s="4" t="n">
+      <c r="G296" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H296" s="4" t="inlineStr">
@@ -23847,7 +23862,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N296" s="4" t="n">
+      <c r="N296" s="8" t="n">
         <v>58.4518381696582</v>
       </c>
       <c r="O296" s="4" t="inlineStr">
@@ -23893,7 +23908,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G297" s="4" t="n">
+      <c r="G297" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H297" s="4" t="inlineStr">
@@ -23926,7 +23941,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N297" s="4" t="n">
+      <c r="N297" s="8" t="n">
         <v>61.0546245679743</v>
       </c>
       <c r="O297" s="4" t="inlineStr">
@@ -23972,7 +23987,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G298" s="4" t="n">
+      <c r="G298" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H298" s="4" t="inlineStr">
@@ -24005,7 +24020,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N298" s="4" t="n">
+      <c r="N298" s="8" t="n">
         <v>37.4177760003047</v>
       </c>
       <c r="O298" s="4" t="inlineStr">
@@ -24051,7 +24066,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G299" s="4" t="n">
+      <c r="G299" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H299" s="4" t="inlineStr">
@@ -24084,7 +24099,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N299" s="4" t="n">
+      <c r="N299" s="8" t="n">
         <v>38.113594453685</v>
       </c>
       <c r="O299" s="4" t="inlineStr">
@@ -24130,7 +24145,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G300" s="4" t="n">
+      <c r="G300" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H300" s="4" t="inlineStr">
@@ -24163,7 +24178,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N300" s="4" t="n">
+      <c r="N300" s="8" t="n">
         <v>42.3918171931345</v>
       </c>
       <c r="O300" s="4" t="inlineStr">
@@ -24209,7 +24224,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G301" s="4" t="n">
+      <c r="G301" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H301" s="4" t="inlineStr">
@@ -24242,7 +24257,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N301" s="4" t="n">
+      <c r="N301" s="8" t="n">
         <v>38.764152717968</v>
       </c>
       <c r="O301" s="4" t="inlineStr">
@@ -24288,7 +24303,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G302" s="4" t="n">
+      <c r="G302" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H302" s="4" t="inlineStr">
@@ -24321,7 +24336,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N302" s="4" t="n">
+      <c r="N302" s="8" t="n">
         <v>39.8318872576244</v>
       </c>
       <c r="O302" s="4" t="inlineStr">
@@ -24367,7 +24382,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G303" s="4" t="n">
+      <c r="G303" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H303" s="4" t="inlineStr">
@@ -24400,7 +24415,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N303" s="4" t="n">
+      <c r="N303" s="8" t="n">
         <v>34.2879483779044</v>
       </c>
       <c r="O303" s="4" t="inlineStr">
@@ -24446,7 +24461,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G304" s="4" t="n">
+      <c r="G304" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H304" s="4" t="inlineStr">
@@ -24479,7 +24494,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N304" s="4" t="n">
+      <c r="N304" s="8" t="n">
         <v>32.3949034358066</v>
       </c>
       <c r="O304" s="4" t="inlineStr">
@@ -24525,7 +24540,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G305" s="4" t="n">
+      <c r="G305" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H305" s="4" t="inlineStr">
@@ -24558,7 +24573,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N305" s="4" t="n">
+      <c r="N305" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O305" s="4" t="inlineStr">
@@ -24604,7 +24619,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G306" s="4" t="n">
+      <c r="G306" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H306" s="4" t="inlineStr">
@@ -24637,7 +24652,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N306" s="4" t="n">
+      <c r="N306" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O306" s="4" t="inlineStr">
@@ -24683,7 +24698,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G307" s="4" t="n">
+      <c r="G307" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H307" s="4" t="inlineStr">
@@ -24716,7 +24731,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N307" s="4" t="n">
+      <c r="N307" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O307" s="4" t="inlineStr">
@@ -24762,7 +24777,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G308" s="4" t="n">
+      <c r="G308" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H308" s="4" t="inlineStr">
@@ -24795,7 +24810,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N308" s="4" t="n">
+      <c r="N308" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O308" s="4" t="inlineStr">
@@ -24841,7 +24856,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G309" s="4" t="n">
+      <c r="G309" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H309" s="4" t="inlineStr">
@@ -24874,7 +24889,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N309" s="4" t="n">
+      <c r="N309" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O309" s="4" t="inlineStr">
@@ -24920,7 +24935,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G310" s="4" t="n">
+      <c r="G310" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H310" s="4" t="inlineStr">
@@ -24953,7 +24968,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N310" s="4" t="n">
+      <c r="N310" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O310" s="4" t="inlineStr">
@@ -24999,7 +25014,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G311" s="4" t="n">
+      <c r="G311" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H311" s="4" t="inlineStr">
@@ -25032,7 +25047,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N311" s="4" t="n">
+      <c r="N311" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O311" s="4" t="inlineStr">
@@ -25078,7 +25093,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G312" s="4" t="n">
+      <c r="G312" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H312" s="4" t="inlineStr">
@@ -25111,7 +25126,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N312" s="4" t="n">
+      <c r="N312" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O312" s="4" t="inlineStr">
@@ -25157,7 +25172,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G313" s="4" t="n">
+      <c r="G313" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H313" s="4" t="inlineStr">
@@ -25190,7 +25205,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N313" s="4" t="n">
+      <c r="N313" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O313" s="4" t="inlineStr">
@@ -25236,7 +25251,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G314" s="4" t="n">
+      <c r="G314" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H314" s="4" t="inlineStr">
@@ -25269,7 +25284,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N314" s="4" t="n">
+      <c r="N314" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O314" s="4" t="inlineStr">
@@ -25315,7 +25330,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G315" s="4" t="n">
+      <c r="G315" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H315" s="4" t="inlineStr">
@@ -25348,7 +25363,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N315" s="4" t="n">
+      <c r="N315" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O315" s="4" t="inlineStr">
@@ -25394,7 +25409,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G316" s="4" t="n">
+      <c r="G316" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H316" s="4" t="inlineStr">
@@ -25427,7 +25442,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N316" s="4" t="n">
+      <c r="N316" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O316" s="4" t="inlineStr">
@@ -25473,7 +25488,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G317" s="4" t="n">
+      <c r="G317" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H317" s="4" t="inlineStr">
@@ -25506,7 +25521,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N317" s="4" t="n">
+      <c r="N317" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O317" s="4" t="inlineStr">
@@ -25552,7 +25567,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G318" s="4" t="n">
+      <c r="G318" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H318" s="4" t="inlineStr">
@@ -25585,7 +25600,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N318" s="4" t="n">
+      <c r="N318" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O318" s="4" t="inlineStr">
@@ -25631,7 +25646,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G319" s="4" t="n">
+      <c r="G319" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H319" s="4" t="inlineStr">
@@ -25664,7 +25679,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N319" s="4" t="n">
+      <c r="N319" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O319" s="4" t="inlineStr">
@@ -25710,7 +25725,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G320" s="4" t="n">
+      <c r="G320" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H320" s="4" t="inlineStr">
@@ -25743,7 +25758,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N320" s="4" t="n">
+      <c r="N320" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O320" s="4" t="inlineStr">
@@ -25789,7 +25804,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G321" s="4" t="n">
+      <c r="G321" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H321" s="4" t="inlineStr">
@@ -25822,7 +25837,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N321" s="4" t="n">
+      <c r="N321" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O321" s="4" t="inlineStr">
@@ -25868,7 +25883,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G322" s="4" t="n">
+      <c r="G322" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H322" s="4" t="inlineStr">
@@ -25901,7 +25916,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N322" s="4" t="n">
+      <c r="N322" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O322" s="4" t="inlineStr">
@@ -25947,7 +25962,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G323" s="4" t="n">
+      <c r="G323" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H323" s="4" t="inlineStr">
@@ -25980,7 +25995,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N323" s="4" t="n">
+      <c r="N323" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O323" s="4" t="inlineStr">
@@ -26026,7 +26041,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G324" s="4" t="n">
+      <c r="G324" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H324" s="4" t="inlineStr">
@@ -26059,7 +26074,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N324" s="4" t="n">
+      <c r="N324" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O324" s="4" t="inlineStr">
@@ -26105,7 +26120,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G325" s="4" t="n">
+      <c r="G325" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H325" s="4" t="inlineStr">
@@ -26138,7 +26153,7 @@
           <t>Valor agregado de los servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N325" s="4" t="n">
+      <c r="N325" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O325" s="4" t="inlineStr">
@@ -26184,7 +26199,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G326" s="4" t="n">
+      <c r="G326" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H326" s="4" t="inlineStr">
@@ -26261,7 +26276,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G327" s="4" t="n">
+      <c r="G327" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H327" s="4" t="inlineStr">
@@ -26338,7 +26353,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G328" s="4" t="n">
+      <c r="G328" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H328" s="4" t="inlineStr">
@@ -26415,7 +26430,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G329" s="4" t="n">
+      <c r="G329" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H329" s="4" t="inlineStr">
@@ -26492,7 +26507,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G330" s="4" t="n">
+      <c r="G330" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H330" s="4" t="inlineStr">
@@ -26569,7 +26584,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G331" s="4" t="n">
+      <c r="G331" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H331" s="4" t="inlineStr">
@@ -26646,7 +26661,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G332" s="4" t="n">
+      <c r="G332" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H332" s="4" t="inlineStr">
@@ -26723,7 +26738,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G333" s="4" t="n">
+      <c r="G333" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H333" s="4" t="inlineStr">
@@ -26800,7 +26815,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G334" s="4" t="n">
+      <c r="G334" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H334" s="4" t="inlineStr">
@@ -26877,7 +26892,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G335" s="4" t="n">
+      <c r="G335" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H335" s="4" t="inlineStr">
@@ -26954,7 +26969,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G336" s="4" t="n">
+      <c r="G336" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H336" s="4" t="inlineStr">
@@ -27031,7 +27046,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G337" s="4" t="n">
+      <c r="G337" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H337" s="4" t="inlineStr">
@@ -27108,7 +27123,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G338" s="4" t="n">
+      <c r="G338" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H338" s="4" t="inlineStr">
@@ -27185,7 +27200,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G339" s="4" t="n">
+      <c r="G339" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H339" s="4" t="inlineStr">
@@ -27262,7 +27277,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G340" s="4" t="n">
+      <c r="G340" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H340" s="4" t="inlineStr">
@@ -27295,7 +27310,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N340" s="4" t="n">
+      <c r="N340" s="8" t="n">
         <v>7663938303.07171</v>
       </c>
       <c r="O340" s="4" t="inlineStr">
@@ -27341,7 +27356,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G341" s="4" t="n">
+      <c r="G341" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H341" s="4" t="inlineStr">
@@ -27374,7 +27389,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N341" s="4" t="n">
+      <c r="N341" s="8" t="n">
         <v>8067267030.61862</v>
       </c>
       <c r="O341" s="4" t="inlineStr">
@@ -27420,7 +27435,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G342" s="4" t="n">
+      <c r="G342" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H342" s="4" t="inlineStr">
@@ -27453,7 +27468,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N342" s="4" t="n">
+      <c r="N342" s="8" t="n">
         <v>8814309884.211651</v>
       </c>
       <c r="O342" s="4" t="inlineStr">
@@ -27499,7 +27514,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G343" s="4" t="n">
+      <c r="G343" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H343" s="4" t="inlineStr">
@@ -27532,7 +27547,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N343" s="4" t="n">
+      <c r="N343" s="8" t="n">
         <v>9608717288.17057</v>
       </c>
       <c r="O343" s="4" t="inlineStr">
@@ -27578,7 +27593,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G344" s="4" t="n">
+      <c r="G344" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H344" s="4" t="inlineStr">
@@ -27611,7 +27626,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N344" s="4" t="n">
+      <c r="N344" s="8" t="n">
         <v>8192413793.10345</v>
       </c>
       <c r="O344" s="4" t="inlineStr">
@@ -27657,7 +27672,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G345" s="4" t="n">
+      <c r="G345" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H345" s="4" t="inlineStr">
@@ -27690,7 +27705,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N345" s="4" t="n">
+      <c r="N345" s="8" t="n">
         <v>8427777777.77778</v>
       </c>
       <c r="O345" s="4" t="inlineStr">
@@ -27736,7 +27751,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G346" s="4" t="n">
+      <c r="G346" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H346" s="4" t="inlineStr">
@@ -27769,7 +27784,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N346" s="4" t="n">
+      <c r="N346" s="8" t="n">
         <v>8781333333.33333</v>
       </c>
       <c r="O346" s="4" t="inlineStr">
@@ -27815,7 +27830,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G347" s="4" t="n">
+      <c r="G347" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H347" s="4" t="inlineStr">
@@ -27848,7 +27863,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N347" s="4" t="n">
+      <c r="N347" s="7" t="n">
         <v>9250000000</v>
       </c>
       <c r="O347" s="4" t="inlineStr">
@@ -27894,7 +27909,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G348" s="4" t="n">
+      <c r="G348" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H348" s="4" t="inlineStr">
@@ -27927,7 +27942,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N348" s="4" t="n">
+      <c r="N348" s="8" t="n">
         <v>10034444444.4444</v>
       </c>
       <c r="O348" s="4" t="inlineStr">
@@ -27973,7 +27988,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G349" s="4" t="n">
+      <c r="G349" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H349" s="4" t="inlineStr">
@@ -28006,7 +28021,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N349" s="4" t="n">
+      <c r="N349" s="8" t="n">
         <v>10285111111.1111</v>
       </c>
       <c r="O349" s="4" t="inlineStr">
@@ -28052,7 +28067,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G350" s="4" t="n">
+      <c r="G350" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H350" s="4" t="inlineStr">
@@ -28085,7 +28100,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N350" s="4" t="n">
+      <c r="N350" s="8" t="n">
         <v>11561111111.1111</v>
       </c>
       <c r="O350" s="4" t="inlineStr">
@@ -28131,7 +28146,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G351" s="4" t="n">
+      <c r="G351" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H351" s="4" t="inlineStr">
@@ -28164,7 +28179,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N351" s="4" t="n">
+      <c r="N351" s="8" t="n">
         <v>12986590909.0909</v>
       </c>
       <c r="O351" s="4" t="inlineStr">
@@ -28210,7 +28225,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G352" s="4" t="n">
+      <c r="G352" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H352" s="4" t="inlineStr">
@@ -28243,7 +28258,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N352" s="4" t="n">
+      <c r="N352" s="8" t="n">
         <v>13977727272.7273</v>
       </c>
       <c r="O352" s="4" t="inlineStr">
@@ -28289,7 +28304,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G353" s="4" t="n">
+      <c r="G353" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H353" s="4" t="inlineStr">
@@ -28322,7 +28337,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N353" s="4" t="n">
+      <c r="N353" s="8" t="n">
         <v>17035581395.3488</v>
       </c>
       <c r="O353" s="4" t="inlineStr">
@@ -28368,7 +28383,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G354" s="4" t="n">
+      <c r="G354" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H354" s="4" t="inlineStr">
@@ -28401,7 +28416,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N354" s="4" t="n">
+      <c r="N354" s="8" t="n">
         <v>26100930232.5581</v>
       </c>
       <c r="O354" s="4" t="inlineStr">
@@ -28447,7 +28462,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G355" s="4" t="n">
+      <c r="G355" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H355" s="4" t="inlineStr">
@@ -28480,7 +28495,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N355" s="4" t="n">
+      <c r="N355" s="8" t="n">
         <v>27464651162.7907</v>
       </c>
       <c r="O355" s="4" t="inlineStr">
@@ -28526,7 +28541,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G356" s="4" t="n">
+      <c r="G356" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H356" s="4" t="inlineStr">
@@ -28559,7 +28574,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N356" s="4" t="n">
+      <c r="N356" s="8" t="n">
         <v>31419534883.7209</v>
       </c>
       <c r="O356" s="4" t="inlineStr">
@@ -28605,7 +28620,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G357" s="4" t="n">
+      <c r="G357" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H357" s="4" t="inlineStr">
@@ -28638,7 +28653,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N357" s="4" t="n">
+      <c r="N357" s="8" t="n">
         <v>36210697674.4186</v>
       </c>
       <c r="O357" s="4" t="inlineStr">
@@ -28684,7 +28699,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G358" s="4" t="n">
+      <c r="G358" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H358" s="4" t="inlineStr">
@@ -28717,7 +28732,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N358" s="4" t="n">
+      <c r="N358" s="8" t="n">
         <v>39316279069.7674</v>
       </c>
       <c r="O358" s="4" t="inlineStr">
@@ -28763,7 +28778,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G359" s="4" t="n">
+      <c r="G359" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H359" s="4" t="inlineStr">
@@ -28796,7 +28811,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N359" s="4" t="n">
+      <c r="N359" s="8" t="n">
         <v>48310930232.5581</v>
       </c>
       <c r="O359" s="4" t="inlineStr">
@@ -28842,7 +28857,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G360" s="4" t="n">
+      <c r="G360" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H360" s="4" t="inlineStr">
@@ -28875,7 +28890,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N360" s="4" t="n">
+      <c r="N360" s="8" t="n">
         <v>59116511627.907</v>
       </c>
       <c r="O360" s="4" t="inlineStr">
@@ -28921,7 +28936,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G361" s="4" t="n">
+      <c r="G361" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H361" s="4" t="inlineStr">
@@ -28954,7 +28969,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N361" s="4" t="n">
+      <c r="N361" s="8" t="n">
         <v>66327441860.4651</v>
       </c>
       <c r="O361" s="4" t="inlineStr">
@@ -29000,7 +29015,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G362" s="4" t="n">
+      <c r="G362" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H362" s="4" t="inlineStr">
@@ -29033,7 +29048,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N362" s="4" t="n">
+      <c r="N362" s="8" t="n">
         <v>67736744186.0465</v>
       </c>
       <c r="O362" s="4" t="inlineStr">
@@ -29079,7 +29094,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G363" s="4" t="n">
+      <c r="G363" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H363" s="4" t="inlineStr">
@@ -29112,7 +29127,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N363" s="4" t="n">
+      <c r="N363" s="8" t="n">
         <v>67556279069.7674</v>
       </c>
       <c r="O363" s="4" t="inlineStr">
@@ -29158,7 +29173,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G364" s="4" t="n">
+      <c r="G364" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H364" s="4" t="inlineStr">
@@ -29191,7 +29206,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N364" s="4" t="n">
+      <c r="N364" s="8" t="n">
         <v>59867743467.9335</v>
       </c>
       <c r="O364" s="4" t="inlineStr">
@@ -29237,7 +29252,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G365" s="4" t="n">
+      <c r="G365" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H365" s="4" t="inlineStr">
@@ -29270,7 +29285,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N365" s="4" t="n">
+      <c r="N365" s="8" t="n">
         <v>61965466666.6667</v>
       </c>
       <c r="O365" s="4" t="inlineStr">
@@ -29316,7 +29331,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G366" s="4" t="n">
+      <c r="G366" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H366" s="4" t="inlineStr">
@@ -29349,7 +29364,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N366" s="4" t="n">
+      <c r="N366" s="8" t="n">
         <v>60516123711.3402</v>
       </c>
       <c r="O366" s="4" t="inlineStr">
@@ -29395,7 +29410,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G367" s="4" t="n">
+      <c r="G367" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H367" s="4" t="inlineStr">
@@ -29428,7 +29443,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N367" s="4" t="n">
+      <c r="N367" s="8" t="n">
         <v>48029034482.7586</v>
       </c>
       <c r="O367" s="4" t="inlineStr">
@@ -29474,7 +29489,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G368" s="4" t="n">
+      <c r="G368" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H368" s="4" t="inlineStr">
@@ -29507,7 +29522,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N368" s="4" t="n">
+      <c r="N368" s="8" t="n">
         <v>60226413793.1035</v>
       </c>
       <c r="O368" s="4" t="inlineStr">
@@ -29553,7 +29568,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G369" s="4" t="n">
+      <c r="G369" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H369" s="4" t="inlineStr">
@@ -29586,7 +29601,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N369" s="4" t="n">
+      <c r="N369" s="8" t="n">
         <v>43536709104.0115</v>
       </c>
       <c r="O369" s="4" t="inlineStr">
@@ -29632,7 +29647,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G370" s="4" t="n">
+      <c r="G370" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H370" s="4" t="inlineStr">
@@ -29665,7 +29680,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N370" s="4" t="n">
+      <c r="N370" s="8" t="n">
         <v>48606952194.7752</v>
       </c>
       <c r="O370" s="4" t="inlineStr">
@@ -29711,7 +29726,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G371" s="4" t="n">
+      <c r="G371" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H371" s="4" t="inlineStr">
@@ -29744,7 +29759,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N371" s="4" t="n">
+      <c r="N371" s="8" t="n">
         <v>53453444786.6256</v>
       </c>
       <c r="O371" s="4" t="inlineStr">
@@ -29790,7 +29805,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G372" s="4" t="n">
+      <c r="G372" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H372" s="4" t="inlineStr">
@@ -29823,7 +29838,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N372" s="4" t="n">
+      <c r="N372" s="8" t="n">
         <v>60416519620.0849</v>
       </c>
       <c r="O372" s="4" t="inlineStr">
@@ -29869,7 +29884,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G373" s="4" t="n">
+      <c r="G373" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H373" s="4" t="inlineStr">
@@ -29902,7 +29917,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N373" s="4" t="n">
+      <c r="N373" s="8" t="n">
         <v>60037460783.1941</v>
       </c>
       <c r="O373" s="4" t="inlineStr">
@@ -29948,7 +29963,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G374" s="4" t="n">
+      <c r="G374" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H374" s="4" t="inlineStr">
@@ -29981,7 +29996,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N374" s="4" t="n">
+      <c r="N374" s="8" t="n">
         <v>58418666666.6667</v>
       </c>
       <c r="O374" s="4" t="inlineStr">
@@ -30027,7 +30042,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G375" s="4" t="n">
+      <c r="G375" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H375" s="4" t="inlineStr">
@@ -30060,7 +30075,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N375" s="4" t="n">
+      <c r="N375" s="8" t="n">
         <v>77389487770.0883</v>
       </c>
       <c r="O375" s="4" t="inlineStr">
@@ -30106,7 +30121,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G376" s="4" t="n">
+      <c r="G376" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H376" s="4" t="inlineStr">
@@ -30139,7 +30154,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N376" s="4" t="n">
+      <c r="N376" s="8" t="n">
         <v>70543211119.099</v>
       </c>
       <c r="O376" s="4" t="inlineStr">
@@ -30185,7 +30200,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G377" s="4" t="n">
+      <c r="G377" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H377" s="4" t="inlineStr">
@@ -30218,7 +30233,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N377" s="4" t="n">
+      <c r="N377" s="8" t="n">
         <v>85837678559.8324</v>
       </c>
       <c r="O377" s="4" t="inlineStr">
@@ -30264,7 +30279,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G378" s="4" t="n">
+      <c r="G378" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H378" s="4" t="inlineStr">
@@ -30297,7 +30312,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N378" s="4" t="n">
+      <c r="N378" s="8" t="n">
         <v>91336763255.05969</v>
       </c>
       <c r="O378" s="4" t="inlineStr">
@@ -30343,7 +30358,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G379" s="4" t="n">
+      <c r="G379" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H379" s="4" t="inlineStr">
@@ -30376,7 +30391,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N379" s="4" t="n">
+      <c r="N379" s="8" t="n">
         <v>97972842461.51311</v>
       </c>
       <c r="O379" s="4" t="inlineStr">
@@ -30422,7 +30437,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G380" s="4" t="n">
+      <c r="G380" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H380" s="4" t="inlineStr">
@@ -30455,7 +30470,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N380" s="4" t="n">
+      <c r="N380" s="8" t="n">
         <v>117146466002.661</v>
       </c>
       <c r="O380" s="4" t="inlineStr">
@@ -30501,7 +30516,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G381" s="4" t="n">
+      <c r="G381" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H381" s="4" t="inlineStr">
@@ -30534,7 +30549,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N381" s="4" t="n">
+      <c r="N381" s="8" t="n">
         <v>122911036746.729</v>
       </c>
       <c r="O381" s="4" t="inlineStr">
@@ -30580,7 +30595,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G382" s="4" t="n">
+      <c r="G382" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H382" s="4" t="inlineStr">
@@ -30613,7 +30628,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N382" s="4" t="n">
+      <c r="N382" s="8" t="n">
         <v>92893587733.65491</v>
       </c>
       <c r="O382" s="4" t="inlineStr">
@@ -30659,7 +30674,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G383" s="4" t="n">
+      <c r="G383" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H383" s="4" t="inlineStr">
@@ -30692,7 +30707,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N383" s="4" t="n">
+      <c r="N383" s="8" t="n">
         <v>83620628582.1082</v>
       </c>
       <c r="O383" s="4" t="inlineStr">
@@ -30738,7 +30753,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G384" s="4" t="n">
+      <c r="G384" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H384" s="4" t="inlineStr">
@@ -30771,7 +30786,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N384" s="4" t="n">
+      <c r="N384" s="8" t="n">
         <v>112451400424.964</v>
       </c>
       <c r="O384" s="4" t="inlineStr">
@@ -30817,7 +30832,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G385" s="4" t="n">
+      <c r="G385" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H385" s="4" t="inlineStr">
@@ -30850,7 +30865,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N385" s="4" t="n">
+      <c r="N385" s="8" t="n">
         <v>145513489651.872</v>
       </c>
       <c r="O385" s="4" t="inlineStr">
@@ -30896,7 +30911,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G386" s="4" t="n">
+      <c r="G386" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H386" s="4" t="inlineStr">
@@ -30929,7 +30944,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N386" s="4" t="n">
+      <c r="N386" s="8" t="n">
         <v>183477522123.894</v>
       </c>
       <c r="O386" s="4" t="inlineStr">
@@ -30975,7 +30990,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G387" s="4" t="n">
+      <c r="G387" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H387" s="4" t="inlineStr">
@@ -31008,7 +31023,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N387" s="4" t="n">
+      <c r="N387" s="8" t="n">
         <v>230364012575.687</v>
       </c>
       <c r="O387" s="4" t="inlineStr">
@@ -31054,7 +31069,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G388" s="4" t="n">
+      <c r="G388" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H388" s="4" t="inlineStr">
@@ -31087,7 +31102,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N388" s="4" t="n">
+      <c r="N388" s="8" t="n">
         <v>315953388510.678</v>
       </c>
       <c r="O388" s="4" t="inlineStr">
@@ -31133,7 +31148,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G389" s="4" t="n">
+      <c r="G389" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H389" s="4" t="inlineStr">
@@ -31166,7 +31181,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N389" s="4" t="n">
+      <c r="N389" s="8" t="n">
         <v>329787628928.472</v>
       </c>
       <c r="O389" s="4" t="inlineStr">
@@ -31212,7 +31227,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G390" s="4" t="n">
+      <c r="G390" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H390" s="4" t="inlineStr">
@@ -31245,7 +31260,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N390" s="4" t="n">
+      <c r="N390" s="8" t="n">
         <v>393192354510.653</v>
       </c>
       <c r="O390" s="4" t="inlineStr">
@@ -31291,7 +31306,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G391" s="4" t="n">
+      <c r="G391" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H391" s="4" t="inlineStr">
@@ -31324,7 +31339,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N391" s="4" t="n">
+      <c r="N391" s="8" t="n">
         <v>316482190800.364</v>
       </c>
       <c r="O391" s="4" t="inlineStr">
@@ -31370,7 +31385,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G392" s="4" t="n">
+      <c r="G392" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H392" s="4" t="inlineStr">
@@ -31403,7 +31418,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N392" s="4" t="n">
+      <c r="N392" s="8" t="n">
         <v>371846610182.327</v>
       </c>
       <c r="O392" s="4" t="inlineStr">
@@ -31449,7 +31464,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G393" s="4" t="n">
+      <c r="G393" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H393" s="4" t="inlineStr">
@@ -31482,7 +31497,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N393" s="4" t="n">
+      <c r="N393" s="8" t="n">
         <v>258512396297.714</v>
       </c>
       <c r="O393" s="4" t="inlineStr">
@@ -31528,7 +31543,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G394" s="4" t="n">
+      <c r="G394" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H394" s="4" t="inlineStr">
@@ -31561,7 +31576,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N394" s="4" t="n">
+      <c r="N394" s="8" t="n">
         <v>214838755021.964</v>
       </c>
       <c r="O394" s="4" t="inlineStr">
@@ -31607,7 +31622,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G395" s="4" t="n">
+      <c r="G395" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H395" s="4" t="inlineStr">
@@ -31640,7 +31655,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N395" s="4" t="n">
+      <c r="N395" s="8" t="n">
         <v>125249941853.534</v>
       </c>
       <c r="O395" s="4" t="inlineStr">
@@ -31686,7 +31701,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G396" s="4" t="n">
+      <c r="G396" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H396" s="4" t="inlineStr">
@@ -31719,7 +31734,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N396" s="4" t="n">
+      <c r="N396" s="8" t="n">
         <v>112948035494.959</v>
       </c>
       <c r="O396" s="4" t="inlineStr">
@@ -31765,7 +31780,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G397" s="4" t="n">
+      <c r="G397" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H397" s="4" t="inlineStr">
@@ -31798,7 +31813,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N397" s="4" t="n">
+      <c r="N397" s="8" t="n">
         <v>115892475742.789</v>
       </c>
       <c r="O397" s="4" t="inlineStr">
@@ -31844,7 +31859,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G398" s="4" t="n">
+      <c r="G398" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H398" s="4" t="inlineStr">
@@ -31877,7 +31892,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N398" s="4" t="n">
+      <c r="N398" s="8" t="n">
         <v>101987075928.918</v>
       </c>
       <c r="O398" s="4" t="inlineStr">
@@ -31923,7 +31938,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G399" s="4" t="n">
+      <c r="G399" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H399" s="4" t="inlineStr">
@@ -31956,7 +31971,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N399" s="4" t="n">
+      <c r="N399" s="8" t="n">
         <v>73014157107.59399</v>
       </c>
       <c r="O399" s="4" t="inlineStr">
@@ -32002,7 +32017,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G400" s="4" t="n">
+      <c r="G400" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H400" s="4" t="inlineStr">
@@ -32035,7 +32050,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N400" s="4" t="n">
+      <c r="N400" s="8" t="n">
         <v>42837965906.8675</v>
       </c>
       <c r="O400" s="4" t="inlineStr">
@@ -32081,7 +32096,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G401" s="4" t="n">
+      <c r="G401" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H401" s="4" t="inlineStr">
@@ -32114,7 +32129,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N401" s="4" t="n">
+      <c r="N401" s="8" t="n">
         <v>56615026262.6535</v>
       </c>
       <c r="O401" s="4" t="inlineStr">
@@ -32160,7 +32175,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G402" s="4" t="n">
+      <c r="G402" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H402" s="4" t="inlineStr">
@@ -32193,7 +32208,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N402" s="4" t="n">
+      <c r="N402" s="8" t="n">
         <v>89013251020.98309</v>
       </c>
       <c r="O402" s="4" t="inlineStr">
@@ -32239,7 +32254,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G403" s="4" t="n">
+      <c r="G403" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H403" s="4" t="inlineStr">
@@ -32272,7 +32287,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N403" s="4" t="n">
+      <c r="N403" s="8" t="n">
         <v>102377501185.925</v>
       </c>
       <c r="O403" s="4" t="inlineStr">
@@ -32318,7 +32333,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G404" s="4" t="n">
+      <c r="G404" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H404" s="4" t="inlineStr">
@@ -32351,7 +32366,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N404" s="4" t="n">
+      <c r="N404" s="8" t="n">
         <v>120566112397.063</v>
       </c>
       <c r="O404" s="4" t="inlineStr">
@@ -32397,7 +32412,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G405" s="4" t="n">
+      <c r="G405" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H405" s="4" t="inlineStr">
@@ -32430,7 +32445,7 @@
           <t>PIB en dólares corrientes</t>
         </is>
       </c>
-      <c r="N405" s="4" t="n">
+      <c r="N405" s="8" t="n">
         <v>99661244155.6306</v>
       </c>
       <c r="O405" s="4" t="inlineStr">
@@ -32476,7 +32491,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G406" s="4" t="n">
+      <c r="G406" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H406" s="4" t="inlineStr">
@@ -32557,7 +32572,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G407" s="4" t="n">
+      <c r="G407" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H407" s="4" t="inlineStr">
@@ -32638,7 +32653,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G408" s="4" t="n">
+      <c r="G408" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H408" s="4" t="inlineStr">
@@ -32719,7 +32734,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G409" s="4" t="n">
+      <c r="G409" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H409" s="4" t="inlineStr">
@@ -32800,7 +32815,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G410" s="4" t="n">
+      <c r="G410" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H410" s="4" t="inlineStr">
@@ -32881,7 +32896,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G411" s="4" t="n">
+      <c r="G411" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H411" s="4" t="inlineStr">
@@ -32962,7 +32977,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G412" s="4" t="n">
+      <c r="G412" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H412" s="4" t="inlineStr">
@@ -33043,7 +33058,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G413" s="4" t="n">
+      <c r="G413" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H413" s="4" t="inlineStr">
@@ -33124,7 +33139,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G414" s="4" t="n">
+      <c r="G414" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H414" s="4" t="inlineStr">
@@ -33205,7 +33220,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G415" s="4" t="n">
+      <c r="G415" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H415" s="4" t="inlineStr">
@@ -33286,7 +33301,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G416" s="4" t="n">
+      <c r="G416" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H416" s="4" t="inlineStr">
@@ -33367,7 +33382,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G417" s="4" t="n">
+      <c r="G417" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H417" s="4" t="inlineStr">
@@ -33448,7 +33463,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G418" s="4" t="n">
+      <c r="G418" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H418" s="4" t="inlineStr">
@@ -33529,7 +33544,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G419" s="4" t="n">
+      <c r="G419" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H419" s="4" t="inlineStr">
@@ -33610,7 +33625,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G420" s="4" t="n">
+      <c r="G420" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H420" s="4" t="inlineStr">
@@ -33691,7 +33706,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G421" s="4" t="n">
+      <c r="G421" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H421" s="4" t="inlineStr">
@@ -33772,7 +33787,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G422" s="4" t="n">
+      <c r="G422" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H422" s="4" t="inlineStr">
@@ -33853,7 +33868,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G423" s="4" t="n">
+      <c r="G423" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H423" s="4" t="inlineStr">
@@ -33934,7 +33949,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G424" s="4" t="n">
+      <c r="G424" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H424" s="4" t="inlineStr">
@@ -34015,7 +34030,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G425" s="4" t="n">
+      <c r="G425" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H425" s="4" t="inlineStr">
@@ -34096,7 +34111,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G426" s="4" t="n">
+      <c r="G426" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H426" s="4" t="inlineStr">
@@ -34177,7 +34192,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G427" s="4" t="n">
+      <c r="G427" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H427" s="4" t="inlineStr">
@@ -34258,7 +34273,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G428" s="4" t="n">
+      <c r="G428" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H428" s="4" t="inlineStr">
@@ -34339,7 +34354,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G429" s="4" t="n">
+      <c r="G429" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H429" s="4" t="inlineStr">
@@ -34420,7 +34435,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G430" s="4" t="n">
+      <c r="G430" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H430" s="4" t="inlineStr">
@@ -34501,7 +34516,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G431" s="4" t="n">
+      <c r="G431" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H431" s="4" t="inlineStr">
@@ -34582,7 +34597,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G432" s="4" t="n">
+      <c r="G432" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H432" s="4" t="inlineStr">
@@ -34663,7 +34678,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G433" s="4" t="n">
+      <c r="G433" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H433" s="4" t="inlineStr">
@@ -34744,7 +34759,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G434" s="4" t="n">
+      <c r="G434" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H434" s="4" t="inlineStr">
@@ -34825,7 +34840,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G435" s="4" t="n">
+      <c r="G435" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H435" s="4" t="inlineStr">
@@ -34906,7 +34921,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G436" s="4" t="n">
+      <c r="G436" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H436" s="4" t="inlineStr">
@@ -34987,7 +35002,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G437" s="4" t="n">
+      <c r="G437" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H437" s="4" t="inlineStr">
@@ -35068,7 +35083,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G438" s="4" t="n">
+      <c r="G438" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H438" s="4" t="inlineStr">
@@ -35149,7 +35164,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G439" s="4" t="n">
+      <c r="G439" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H439" s="4" t="inlineStr">
@@ -35230,7 +35245,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G440" s="4" t="n">
+      <c r="G440" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H440" s="4" t="inlineStr">
@@ -35311,7 +35326,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G441" s="4" t="n">
+      <c r="G441" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H441" s="4" t="inlineStr">
@@ -35392,7 +35407,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G442" s="4" t="n">
+      <c r="G442" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H442" s="4" t="inlineStr">
@@ -35473,7 +35488,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G443" s="4" t="n">
+      <c r="G443" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H443" s="4" t="inlineStr">
@@ -35554,7 +35569,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G444" s="4" t="n">
+      <c r="G444" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H444" s="4" t="inlineStr">
@@ -35635,7 +35650,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G445" s="4" t="n">
+      <c r="G445" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H445" s="4" t="inlineStr">
@@ -35716,7 +35731,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G446" s="4" t="n">
+      <c r="G446" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H446" s="4" t="inlineStr">
@@ -35797,7 +35812,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G447" s="4" t="n">
+      <c r="G447" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H447" s="4" t="inlineStr">
@@ -35878,7 +35893,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G448" s="4" t="n">
+      <c r="G448" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H448" s="4" t="inlineStr">
@@ -35959,7 +35974,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G449" s="4" t="n">
+      <c r="G449" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H449" s="4" t="inlineStr">
@@ -36040,7 +36055,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G450" s="4" t="n">
+      <c r="G450" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H450" s="4" t="inlineStr">
@@ -36121,7 +36136,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G451" s="4" t="n">
+      <c r="G451" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H451" s="4" t="inlineStr">
@@ -36202,7 +36217,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G452" s="4" t="n">
+      <c r="G452" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H452" s="4" t="inlineStr">
@@ -36283,7 +36298,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G453" s="4" t="n">
+      <c r="G453" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H453" s="4" t="inlineStr">
@@ -36364,7 +36379,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G454" s="4" t="n">
+      <c r="G454" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H454" s="4" t="inlineStr">
@@ -36445,7 +36460,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G455" s="4" t="n">
+      <c r="G455" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H455" s="4" t="inlineStr">
@@ -36526,7 +36541,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G456" s="4" t="n">
+      <c r="G456" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H456" s="4" t="inlineStr">
@@ -36607,7 +36622,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G457" s="4" t="n">
+      <c r="G457" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H457" s="4" t="inlineStr">
@@ -36688,7 +36703,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G458" s="4" t="n">
+      <c r="G458" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H458" s="4" t="inlineStr">
@@ -36769,7 +36784,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G459" s="4" t="n">
+      <c r="G459" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H459" s="4" t="inlineStr">
@@ -36850,7 +36865,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G460" s="4" t="n">
+      <c r="G460" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H460" s="4" t="inlineStr">
@@ -36931,7 +36946,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G461" s="4" t="n">
+      <c r="G461" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H461" s="4" t="inlineStr">
@@ -37012,7 +37027,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G462" s="4" t="n">
+      <c r="G462" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H462" s="4" t="inlineStr">
@@ -37093,7 +37108,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G463" s="4" t="n">
+      <c r="G463" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H463" s="4" t="inlineStr">
@@ -37174,7 +37189,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G464" s="4" t="n">
+      <c r="G464" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H464" s="4" t="inlineStr">
@@ -37255,7 +37270,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G465" s="4" t="n">
+      <c r="G465" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H465" s="4" t="inlineStr">
@@ -37336,7 +37351,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G466" s="4" t="n">
+      <c r="G466" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H466" s="4" t="inlineStr">
@@ -37417,7 +37432,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G467" s="4" t="n">
+      <c r="G467" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H467" s="4" t="inlineStr">
@@ -37498,7 +37513,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G468" s="4" t="n">
+      <c r="G468" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H468" s="4" t="inlineStr">
@@ -37579,7 +37594,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G469" s="4" t="n">
+      <c r="G469" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H469" s="4" t="inlineStr">
@@ -37660,7 +37675,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G470" s="4" t="n">
+      <c r="G470" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H470" s="4" t="inlineStr">
@@ -37741,7 +37756,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G471" s="4" t="n">
+      <c r="G471" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H471" s="4" t="inlineStr">
@@ -37822,7 +37837,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G472" s="4" t="n">
+      <c r="G472" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="H472" s="4" t="inlineStr">
@@ -37903,7 +37918,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G473" s="4" t="n">
+      <c r="G473" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H473" s="4" t="inlineStr">
@@ -37984,7 +37999,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G474" s="4" t="n">
+      <c r="G474" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H474" s="4" t="inlineStr">
@@ -38065,7 +38080,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G475" s="4" t="n">
+      <c r="G475" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H475" s="4" t="inlineStr">
@@ -38146,7 +38161,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G476" s="4" t="n">
+      <c r="G476" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H476" s="4" t="inlineStr">
@@ -38227,7 +38242,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G477" s="4" t="n">
+      <c r="G477" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H477" s="4" t="inlineStr">
@@ -38308,7 +38323,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G478" s="4" t="n">
+      <c r="G478" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H478" s="4" t="inlineStr">
@@ -38389,7 +38404,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G479" s="4" t="n">
+      <c r="G479" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H479" s="4" t="inlineStr">
@@ -38470,7 +38485,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G480" s="4" t="n">
+      <c r="G480" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H480" s="4" t="inlineStr">
@@ -38551,7 +38566,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G481" s="4" t="n">
+      <c r="G481" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H481" s="4" t="inlineStr">
@@ -38632,7 +38647,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G482" s="4" t="n">
+      <c r="G482" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H482" s="4" t="inlineStr">
@@ -38713,7 +38728,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G483" s="4" t="n">
+      <c r="G483" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H483" s="4" t="inlineStr">
@@ -38794,7 +38809,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G484" s="4" t="n">
+      <c r="G484" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H484" s="4" t="inlineStr">
@@ -38875,7 +38890,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G485" s="4" t="n">
+      <c r="G485" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H485" s="4" t="inlineStr">
@@ -38956,7 +38971,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G486" s="4" t="n">
+      <c r="G486" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H486" s="4" t="inlineStr">
@@ -39037,7 +39052,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G487" s="4" t="n">
+      <c r="G487" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H487" s="4" t="inlineStr">
@@ -39118,7 +39133,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G488" s="4" t="n">
+      <c r="G488" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H488" s="4" t="inlineStr">
@@ -39199,7 +39214,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G489" s="4" t="n">
+      <c r="G489" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H489" s="4" t="inlineStr">
@@ -39280,7 +39295,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G490" s="4" t="n">
+      <c r="G490" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H490" s="4" t="inlineStr">
@@ -39361,7 +39376,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G491" s="4" t="n">
+      <c r="G491" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H491" s="4" t="inlineStr">
@@ -39442,7 +39457,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G492" s="4" t="n">
+      <c r="G492" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H492" s="4" t="inlineStr">
@@ -39523,7 +39538,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G493" s="4" t="n">
+      <c r="G493" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H493" s="4" t="inlineStr">
@@ -39604,7 +39619,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G494" s="4" t="n">
+      <c r="G494" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H494" s="4" t="inlineStr">
@@ -39685,7 +39700,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G495" s="4" t="n">
+      <c r="G495" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H495" s="4" t="inlineStr">
@@ -39766,7 +39781,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G496" s="4" t="n">
+      <c r="G496" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H496" s="4" t="inlineStr">
@@ -39847,7 +39862,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G497" s="4" t="n">
+      <c r="G497" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H497" s="4" t="inlineStr">
@@ -39928,7 +39943,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G498" s="4" t="n">
+      <c r="G498" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H498" s="4" t="inlineStr">
@@ -40009,7 +40024,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G499" s="4" t="n">
+      <c r="G499" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H499" s="4" t="inlineStr">
@@ -40090,7 +40105,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G500" s="4" t="n">
+      <c r="G500" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H500" s="4" t="inlineStr">
@@ -40171,7 +40186,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G501" s="4" t="n">
+      <c r="G501" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H501" s="4" t="inlineStr">
@@ -40252,7 +40267,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G502" s="4" t="n">
+      <c r="G502" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H502" s="4" t="inlineStr">
@@ -40333,7 +40348,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G503" s="4" t="n">
+      <c r="G503" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H503" s="4" t="inlineStr">
@@ -40414,7 +40429,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G504" s="4" t="n">
+      <c r="G504" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H504" s="4" t="inlineStr">
@@ -40495,7 +40510,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G505" s="4" t="n">
+      <c r="G505" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H505" s="4" t="inlineStr">
@@ -40576,7 +40591,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G506" s="4" t="n">
+      <c r="G506" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H506" s="4" t="inlineStr">
@@ -40657,7 +40672,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G507" s="4" t="n">
+      <c r="G507" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H507" s="4" t="inlineStr">
@@ -40738,7 +40753,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G508" s="4" t="n">
+      <c r="G508" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H508" s="4" t="inlineStr">
@@ -40819,7 +40834,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G509" s="4" t="n">
+      <c r="G509" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H509" s="4" t="inlineStr">
@@ -40900,7 +40915,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G510" s="4" t="n">
+      <c r="G510" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H510" s="4" t="inlineStr">
@@ -40981,7 +40996,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G511" s="4" t="n">
+      <c r="G511" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H511" s="4" t="inlineStr">
@@ -41062,7 +41077,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G512" s="4" t="n">
+      <c r="G512" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H512" s="4" t="inlineStr">
@@ -41143,7 +41158,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G513" s="4" t="n">
+      <c r="G513" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H513" s="4" t="inlineStr">
@@ -41224,7 +41239,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G514" s="4" t="n">
+      <c r="G514" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H514" s="4" t="inlineStr">
@@ -41305,7 +41320,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G515" s="4" t="n">
+      <c r="G515" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H515" s="4" t="inlineStr">
@@ -41386,7 +41401,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G516" s="4" t="n">
+      <c r="G516" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H516" s="4" t="inlineStr">
@@ -41467,7 +41482,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G517" s="4" t="n">
+      <c r="G517" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H517" s="4" t="inlineStr">
@@ -41548,7 +41563,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G518" s="4" t="n">
+      <c r="G518" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H518" s="4" t="inlineStr">
@@ -41629,7 +41644,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G519" s="4" t="n">
+      <c r="G519" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H519" s="4" t="inlineStr">
@@ -41710,7 +41725,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G520" s="4" t="n">
+      <c r="G520" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H520" s="4" t="inlineStr">
@@ -41791,7 +41806,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G521" s="4" t="n">
+      <c r="G521" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H521" s="4" t="inlineStr">
@@ -41872,7 +41887,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G522" s="4" t="n">
+      <c r="G522" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H522" s="4" t="inlineStr">
@@ -41953,7 +41968,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G523" s="4" t="n">
+      <c r="G523" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H523" s="4" t="inlineStr">
@@ -42034,7 +42049,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G524" s="4" t="n">
+      <c r="G524" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H524" s="4" t="inlineStr">
@@ -42115,7 +42130,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G525" s="4" t="n">
+      <c r="G525" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H525" s="4" t="inlineStr">
@@ -42196,7 +42211,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G526" s="4" t="n">
+      <c r="G526" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H526" s="4" t="inlineStr">
@@ -42277,7 +42292,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G527" s="4" t="n">
+      <c r="G527" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H527" s="4" t="inlineStr">
@@ -42358,7 +42373,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G528" s="4" t="n">
+      <c r="G528" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H528" s="4" t="inlineStr">
@@ -42439,7 +42454,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G529" s="4" t="n">
+      <c r="G529" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H529" s="4" t="inlineStr">
@@ -42520,7 +42535,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G530" s="4" t="n">
+      <c r="G530" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H530" s="4" t="inlineStr">
@@ -42601,7 +42616,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G531" s="4" t="n">
+      <c r="G531" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H531" s="4" t="inlineStr">
@@ -42682,7 +42697,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G532" s="4" t="n">
+      <c r="G532" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H532" s="4" t="inlineStr">
@@ -42763,7 +42778,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G533" s="4" t="n">
+      <c r="G533" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H533" s="4" t="inlineStr">
@@ -42844,7 +42859,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G534" s="4" t="n">
+      <c r="G534" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H534" s="4" t="inlineStr">
@@ -42925,7 +42940,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G535" s="4" t="n">
+      <c r="G535" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H535" s="4" t="inlineStr">
@@ -43006,7 +43021,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G536" s="4" t="n">
+      <c r="G536" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H536" s="4" t="inlineStr">
@@ -43087,7 +43102,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G537" s="4" t="n">
+      <c r="G537" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H537" s="4" t="inlineStr">
@@ -43168,7 +43183,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G538" s="4" t="n">
+      <c r="G538" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H538" s="4" t="inlineStr">
@@ -43249,7 +43264,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G539" s="4" t="n">
+      <c r="G539" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="H539" s="4" t="inlineStr">
@@ -43330,7 +43345,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G540" s="4" t="n">
+      <c r="G540" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H540" s="4" t="inlineStr">
@@ -43411,7 +43426,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G541" s="4" t="n">
+      <c r="G541" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H541" s="4" t="inlineStr">
@@ -43492,7 +43507,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G542" s="4" t="n">
+      <c r="G542" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H542" s="4" t="inlineStr">
@@ -43573,7 +43588,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G543" s="4" t="n">
+      <c r="G543" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H543" s="4" t="inlineStr">
@@ -43654,7 +43669,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G544" s="4" t="n">
+      <c r="G544" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H544" s="4" t="inlineStr">
@@ -43735,7 +43750,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G545" s="4" t="n">
+      <c r="G545" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H545" s="4" t="inlineStr">
@@ -43816,7 +43831,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G546" s="4" t="n">
+      <c r="G546" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H546" s="4" t="inlineStr">
@@ -43897,7 +43912,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G547" s="4" t="n">
+      <c r="G547" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H547" s="4" t="inlineStr">
@@ -43978,7 +43993,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G548" s="4" t="n">
+      <c r="G548" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H548" s="4" t="inlineStr">
@@ -44059,7 +44074,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G549" s="4" t="n">
+      <c r="G549" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H549" s="4" t="inlineStr">
@@ -44140,7 +44155,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G550" s="4" t="n">
+      <c r="G550" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H550" s="4" t="inlineStr">
@@ -44221,7 +44236,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G551" s="4" t="n">
+      <c r="G551" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H551" s="4" t="inlineStr">
@@ -44302,7 +44317,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G552" s="4" t="n">
+      <c r="G552" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H552" s="4" t="inlineStr">
@@ -44383,7 +44398,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G553" s="4" t="n">
+      <c r="G553" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H553" s="4" t="inlineStr">
@@ -44464,7 +44479,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G554" s="4" t="n">
+      <c r="G554" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H554" s="4" t="inlineStr">
@@ -44545,7 +44560,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G555" s="4" t="n">
+      <c r="G555" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H555" s="4" t="inlineStr">
@@ -44626,7 +44641,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G556" s="4" t="n">
+      <c r="G556" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H556" s="4" t="inlineStr">
@@ -44707,7 +44722,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G557" s="4" t="n">
+      <c r="G557" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H557" s="4" t="inlineStr">
@@ -44788,7 +44803,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G558" s="4" t="n">
+      <c r="G558" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H558" s="4" t="inlineStr">
@@ -44869,7 +44884,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G559" s="4" t="n">
+      <c r="G559" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H559" s="4" t="inlineStr">
@@ -44950,7 +44965,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G560" s="4" t="n">
+      <c r="G560" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H560" s="4" t="inlineStr">
@@ -45031,7 +45046,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G561" s="4" t="n">
+      <c r="G561" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H561" s="4" t="inlineStr">
@@ -45112,7 +45127,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G562" s="4" t="n">
+      <c r="G562" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H562" s="4" t="inlineStr">
@@ -45193,7 +45208,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G563" s="4" t="n">
+      <c r="G563" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H563" s="4" t="inlineStr">
@@ -45274,7 +45289,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G564" s="4" t="n">
+      <c r="G564" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H564" s="4" t="inlineStr">
@@ -45355,7 +45370,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G565" s="4" t="n">
+      <c r="G565" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H565" s="4" t="inlineStr">
@@ -45436,7 +45451,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G566" s="4" t="n">
+      <c r="G566" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H566" s="4" t="inlineStr">
@@ -45517,7 +45532,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G567" s="4" t="n">
+      <c r="G567" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H567" s="4" t="inlineStr">
@@ -45598,7 +45613,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G568" s="4" t="n">
+      <c r="G568" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H568" s="4" t="inlineStr">
@@ -45679,7 +45694,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G569" s="4" t="n">
+      <c r="G569" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H569" s="4" t="inlineStr">
@@ -45760,7 +45775,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G570" s="4" t="n">
+      <c r="G570" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H570" s="4" t="inlineStr">
@@ -45841,7 +45856,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G571" s="4" t="n">
+      <c r="G571" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H571" s="4" t="inlineStr">
@@ -45922,7 +45937,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G572" s="4" t="n">
+      <c r="G572" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H572" s="4" t="inlineStr">
@@ -46003,7 +46018,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G573" s="4" t="n">
+      <c r="G573" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H573" s="4" t="inlineStr">
@@ -46084,7 +46099,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G574" s="4" t="n">
+      <c r="G574" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H574" s="4" t="inlineStr">
@@ -46165,7 +46180,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G575" s="4" t="n">
+      <c r="G575" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H575" s="4" t="inlineStr">
@@ -46246,7 +46261,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G576" s="4" t="n">
+      <c r="G576" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H576" s="4" t="inlineStr">
@@ -46327,7 +46342,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G577" s="4" t="n">
+      <c r="G577" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H577" s="4" t="inlineStr">
@@ -46408,7 +46423,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G578" s="4" t="n">
+      <c r="G578" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H578" s="4" t="inlineStr">
@@ -46489,7 +46504,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G579" s="4" t="n">
+      <c r="G579" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H579" s="4" t="inlineStr">
@@ -46570,7 +46585,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G580" s="4" t="n">
+      <c r="G580" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H580" s="4" t="inlineStr">
@@ -46651,7 +46666,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G581" s="4" t="n">
+      <c r="G581" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H581" s="4" t="inlineStr">
@@ -46732,7 +46747,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G582" s="4" t="n">
+      <c r="G582" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H582" s="4" t="inlineStr">
@@ -46813,7 +46828,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G583" s="4" t="n">
+      <c r="G583" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H583" s="4" t="inlineStr">
@@ -46894,7 +46909,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G584" s="4" t="n">
+      <c r="G584" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H584" s="4" t="inlineStr">
@@ -46975,7 +46990,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G585" s="4" t="n">
+      <c r="G585" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H585" s="4" t="inlineStr">
@@ -47056,7 +47071,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G586" s="4" t="n">
+      <c r="G586" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H586" s="4" t="inlineStr">
@@ -47137,7 +47152,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G587" s="4" t="n">
+      <c r="G587" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H587" s="4" t="inlineStr">
@@ -47218,7 +47233,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G588" s="4" t="n">
+      <c r="G588" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H588" s="4" t="inlineStr">
@@ -47299,7 +47314,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G589" s="4" t="n">
+      <c r="G589" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H589" s="4" t="inlineStr">
@@ -47380,7 +47395,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G590" s="4" t="n">
+      <c r="G590" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H590" s="4" t="inlineStr">
@@ -47461,7 +47476,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G591" s="4" t="n">
+      <c r="G591" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H591" s="4" t="inlineStr">
@@ -47542,7 +47557,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G592" s="4" t="n">
+      <c r="G592" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H592" s="4" t="inlineStr">
@@ -47623,7 +47638,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G593" s="4" t="n">
+      <c r="G593" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H593" s="4" t="inlineStr">
@@ -47704,7 +47719,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G594" s="4" t="n">
+      <c r="G594" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H594" s="4" t="inlineStr">
@@ -47785,7 +47800,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G595" s="4" t="n">
+      <c r="G595" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H595" s="4" t="inlineStr">
@@ -47866,7 +47881,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G596" s="4" t="n">
+      <c r="G596" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H596" s="4" t="inlineStr">
@@ -47947,7 +47962,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G597" s="4" t="n">
+      <c r="G597" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H597" s="4" t="inlineStr">
@@ -48028,7 +48043,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G598" s="4" t="n">
+      <c r="G598" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H598" s="4" t="inlineStr">
@@ -48109,7 +48124,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G599" s="4" t="n">
+      <c r="G599" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H599" s="4" t="inlineStr">
@@ -48190,7 +48205,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G600" s="4" t="n">
+      <c r="G600" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H600" s="4" t="inlineStr">
@@ -48271,7 +48286,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G601" s="4" t="n">
+      <c r="G601" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H601" s="4" t="inlineStr">
@@ -48352,7 +48367,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G602" s="4" t="n">
+      <c r="G602" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H602" s="4" t="inlineStr">
@@ -48433,7 +48448,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G603" s="4" t="n">
+      <c r="G603" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H603" s="4" t="inlineStr">
@@ -48514,7 +48529,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G604" s="4" t="n">
+      <c r="G604" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H604" s="4" t="inlineStr">
@@ -48595,7 +48610,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G605" s="4" t="n">
+      <c r="G605" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H605" s="4" t="inlineStr">
@@ -48676,7 +48691,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G606" s="4" t="n">
+      <c r="G606" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="H606" s="4" t="inlineStr">
@@ -48757,7 +48772,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G607" s="4" t="n">
+      <c r="G607" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H607" s="4" t="inlineStr">
@@ -48790,7 +48805,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N607" s="4" t="n">
+      <c r="N607" s="8" t="n">
         <v>7138469961.08128</v>
       </c>
       <c r="O607" s="4" t="inlineStr">
@@ -48836,7 +48851,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G608" s="4" t="n">
+      <c r="G608" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H608" s="4" t="inlineStr">
@@ -48869,7 +48884,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N608" s="4" t="n">
+      <c r="N608" s="8" t="n">
         <v>7482939451.9577</v>
       </c>
       <c r="O608" s="4" t="inlineStr">
@@ -48915,7 +48930,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G609" s="4" t="n">
+      <c r="G609" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H609" s="4" t="inlineStr">
@@ -48948,7 +48963,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N609" s="4" t="n">
+      <c r="N609" s="8" t="n">
         <v>8179351181.66364</v>
       </c>
       <c r="O609" s="4" t="inlineStr">
@@ -48994,7 +49009,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G610" s="4" t="n">
+      <c r="G610" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H610" s="4" t="inlineStr">
@@ -49027,7 +49042,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N610" s="4" t="n">
+      <c r="N610" s="8" t="n">
         <v>8996925069.85677</v>
       </c>
       <c r="O610" s="4" t="inlineStr">
@@ -49073,7 +49088,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G611" s="4" t="n">
+      <c r="G611" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H611" s="4" t="inlineStr">
@@ -49106,7 +49121,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N611" s="4" t="n">
+      <c r="N611" s="8" t="n">
         <v>7492344827.58621</v>
       </c>
       <c r="O611" s="4" t="inlineStr">
@@ -49152,7 +49167,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G612" s="4" t="n">
+      <c r="G612" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H612" s="4" t="inlineStr">
@@ -49185,7 +49200,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N612" s="4" t="n">
+      <c r="N612" s="7" t="n">
         <v>7731600000</v>
       </c>
       <c r="O612" s="4" t="inlineStr">
@@ -49231,7 +49246,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G613" s="4" t="n">
+      <c r="G613" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H613" s="4" t="inlineStr">
@@ -49264,7 +49279,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N613" s="4" t="n">
+      <c r="N613" s="7" t="n">
         <v>8115800000</v>
       </c>
       <c r="O613" s="4" t="inlineStr">
@@ -49310,7 +49325,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G614" s="4" t="n">
+      <c r="G614" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H614" s="4" t="inlineStr">
@@ -49343,7 +49358,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N614" s="4" t="n">
+      <c r="N614" s="8" t="n">
         <v>8605244444.444441</v>
       </c>
       <c r="O614" s="4" t="inlineStr">
@@ -49389,7 +49404,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G615" s="4" t="n">
+      <c r="G615" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H615" s="4" t="inlineStr">
@@ -49422,7 +49437,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N615" s="4" t="n">
+      <c r="N615" s="8" t="n">
         <v>9331333333.33333</v>
       </c>
       <c r="O615" s="4" t="inlineStr">
@@ -49468,7 +49483,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G616" s="4" t="n">
+      <c r="G616" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H616" s="4" t="inlineStr">
@@ -49501,7 +49516,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N616" s="4" t="n">
+      <c r="N616" s="8" t="n">
         <v>9676933333.33333</v>
       </c>
       <c r="O616" s="4" t="inlineStr">
@@ -49547,7 +49562,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G617" s="4" t="n">
+      <c r="G617" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H617" s="4" t="inlineStr">
@@ -49580,7 +49595,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N617" s="4" t="n">
+      <c r="N617" s="7" t="n">
         <v>11020400000</v>
       </c>
       <c r="O617" s="4" t="inlineStr">
@@ -49626,7 +49641,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G618" s="4" t="n">
+      <c r="G618" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H618" s="4" t="inlineStr">
@@ -49659,7 +49674,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N618" s="4" t="n">
+      <c r="N618" s="8" t="n">
         <v>12248590909.0909</v>
       </c>
       <c r="O618" s="4" t="inlineStr">
@@ -49705,7 +49720,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G619" s="4" t="n">
+      <c r="G619" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H619" s="4" t="inlineStr">
@@ -49738,7 +49753,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N619" s="4" t="n">
+      <c r="N619" s="8" t="n">
         <v>13508636363.6364</v>
       </c>
       <c r="O619" s="4" t="inlineStr">
@@ -49784,7 +49799,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G620" s="4" t="n">
+      <c r="G620" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H620" s="4" t="inlineStr">
@@ -49817,7 +49832,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N620" s="4" t="n">
+      <c r="N620" s="8" t="n">
         <v>16347581395.3488</v>
       </c>
       <c r="O620" s="4" t="inlineStr">
@@ -49863,7 +49878,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G621" s="4" t="n">
+      <c r="G621" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H621" s="4" t="inlineStr">
@@ -49896,7 +49911,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N621" s="4" t="n">
+      <c r="N621" s="8" t="n">
         <v>25463930232.5581</v>
       </c>
       <c r="O621" s="4" t="inlineStr">
@@ -49942,7 +49957,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G622" s="4" t="n">
+      <c r="G622" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H622" s="4" t="inlineStr">
@@ -49975,7 +49990,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N622" s="4" t="n">
+      <c r="N622" s="8" t="n">
         <v>27564651162.7907</v>
       </c>
       <c r="O622" s="4" t="inlineStr">
@@ -50021,7 +50036,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G623" s="4" t="n">
+      <c r="G623" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H623" s="4" t="inlineStr">
@@ -50054,7 +50069,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N623" s="4" t="n">
+      <c r="N623" s="8" t="n">
         <v>31627534883.7209</v>
       </c>
       <c r="O623" s="4" t="inlineStr">
@@ -50100,7 +50115,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G624" s="4" t="n">
+      <c r="G624" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H624" s="4" t="inlineStr">
@@ -50133,7 +50148,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N624" s="4" t="n">
+      <c r="N624" s="8" t="n">
         <v>36298697674.4186</v>
       </c>
       <c r="O624" s="4" t="inlineStr">
@@ -50179,7 +50194,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G625" s="4" t="n">
+      <c r="G625" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H625" s="4" t="inlineStr">
@@ -50212,7 +50227,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N625" s="4" t="n">
+      <c r="N625" s="8" t="n">
         <v>39354279069.7674</v>
       </c>
       <c r="O625" s="4" t="inlineStr">
@@ -50258,7 +50273,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G626" s="4" t="n">
+      <c r="G626" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H626" s="4" t="inlineStr">
@@ -50291,7 +50306,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N626" s="4" t="n">
+      <c r="N626" s="8" t="n">
         <v>48307930232.5581</v>
       </c>
       <c r="O626" s="4" t="inlineStr">
@@ -50337,7 +50352,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G627" s="4" t="n">
+      <c r="G627" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H627" s="4" t="inlineStr">
@@ -50370,7 +50385,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N627" s="4" t="n">
+      <c r="N627" s="8" t="n">
         <v>59445511627.907</v>
       </c>
       <c r="O627" s="4" t="inlineStr">
@@ -50416,7 +50431,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G628" s="4" t="n">
+      <c r="G628" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H628" s="4" t="inlineStr">
@@ -50449,7 +50464,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N628" s="4" t="n">
+      <c r="N628" s="8" t="n">
         <v>66901441860.4651</v>
       </c>
       <c r="O628" s="4" t="inlineStr">
@@ -50495,7 +50510,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G629" s="4" t="n">
+      <c r="G629" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H629" s="4" t="inlineStr">
@@ -50528,7 +50543,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N629" s="4" t="n">
+      <c r="N629" s="8" t="n">
         <v>66206744186.0465</v>
       </c>
       <c r="O629" s="4" t="inlineStr">
@@ -50574,7 +50589,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G630" s="4" t="n">
+      <c r="G630" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H630" s="4" t="inlineStr">
@@ -50607,7 +50622,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N630" s="4" t="n">
+      <c r="N630" s="8" t="n">
         <v>65443279069.7674</v>
       </c>
       <c r="O630" s="4" t="inlineStr">
@@ -50653,7 +50668,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G631" s="4" t="n">
+      <c r="G631" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H631" s="4" t="inlineStr">
@@ -50686,7 +50701,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N631" s="4" t="n">
+      <c r="N631" s="8" t="n">
         <v>57805742992.8741</v>
       </c>
       <c r="O631" s="4" t="inlineStr">
@@ -50732,7 +50747,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G632" s="4" t="n">
+      <c r="G632" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H632" s="4" t="inlineStr">
@@ -50765,7 +50780,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N632" s="4" t="n">
+      <c r="N632" s="8" t="n">
         <v>59732466666.6667</v>
       </c>
       <c r="O632" s="4" t="inlineStr">
@@ -50811,7 +50826,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G633" s="4" t="n">
+      <c r="G633" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H633" s="4" t="inlineStr">
@@ -50844,7 +50859,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N633" s="4" t="n">
+      <c r="N633" s="8" t="n">
         <v>58914123711.3402</v>
       </c>
       <c r="O633" s="4" t="inlineStr">
@@ -50890,7 +50905,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G634" s="4" t="n">
+      <c r="G634" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H634" s="4" t="inlineStr">
@@ -50923,7 +50938,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N634" s="4" t="n">
+      <c r="N634" s="8" t="n">
         <v>46410034482.7586</v>
       </c>
       <c r="O634" s="4" t="inlineStr">
@@ -50969,7 +50984,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G635" s="4" t="n">
+      <c r="G635" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H635" s="4" t="inlineStr">
@@ -51002,7 +51017,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N635" s="4" t="n">
+      <c r="N635" s="8" t="n">
         <v>58455413793.1035</v>
       </c>
       <c r="O635" s="4" t="inlineStr">
@@ -51048,7 +51063,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G636" s="4" t="n">
+      <c r="G636" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H636" s="4" t="inlineStr">
@@ -51081,7 +51096,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N636" s="4" t="n">
+      <c r="N636" s="8" t="n">
         <v>41168709007.9269</v>
       </c>
       <c r="O636" s="4" t="inlineStr">
@@ -51127,7 +51142,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G637" s="4" t="n">
+      <c r="G637" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H637" s="4" t="inlineStr">
@@ -51160,7 +51175,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N637" s="4" t="n">
+      <c r="N637" s="8" t="n">
         <v>47832952194.7752</v>
       </c>
       <c r="O637" s="4" t="inlineStr">
@@ -51206,7 +51221,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G638" s="4" t="n">
+      <c r="G638" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H638" s="4" t="inlineStr">
@@ -51239,7 +51254,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N638" s="4" t="n">
+      <c r="N638" s="8" t="n">
         <v>52855445666.52</v>
       </c>
       <c r="O638" s="4" t="inlineStr">
@@ -51285,7 +51300,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G639" s="4" t="n">
+      <c r="G639" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H639" s="4" t="inlineStr">
@@ -51318,7 +51333,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N639" s="4" t="n">
+      <c r="N639" s="8" t="n">
         <v>58670519620.0764</v>
       </c>
       <c r="O639" s="4" t="inlineStr">
@@ -51364,7 +51379,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G640" s="4" t="n">
+      <c r="G640" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H640" s="4" t="inlineStr">
@@ -51397,7 +51412,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N640" s="4" t="n">
+      <c r="N640" s="8" t="n">
         <v>58322460324.5268</v>
       </c>
       <c r="O640" s="4" t="inlineStr">
@@ -51443,7 +51458,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G641" s="4" t="n">
+      <c r="G641" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H641" s="4" t="inlineStr">
@@ -51476,7 +51491,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N641" s="4" t="n">
+      <c r="N641" s="8" t="n">
         <v>56535715151.5151</v>
       </c>
       <c r="O641" s="4" t="inlineStr">
@@ -51522,7 +51537,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G642" s="4" t="n">
+      <c r="G642" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H642" s="4" t="inlineStr">
@@ -51555,7 +51570,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N642" s="4" t="n">
+      <c r="N642" s="8" t="n">
         <v>75446487534.50929</v>
       </c>
       <c r="O642" s="4" t="inlineStr">
@@ -51601,7 +51616,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G643" s="4" t="n">
+      <c r="G643" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H643" s="4" t="inlineStr">
@@ -51634,7 +51649,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N643" s="4" t="n">
+      <c r="N643" s="8" t="n">
         <v>68818004553.0793</v>
       </c>
       <c r="O643" s="4" t="inlineStr">
@@ -51680,7 +51695,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G644" s="4" t="n">
+      <c r="G644" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H644" s="4" t="inlineStr">
@@ -51713,7 +51728,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N644" s="4" t="n">
+      <c r="N644" s="8" t="n">
         <v>83374181049.7536</v>
       </c>
       <c r="O644" s="4" t="inlineStr">
@@ -51759,7 +51774,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G645" s="4" t="n">
+      <c r="G645" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H645" s="4" t="inlineStr">
@@ -51792,7 +51807,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N645" s="4" t="n">
+      <c r="N645" s="8" t="n">
         <v>88840557618.01401</v>
       </c>
       <c r="O645" s="4" t="inlineStr">
@@ -51838,7 +51853,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G646" s="4" t="n">
+      <c r="G646" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H646" s="4" t="inlineStr">
@@ -51871,7 +51886,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N646" s="4" t="n">
+      <c r="N646" s="8" t="n">
         <v>96507809649.5934</v>
       </c>
       <c r="O646" s="4" t="inlineStr">
@@ -51917,7 +51932,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G647" s="4" t="n">
+      <c r="G647" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H647" s="4" t="inlineStr">
@@ -51950,7 +51965,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N647" s="4" t="n">
+      <c r="N647" s="8" t="n">
         <v>115753015343.322</v>
       </c>
       <c r="O647" s="4" t="inlineStr">
@@ -51996,7 +52011,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G648" s="4" t="n">
+      <c r="G648" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H648" s="4" t="inlineStr">
@@ -52029,7 +52044,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N648" s="4" t="n">
+      <c r="N648" s="8" t="n">
         <v>120881073251.055</v>
       </c>
       <c r="O648" s="4" t="inlineStr">
@@ -52075,7 +52090,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G649" s="4" t="n">
+      <c r="G649" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H649" s="4" t="inlineStr">
@@ -52108,7 +52123,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N649" s="4" t="n">
+      <c r="N649" s="8" t="n">
         <v>90144246705.1425</v>
       </c>
       <c r="O649" s="4" t="inlineStr">
@@ -52154,7 +52169,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G650" s="4" t="n">
+      <c r="G650" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H650" s="4" t="inlineStr">
@@ -52187,7 +52202,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N650" s="4" t="n">
+      <c r="N650" s="8" t="n">
         <v>81432951034.1391</v>
       </c>
       <c r="O650" s="4" t="inlineStr">
@@ -52233,7 +52248,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G651" s="4" t="n">
+      <c r="G651" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H651" s="4" t="inlineStr">
@@ -52266,7 +52281,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N651" s="4" t="n">
+      <c r="N651" s="8" t="n">
         <v>108962334862.689</v>
       </c>
       <c r="O651" s="4" t="inlineStr">
@@ -52312,7 +52327,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G652" s="4" t="n">
+      <c r="G652" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H652" s="4" t="inlineStr">
@@ -52345,7 +52360,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N652" s="4" t="n">
+      <c r="N652" s="8" t="n">
         <v>143313252302.907</v>
       </c>
       <c r="O652" s="4" t="inlineStr">
@@ -52391,7 +52406,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G653" s="4" t="n">
+      <c r="G653" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H653" s="4" t="inlineStr">
@@ -52424,7 +52439,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N653" s="4" t="n">
+      <c r="N653" s="8" t="n">
         <v>182474350721.938</v>
       </c>
       <c r="O653" s="4" t="inlineStr">
@@ -52470,7 +52485,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G654" s="4" t="n">
+      <c r="G654" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H654" s="4" t="inlineStr">
@@ -52503,7 +52518,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N654" s="4" t="n">
+      <c r="N654" s="8" t="n">
         <v>232795087564.043</v>
       </c>
       <c r="O654" s="4" t="inlineStr">
@@ -52549,7 +52564,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G655" s="4" t="n">
+      <c r="G655" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H655" s="4" t="inlineStr">
@@ -52582,7 +52597,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N655" s="4" t="n">
+      <c r="N655" s="8" t="n">
         <v>316632843886.972</v>
       </c>
       <c r="O655" s="4" t="inlineStr">
@@ -52628,7 +52643,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G656" s="4" t="n">
+      <c r="G656" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H656" s="4" t="inlineStr">
@@ -52661,7 +52676,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N656" s="4" t="n">
+      <c r="N656" s="8" t="n">
         <v>327123127389.723</v>
       </c>
       <c r="O656" s="4" t="inlineStr">
@@ -52707,7 +52722,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G657" s="4" t="n">
+      <c r="G657" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H657" s="4" t="inlineStr">
@@ -52740,7 +52755,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N657" s="4" t="n">
+      <c r="N657" s="8" t="n">
         <v>388341431499.169</v>
       </c>
       <c r="O657" s="4" t="inlineStr">
@@ -52786,7 +52801,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G658" s="4" t="n">
+      <c r="G658" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H658" s="4" t="inlineStr">
@@ -52819,7 +52834,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N658" s="4" t="n">
+      <c r="N658" s="8" t="n">
         <v>308493145268.459</v>
       </c>
       <c r="O658" s="4" t="inlineStr">
@@ -52865,7 +52880,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G659" s="4" t="n">
+      <c r="G659" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H659" s="4" t="inlineStr">
@@ -52898,7 +52913,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N659" s="4" t="n">
+      <c r="N659" s="8" t="n">
         <v>360753469316.533</v>
       </c>
       <c r="O659" s="4" t="inlineStr">
@@ -52944,7 +52959,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G660" s="4" t="n">
+      <c r="G660" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H660" s="4" t="inlineStr">
@@ -52977,7 +52992,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N660" s="4" t="n">
+      <c r="N660" s="8" t="n">
         <v>249804122288.581</v>
       </c>
       <c r="O660" s="4" t="inlineStr">
@@ -53023,7 +53038,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G661" s="4" t="n">
+      <c r="G661" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H661" s="4" t="inlineStr">
@@ -53056,7 +53071,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N661" s="4" t="n">
+      <c r="N661" s="8" t="n">
         <v>207410068590.518</v>
       </c>
       <c r="O661" s="4" t="inlineStr">
@@ -53102,7 +53117,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G662" s="4" t="n">
+      <c r="G662" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H662" s="4" t="inlineStr">
@@ -53135,7 +53150,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N662" s="4" t="n">
+      <c r="N662" s="8" t="n">
         <v>117591727941.829</v>
       </c>
       <c r="O662" s="4" t="inlineStr">
@@ -53181,7 +53196,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G663" s="4" t="n">
+      <c r="G663" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H663" s="4" t="inlineStr">
@@ -53214,7 +53229,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N663" s="4" t="n">
+      <c r="N663" s="8" t="n">
         <v>106026667973.003</v>
       </c>
       <c r="O663" s="4" t="inlineStr">
@@ -53260,7 +53275,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G664" s="4" t="n">
+      <c r="G664" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H664" s="4" t="inlineStr">
@@ -53293,7 +53308,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N664" s="4" t="n">
+      <c r="N664" s="8" t="n">
         <v>108332489846.706</v>
       </c>
       <c r="O664" s="4" t="inlineStr">
@@ -53339,7 +53354,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G665" s="4" t="n">
+      <c r="G665" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H665" s="4" t="inlineStr">
@@ -53372,7 +53387,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N665" s="4" t="n">
+      <c r="N665" s="8" t="n">
         <v>94014075928.9176</v>
       </c>
       <c r="O665" s="4" t="inlineStr">
@@ -53418,7 +53433,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G666" s="4" t="n">
+      <c r="G666" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H666" s="4" t="inlineStr">
@@ -53451,7 +53466,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N666" s="4" t="n">
+      <c r="N666" s="8" t="n">
         <v>68975387107.59399</v>
       </c>
       <c r="O666" s="4" t="inlineStr">
@@ -53497,7 +53512,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G667" s="4" t="n">
+      <c r="G667" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H667" s="4" t="inlineStr">
@@ -53530,7 +53545,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N667" s="4" t="n">
+      <c r="N667" s="8" t="n">
         <v>41683565906.8675</v>
       </c>
       <c r="O667" s="4" t="inlineStr">
@@ -53576,7 +53591,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G668" s="4" t="n">
+      <c r="G668" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H668" s="4" t="inlineStr">
@@ -53609,7 +53624,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N668" s="4" t="n">
+      <c r="N668" s="8" t="n">
         <v>55586156262.6535</v>
       </c>
       <c r="O668" s="4" t="inlineStr">
@@ -53655,7 +53670,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G669" s="4" t="n">
+      <c r="G669" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H669" s="4" t="inlineStr">
@@ -53688,7 +53703,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N669" s="4" t="n">
+      <c r="N669" s="8" t="n">
         <v>88026541020.98309</v>
       </c>
       <c r="O669" s="4" t="inlineStr">
@@ -53734,7 +53749,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G670" s="4" t="n">
+      <c r="G670" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H670" s="4" t="inlineStr">
@@ -53767,7 +53782,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N670" s="4" t="n">
+      <c r="N670" s="8" t="n">
         <v>103377501185.925</v>
       </c>
       <c r="O670" s="4" t="inlineStr">
@@ -53813,7 +53828,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G671" s="4" t="n">
+      <c r="G671" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H671" s="4" t="inlineStr">
@@ -53846,7 +53861,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N671" s="4" t="n">
+      <c r="N671" s="8" t="n">
         <v>121566112397.063</v>
       </c>
       <c r="O671" s="4" t="inlineStr">
@@ -53892,7 +53907,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G672" s="4" t="n">
+      <c r="G672" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H672" s="4" t="inlineStr">
@@ -53925,7 +53940,7 @@
           <t>Ingreso nacional bruto en dólares corrientes</t>
         </is>
       </c>
-      <c r="N672" s="4" t="n">
+      <c r="N672" s="8" t="n">
         <v>98061244155.6306</v>
       </c>
       <c r="O672" s="4" t="inlineStr">
@@ -54030,7 +54045,7 @@
           <t>Número de indicadores</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="7" t="n">
         <v>10</v>
       </c>
     </row>
@@ -54040,7 +54055,7 @@
           <t>Número de registros</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="7" t="n">
         <v>666</v>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_macroeconomia.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_macroeconomia.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5931,7 +5931,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -6010,7 +6010,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6405,7 +6405,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7669,7 +7669,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8064,7 +8064,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8459,7 +8459,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8617,7 +8617,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8775,7 +8775,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -9012,7 +9012,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9091,7 +9091,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9249,7 +9249,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9486,7 +9486,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9565,7 +9565,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9644,7 +9644,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9802,7 +9802,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9881,7 +9881,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10276,7 +10276,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10355,7 +10355,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10592,7 +10592,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10671,7 +10671,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10829,7 +10829,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10908,7 +10908,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11066,7 +11066,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11143,7 +11143,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11220,7 +11220,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11451,7 +11451,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11605,7 +11605,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11682,7 +11682,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11761,7 +11761,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11840,7 +11840,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11919,7 +11919,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11998,7 +11998,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12077,7 +12077,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12156,7 +12156,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12235,7 +12235,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12314,7 +12314,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12393,7 +12393,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12472,7 +12472,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12551,7 +12551,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12709,7 +12709,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12788,7 +12788,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12867,7 +12867,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12946,7 +12946,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -13025,7 +13025,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13104,7 +13104,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13183,7 +13183,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13262,7 +13262,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13341,7 +13341,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13420,7 +13420,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13499,7 +13499,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13578,7 +13578,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13657,7 +13657,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13736,7 +13736,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13815,7 +13815,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13973,7 +13973,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -14052,7 +14052,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14131,7 +14131,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14368,7 +14368,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14447,7 +14447,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14526,7 +14526,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14605,7 +14605,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14684,7 +14684,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14763,7 +14763,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14842,7 +14842,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14921,7 +14921,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -15000,7 +15000,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -15079,7 +15079,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15235,7 +15235,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15312,7 +15312,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15389,7 +15389,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15466,7 +15466,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15543,7 +15543,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15620,7 +15620,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15697,7 +15697,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15774,7 +15774,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15851,7 +15851,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15928,7 +15928,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -16005,7 +16005,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16159,7 +16159,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16236,7 +16236,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16313,7 +16313,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16390,7 +16390,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16467,7 +16467,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16544,7 +16544,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16621,7 +16621,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16698,7 +16698,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16775,7 +16775,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16852,7 +16852,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16931,7 +16931,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -17010,7 +17010,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -17089,7 +17089,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17168,7 +17168,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17247,7 +17247,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17326,7 +17326,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17405,7 +17405,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17484,7 +17484,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17563,7 +17563,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17642,7 +17642,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17721,7 +17721,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17800,7 +17800,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17879,7 +17879,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17958,7 +17958,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -18037,7 +18037,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18195,7 +18195,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18274,7 +18274,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18353,7 +18353,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18432,7 +18432,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18511,7 +18511,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18590,7 +18590,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18748,7 +18748,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18827,7 +18827,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18985,7 +18985,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -19064,7 +19064,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19143,7 +19143,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19222,7 +19222,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19301,7 +19301,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19380,7 +19380,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19459,7 +19459,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19538,7 +19538,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19617,7 +19617,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19696,7 +19696,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19775,7 +19775,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19854,7 +19854,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19933,7 +19933,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -20012,7 +20012,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -20091,7 +20091,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20170,7 +20170,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20249,7 +20249,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20328,7 +20328,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20405,7 +20405,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20482,7 +20482,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20559,7 +20559,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20636,7 +20636,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20713,7 +20713,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20790,7 +20790,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20867,7 +20867,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20944,7 +20944,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -21021,7 +21021,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -21098,7 +21098,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21252,7 +21252,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21406,7 +21406,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21483,7 +21483,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21560,7 +21560,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21637,7 +21637,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21714,7 +21714,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21791,7 +21791,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21868,7 +21868,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21945,7 +21945,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -22022,7 +22022,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -22101,7 +22101,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22180,7 +22180,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22259,7 +22259,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22338,7 +22338,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22417,7 +22417,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22496,7 +22496,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22575,7 +22575,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22654,7 +22654,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22733,7 +22733,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22812,7 +22812,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22891,7 +22891,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22970,7 +22970,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -23049,7 +23049,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -23128,7 +23128,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23207,7 +23207,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23286,7 +23286,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23365,7 +23365,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23444,7 +23444,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23523,7 +23523,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23602,7 +23602,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23681,7 +23681,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23760,7 +23760,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23839,7 +23839,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23918,7 +23918,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23997,7 +23997,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -24076,7 +24076,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -24155,7 +24155,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24234,7 +24234,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24313,7 +24313,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24392,7 +24392,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24471,7 +24471,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24550,7 +24550,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24629,7 +24629,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24708,7 +24708,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24866,7 +24866,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24945,7 +24945,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -25024,7 +25024,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -25103,7 +25103,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -25182,7 +25182,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25261,7 +25261,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25340,7 +25340,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25498,7 +25498,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25652,7 +25652,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25729,7 +25729,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25806,7 +25806,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25883,7 +25883,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25960,7 +25960,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -26037,7 +26037,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -26114,7 +26114,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -26191,7 +26191,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26268,7 +26268,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26345,7 +26345,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26422,7 +26422,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26576,7 +26576,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26655,7 +26655,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26734,7 +26734,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26813,7 +26813,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -26892,7 +26892,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -26971,7 +26971,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -27050,7 +27050,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -27129,7 +27129,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -27208,7 +27208,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27287,7 +27287,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27366,7 +27366,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27445,7 +27445,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27524,7 +27524,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27603,7 +27603,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27682,7 +27682,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27761,7 +27761,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27840,7 +27840,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -27919,7 +27919,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -27998,7 +27998,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -28077,7 +28077,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -28156,7 +28156,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -28235,7 +28235,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28393,7 +28393,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28472,7 +28472,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28551,7 +28551,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28630,7 +28630,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28709,7 +28709,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28788,7 +28788,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28867,7 +28867,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -28946,7 +28946,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -29025,7 +29025,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -29104,7 +29104,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -29183,7 +29183,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -29262,7 +29262,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29341,7 +29341,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29420,7 +29420,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29499,7 +29499,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29578,7 +29578,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29657,7 +29657,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29736,7 +29736,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29815,7 +29815,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -29894,7 +29894,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -29973,7 +29973,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -30052,7 +30052,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -30131,7 +30131,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -30210,7 +30210,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -30289,7 +30289,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30368,7 +30368,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30447,7 +30447,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30526,7 +30526,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30605,7 +30605,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30684,7 +30684,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30763,7 +30763,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30842,7 +30842,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -30921,7 +30921,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -31000,7 +31000,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -31079,7 +31079,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -31158,7 +31158,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -31237,7 +31237,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -31316,7 +31316,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31395,7 +31395,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31474,7 +31474,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31553,7 +31553,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31632,7 +31632,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31711,7 +31711,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31790,7 +31790,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31867,7 +31867,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -31946,7 +31946,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -32025,7 +32025,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -32104,7 +32104,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -32183,7 +32183,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32262,7 +32262,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32341,7 +32341,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32420,7 +32420,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32499,7 +32499,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32578,7 +32578,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32657,7 +32657,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32736,7 +32736,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32815,7 +32815,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -32894,7 +32894,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -32973,7 +32973,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -33052,7 +33052,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -33131,7 +33131,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -33210,7 +33210,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33289,7 +33289,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33368,7 +33368,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33447,7 +33447,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33526,7 +33526,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33605,7 +33605,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33684,7 +33684,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33763,7 +33763,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33842,7 +33842,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -33921,7 +33921,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -34000,7 +34000,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -34079,7 +34079,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -34158,7 +34158,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -34237,7 +34237,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34316,7 +34316,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34395,7 +34395,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34474,7 +34474,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34553,7 +34553,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34632,7 +34632,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34711,7 +34711,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34790,7 +34790,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34869,7 +34869,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -34948,7 +34948,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -35027,7 +35027,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -35106,7 +35106,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -35185,7 +35185,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -35264,7 +35264,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35343,7 +35343,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35422,7 +35422,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35501,7 +35501,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35580,7 +35580,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35659,7 +35659,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35738,7 +35738,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35817,7 +35817,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -35896,7 +35896,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -35975,7 +35975,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -36054,7 +36054,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -36133,7 +36133,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -36212,7 +36212,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -36291,7 +36291,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36370,7 +36370,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36449,7 +36449,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36528,7 +36528,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36607,7 +36607,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36686,7 +36686,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36765,7 +36765,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36844,7 +36844,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -36923,7 +36923,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -37002,7 +37002,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -37081,7 +37081,7 @@
       </c>
       <c r="P469" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q469" s="4" t="n"/>
@@ -37160,7 +37160,7 @@
       </c>
       <c r="P470" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q470" s="4" t="n"/>
@@ -37239,7 +37239,7 @@
       </c>
       <c r="P471" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q471" s="4" t="n"/>
@@ -37318,7 +37318,7 @@
       </c>
       <c r="P472" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q472" s="4" t="n"/>
@@ -37397,7 +37397,7 @@
       </c>
       <c r="P473" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q473" s="4" t="n"/>
@@ -37476,7 +37476,7 @@
       </c>
       <c r="P474" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q474" s="4" t="n"/>
@@ -37555,7 +37555,7 @@
       </c>
       <c r="P475" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q475" s="4" t="n"/>
@@ -37634,7 +37634,7 @@
       </c>
       <c r="P476" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q476" s="4" t="n"/>
@@ -37713,7 +37713,7 @@
       </c>
       <c r="P477" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q477" s="4" t="n"/>
@@ -37792,7 +37792,7 @@
       </c>
       <c r="P478" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q478" s="4" t="n"/>
@@ -37871,7 +37871,7 @@
       </c>
       <c r="P479" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q479" s="4" t="n"/>
@@ -37950,7 +37950,7 @@
       </c>
       <c r="P480" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q480" s="4" t="n"/>
@@ -38029,7 +38029,7 @@
       </c>
       <c r="P481" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q481" s="4" t="n"/>
@@ -38108,7 +38108,7 @@
       </c>
       <c r="P482" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q482" s="4" t="n"/>
@@ -38187,7 +38187,7 @@
       </c>
       <c r="P483" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q483" s="4" t="n"/>
@@ -38266,7 +38266,7 @@
       </c>
       <c r="P484" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q484" s="4" t="n"/>
@@ -38345,7 +38345,7 @@
       </c>
       <c r="P485" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q485" s="4" t="n"/>
@@ -38424,7 +38424,7 @@
       </c>
       <c r="P486" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q486" s="4" t="n"/>
@@ -38503,7 +38503,7 @@
       </c>
       <c r="P487" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q487" s="4" t="n"/>
@@ -38582,7 +38582,7 @@
       </c>
       <c r="P488" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q488" s="4" t="n"/>
@@ -38661,7 +38661,7 @@
       </c>
       <c r="P489" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q489" s="4" t="n"/>
@@ -38740,7 +38740,7 @@
       </c>
       <c r="P490" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q490" s="4" t="n"/>
@@ -38819,7 +38819,7 @@
       </c>
       <c r="P491" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q491" s="4" t="n"/>
@@ -38898,7 +38898,7 @@
       </c>
       <c r="P492" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q492" s="4" t="n"/>
@@ -38977,7 +38977,7 @@
       </c>
       <c r="P493" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q493" s="4" t="n"/>
@@ -39056,7 +39056,7 @@
       </c>
       <c r="P494" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q494" s="4" t="n"/>
@@ -39135,7 +39135,7 @@
       </c>
       <c r="P495" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q495" s="4" t="n"/>
@@ -39214,7 +39214,7 @@
       </c>
       <c r="P496" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q496" s="4" t="n"/>
@@ -39293,7 +39293,7 @@
       </c>
       <c r="P497" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q497" s="4" t="n"/>
@@ -39372,7 +39372,7 @@
       </c>
       <c r="P498" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q498" s="4" t="n"/>
@@ -39451,7 +39451,7 @@
       </c>
       <c r="P499" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q499" s="4" t="n"/>
@@ -39530,7 +39530,7 @@
       </c>
       <c r="P500" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q500" s="4" t="n"/>
@@ -39609,7 +39609,7 @@
       </c>
       <c r="P501" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q501" s="4" t="n"/>
@@ -39688,7 +39688,7 @@
       </c>
       <c r="P502" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q502" s="4" t="n"/>
@@ -39767,7 +39767,7 @@
       </c>
       <c r="P503" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q503" s="4" t="n"/>
@@ -39846,7 +39846,7 @@
       </c>
       <c r="P504" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q504" s="4" t="n"/>
@@ -39925,7 +39925,7 @@
       </c>
       <c r="P505" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q505" s="4" t="n"/>
@@ -40004,7 +40004,7 @@
       </c>
       <c r="P506" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q506" s="4" t="n"/>
@@ -40083,7 +40083,7 @@
       </c>
       <c r="P507" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q507" s="4" t="n"/>
@@ -40162,7 +40162,7 @@
       </c>
       <c r="P508" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q508" s="4" t="n"/>
@@ -40241,7 +40241,7 @@
       </c>
       <c r="P509" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q509" s="4" t="n"/>
@@ -40320,7 +40320,7 @@
       </c>
       <c r="P510" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q510" s="4" t="n"/>
@@ -40399,7 +40399,7 @@
       </c>
       <c r="P511" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q511" s="4" t="n"/>
@@ -40478,7 +40478,7 @@
       </c>
       <c r="P512" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q512" s="4" t="n"/>
@@ -40557,7 +40557,7 @@
       </c>
       <c r="P513" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q513" s="4" t="n"/>
@@ -40636,7 +40636,7 @@
       </c>
       <c r="P514" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q514" s="4" t="n"/>
@@ -40715,7 +40715,7 @@
       </c>
       <c r="P515" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q515" s="4" t="n"/>
@@ -40794,7 +40794,7 @@
       </c>
       <c r="P516" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q516" s="4" t="n"/>
@@ -40873,7 +40873,7 @@
       </c>
       <c r="P517" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q517" s="4" t="n"/>
@@ -40952,7 +40952,7 @@
       </c>
       <c r="P518" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q518" s="4" t="n"/>
@@ -41031,7 +41031,7 @@
       </c>
       <c r="P519" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q519" s="4" t="n"/>
@@ -41110,7 +41110,7 @@
       </c>
       <c r="P520" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q520" s="4" t="n"/>
@@ -41189,7 +41189,7 @@
       </c>
       <c r="P521" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q521" s="4" t="n"/>
@@ -41268,7 +41268,7 @@
       </c>
       <c r="P522" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q522" s="4" t="n"/>
@@ -41347,7 +41347,7 @@
       </c>
       <c r="P523" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q523" s="4" t="n"/>
@@ -41426,7 +41426,7 @@
       </c>
       <c r="P524" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q524" s="4" t="n"/>
@@ -41505,7 +41505,7 @@
       </c>
       <c r="P525" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q525" s="4" t="n"/>
@@ -41584,7 +41584,7 @@
       </c>
       <c r="P526" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q526" s="4" t="n"/>
@@ -41663,7 +41663,7 @@
       </c>
       <c r="P527" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q527" s="4" t="n"/>
@@ -41742,7 +41742,7 @@
       </c>
       <c r="P528" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q528" s="4" t="n"/>
@@ -41821,7 +41821,7 @@
       </c>
       <c r="P529" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q529" s="4" t="n"/>
@@ -41900,7 +41900,7 @@
       </c>
       <c r="P530" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q530" s="4" t="n"/>
@@ -41979,7 +41979,7 @@
       </c>
       <c r="P531" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q531" s="4" t="n"/>
@@ -42058,7 +42058,7 @@
       </c>
       <c r="P532" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q532" s="4" t="n"/>
@@ -42137,7 +42137,7 @@
       </c>
       <c r="P533" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q533" s="4" t="n"/>
@@ -42216,7 +42216,7 @@
       </c>
       <c r="P534" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q534" s="4" t="n"/>
@@ -42293,7 +42293,7 @@
       </c>
       <c r="P535" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q535" s="4" t="n"/>
@@ -42372,7 +42372,7 @@
       </c>
       <c r="P536" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q536" s="4" t="n"/>
@@ -42451,7 +42451,7 @@
       </c>
       <c r="P537" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q537" s="4" t="n"/>
@@ -42530,7 +42530,7 @@
       </c>
       <c r="P538" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q538" s="4" t="n"/>
@@ -42609,7 +42609,7 @@
       </c>
       <c r="P539" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q539" s="4" t="n"/>
@@ -42688,7 +42688,7 @@
       </c>
       <c r="P540" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q540" s="4" t="n"/>
@@ -42767,7 +42767,7 @@
       </c>
       <c r="P541" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q541" s="4" t="n"/>
@@ -42846,7 +42846,7 @@
       </c>
       <c r="P542" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q542" s="4" t="n"/>
@@ -42925,7 +42925,7 @@
       </c>
       <c r="P543" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q543" s="4" t="n"/>
@@ -43004,7 +43004,7 @@
       </c>
       <c r="P544" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q544" s="4" t="n"/>
@@ -43083,7 +43083,7 @@
       </c>
       <c r="P545" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q545" s="4" t="n"/>
@@ -43162,7 +43162,7 @@
       </c>
       <c r="P546" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q546" s="4" t="n"/>
@@ -43241,7 +43241,7 @@
       </c>
       <c r="P547" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q547" s="4" t="n"/>
@@ -43320,7 +43320,7 @@
       </c>
       <c r="P548" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q548" s="4" t="n"/>
@@ -43399,7 +43399,7 @@
       </c>
       <c r="P549" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q549" s="4" t="n"/>
@@ -43478,7 +43478,7 @@
       </c>
       <c r="P550" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q550" s="4" t="n"/>
@@ -43557,7 +43557,7 @@
       </c>
       <c r="P551" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q551" s="4" t="n"/>
@@ -43636,7 +43636,7 @@
       </c>
       <c r="P552" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q552" s="4" t="n"/>
@@ -43715,7 +43715,7 @@
       </c>
       <c r="P553" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q553" s="4" t="n"/>
@@ -43794,7 +43794,7 @@
       </c>
       <c r="P554" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q554" s="4" t="n"/>
@@ -43873,7 +43873,7 @@
       </c>
       <c r="P555" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q555" s="4" t="n"/>
@@ -43952,7 +43952,7 @@
       </c>
       <c r="P556" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q556" s="4" t="n"/>
@@ -44031,7 +44031,7 @@
       </c>
       <c r="P557" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q557" s="4" t="n"/>
@@ -44110,7 +44110,7 @@
       </c>
       <c r="P558" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q558" s="4" t="n"/>
@@ -44189,7 +44189,7 @@
       </c>
       <c r="P559" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q559" s="4" t="n"/>
@@ -44268,7 +44268,7 @@
       </c>
       <c r="P560" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q560" s="4" t="n"/>
@@ -44347,7 +44347,7 @@
       </c>
       <c r="P561" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q561" s="4" t="n"/>
@@ -44426,7 +44426,7 @@
       </c>
       <c r="P562" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q562" s="4" t="n"/>
@@ -44505,7 +44505,7 @@
       </c>
       <c r="P563" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q563" s="4" t="n"/>
@@ -44584,7 +44584,7 @@
       </c>
       <c r="P564" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q564" s="4" t="n"/>
@@ -44663,7 +44663,7 @@
       </c>
       <c r="P565" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q565" s="4" t="n"/>
@@ -44742,7 +44742,7 @@
       </c>
       <c r="P566" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q566" s="4" t="n"/>
@@ -44821,7 +44821,7 @@
       </c>
       <c r="P567" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q567" s="4" t="n"/>
@@ -44900,7 +44900,7 @@
       </c>
       <c r="P568" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q568" s="4" t="n"/>
@@ -44979,7 +44979,7 @@
       </c>
       <c r="P569" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q569" s="4" t="n"/>
@@ -45058,7 +45058,7 @@
       </c>
       <c r="P570" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q570" s="4" t="n"/>
@@ -45137,7 +45137,7 @@
       </c>
       <c r="P571" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q571" s="4" t="n"/>
@@ -45216,7 +45216,7 @@
       </c>
       <c r="P572" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q572" s="4" t="n"/>
@@ -45295,7 +45295,7 @@
       </c>
       <c r="P573" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q573" s="4" t="n"/>
@@ -45374,7 +45374,7 @@
       </c>
       <c r="P574" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q574" s="4" t="n"/>
@@ -45453,7 +45453,7 @@
       </c>
       <c r="P575" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q575" s="4" t="n"/>
@@ -45532,7 +45532,7 @@
       </c>
       <c r="P576" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q576" s="4" t="n"/>
@@ -45611,7 +45611,7 @@
       </c>
       <c r="P577" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q577" s="4" t="n"/>
@@ -45690,7 +45690,7 @@
       </c>
       <c r="P578" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q578" s="4" t="n"/>
@@ -45769,7 +45769,7 @@
       </c>
       <c r="P579" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q579" s="4" t="n"/>
@@ -45848,7 +45848,7 @@
       </c>
       <c r="P580" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q580" s="4" t="n"/>
@@ -45927,7 +45927,7 @@
       </c>
       <c r="P581" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q581" s="4" t="n"/>
@@ -46006,7 +46006,7 @@
       </c>
       <c r="P582" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q582" s="4" t="n"/>
@@ -46085,7 +46085,7 @@
       </c>
       <c r="P583" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q583" s="4" t="n"/>
@@ -46164,7 +46164,7 @@
       </c>
       <c r="P584" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q584" s="4" t="n"/>
@@ -46243,7 +46243,7 @@
       </c>
       <c r="P585" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q585" s="4" t="n"/>
@@ -46322,7 +46322,7 @@
       </c>
       <c r="P586" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q586" s="4" t="n"/>
@@ -46401,7 +46401,7 @@
       </c>
       <c r="P587" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q587" s="4" t="n"/>
@@ -46480,7 +46480,7 @@
       </c>
       <c r="P588" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q588" s="4" t="n"/>
@@ -46559,7 +46559,7 @@
       </c>
       <c r="P589" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q589" s="4" t="n"/>
@@ -46638,7 +46638,7 @@
       </c>
       <c r="P590" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q590" s="4" t="n"/>
@@ -46717,7 +46717,7 @@
       </c>
       <c r="P591" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q591" s="4" t="n"/>
@@ -46796,7 +46796,7 @@
       </c>
       <c r="P592" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q592" s="4" t="n"/>
@@ -46875,7 +46875,7 @@
       </c>
       <c r="P593" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q593" s="4" t="n"/>
@@ -46954,7 +46954,7 @@
       </c>
       <c r="P594" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q594" s="4" t="n"/>
@@ -47033,7 +47033,7 @@
       </c>
       <c r="P595" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q595" s="4" t="n"/>
@@ -47112,7 +47112,7 @@
       </c>
       <c r="P596" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q596" s="4" t="n"/>
@@ -47191,7 +47191,7 @@
       </c>
       <c r="P597" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q597" s="4" t="n"/>
@@ -47270,7 +47270,7 @@
       </c>
       <c r="P598" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q598" s="4" t="n"/>
@@ -47349,7 +47349,7 @@
       </c>
       <c r="P599" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q599" s="4" t="n"/>
@@ -47428,7 +47428,7 @@
       </c>
       <c r="P600" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q600" s="4" t="n"/>
@@ -47507,7 +47507,7 @@
       </c>
       <c r="P601" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q601" s="4" t="n"/>
@@ -47586,7 +47586,7 @@
       </c>
       <c r="P602" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q602" s="4" t="n"/>
@@ -47665,7 +47665,7 @@
       </c>
       <c r="P603" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q603" s="4" t="n"/>
@@ -47744,7 +47744,7 @@
       </c>
       <c r="P604" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q604" s="4" t="n"/>
@@ -47823,7 +47823,7 @@
       </c>
       <c r="P605" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q605" s="4" t="n"/>
@@ -47902,7 +47902,7 @@
       </c>
       <c r="P606" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q606" s="4" t="n"/>
@@ -47981,7 +47981,7 @@
       </c>
       <c r="P607" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q607" s="4" t="n"/>
@@ -48060,7 +48060,7 @@
       </c>
       <c r="P608" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q608" s="4" t="n"/>
@@ -48139,7 +48139,7 @@
       </c>
       <c r="P609" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q609" s="4" t="n"/>
@@ -48218,7 +48218,7 @@
       </c>
       <c r="P610" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q610" s="4" t="n"/>
@@ -48297,7 +48297,7 @@
       </c>
       <c r="P611" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q611" s="4" t="n"/>
@@ -48376,7 +48376,7 @@
       </c>
       <c r="P612" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q612" s="4" t="n"/>
@@ -48455,7 +48455,7 @@
       </c>
       <c r="P613" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q613" s="4" t="n"/>
@@ -48534,7 +48534,7 @@
       </c>
       <c r="P614" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q614" s="4" t="n"/>
@@ -48613,7 +48613,7 @@
       </c>
       <c r="P615" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q615" s="4" t="n"/>
@@ -48692,7 +48692,7 @@
       </c>
       <c r="P616" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q616" s="4" t="n"/>
@@ -48771,7 +48771,7 @@
       </c>
       <c r="P617" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q617" s="4" t="n"/>
@@ -48850,7 +48850,7 @@
       </c>
       <c r="P618" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q618" s="4" t="n"/>
@@ -48929,7 +48929,7 @@
       </c>
       <c r="P619" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q619" s="4" t="n"/>
@@ -49008,7 +49008,7 @@
       </c>
       <c r="P620" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q620" s="4" t="n"/>
@@ -49087,7 +49087,7 @@
       </c>
       <c r="P621" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q621" s="4" t="n"/>
@@ -49166,7 +49166,7 @@
       </c>
       <c r="P622" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q622" s="4" t="n"/>
@@ -49245,7 +49245,7 @@
       </c>
       <c r="P623" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q623" s="4" t="n"/>
@@ -49324,7 +49324,7 @@
       </c>
       <c r="P624" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q624" s="4" t="n"/>
@@ -49403,7 +49403,7 @@
       </c>
       <c r="P625" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q625" s="4" t="n"/>
@@ -49482,7 +49482,7 @@
       </c>
       <c r="P626" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q626" s="4" t="n"/>
@@ -49561,7 +49561,7 @@
       </c>
       <c r="P627" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q627" s="4" t="n"/>
@@ -49640,7 +49640,7 @@
       </c>
       <c r="P628" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q628" s="4" t="n"/>
@@ -49719,7 +49719,7 @@
       </c>
       <c r="P629" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q629" s="4" t="n"/>
@@ -49798,7 +49798,7 @@
       </c>
       <c r="P630" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q630" s="4" t="n"/>
@@ -49877,7 +49877,7 @@
       </c>
       <c r="P631" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q631" s="4" t="n"/>
@@ -49956,7 +49956,7 @@
       </c>
       <c r="P632" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q632" s="4" t="n"/>
@@ -50035,7 +50035,7 @@
       </c>
       <c r="P633" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q633" s="4" t="n"/>
@@ -50114,7 +50114,7 @@
       </c>
       <c r="P634" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q634" s="4" t="n"/>
@@ -50193,7 +50193,7 @@
       </c>
       <c r="P635" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q635" s="4" t="n"/>
@@ -50272,7 +50272,7 @@
       </c>
       <c r="P636" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q636" s="4" t="n"/>
@@ -50351,7 +50351,7 @@
       </c>
       <c r="P637" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q637" s="4" t="n"/>
@@ -50430,7 +50430,7 @@
       </c>
       <c r="P638" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q638" s="4" t="n"/>
@@ -50509,7 +50509,7 @@
       </c>
       <c r="P639" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q639" s="4" t="n"/>
@@ -50588,7 +50588,7 @@
       </c>
       <c r="P640" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q640" s="4" t="n"/>
@@ -50667,7 +50667,7 @@
       </c>
       <c r="P641" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q641" s="4" t="n"/>
@@ -50746,7 +50746,7 @@
       </c>
       <c r="P642" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q642" s="4" t="n"/>
@@ -50825,7 +50825,7 @@
       </c>
       <c r="P643" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q643" s="4" t="n"/>
@@ -50904,7 +50904,7 @@
       </c>
       <c r="P644" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q644" s="4" t="n"/>
@@ -50983,7 +50983,7 @@
       </c>
       <c r="P645" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q645" s="4" t="n"/>
@@ -51062,7 +51062,7 @@
       </c>
       <c r="P646" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q646" s="4" t="n"/>
@@ -51141,7 +51141,7 @@
       </c>
       <c r="P647" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q647" s="4" t="n"/>
@@ -51220,7 +51220,7 @@
       </c>
       <c r="P648" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q648" s="4" t="n"/>
@@ -51299,7 +51299,7 @@
       </c>
       <c r="P649" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q649" s="4" t="n"/>
@@ -51378,7 +51378,7 @@
       </c>
       <c r="P650" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q650" s="4" t="n"/>
@@ -51457,7 +51457,7 @@
       </c>
       <c r="P651" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q651" s="4" t="n"/>
@@ -51536,7 +51536,7 @@
       </c>
       <c r="P652" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q652" s="4" t="n"/>
@@ -51615,7 +51615,7 @@
       </c>
       <c r="P653" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q653" s="4" t="n"/>
@@ -51694,7 +51694,7 @@
       </c>
       <c r="P654" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q654" s="4" t="n"/>
@@ -51773,7 +51773,7 @@
       </c>
       <c r="P655" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q655" s="4" t="n"/>
@@ -51852,7 +51852,7 @@
       </c>
       <c r="P656" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q656" s="4" t="n"/>
@@ -51931,7 +51931,7 @@
       </c>
       <c r="P657" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q657" s="4" t="n"/>
@@ -52010,7 +52010,7 @@
       </c>
       <c r="P658" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q658" s="4" t="n"/>
@@ -52089,7 +52089,7 @@
       </c>
       <c r="P659" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q659" s="4" t="n"/>
@@ -52168,7 +52168,7 @@
       </c>
       <c r="P660" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q660" s="4" t="n"/>
@@ -52247,7 +52247,7 @@
       </c>
       <c r="P661" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q661" s="4" t="n"/>
@@ -52326,7 +52326,7 @@
       </c>
       <c r="P662" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q662" s="4" t="n"/>
@@ -52405,7 +52405,7 @@
       </c>
       <c r="P663" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q663" s="4" t="n"/>
@@ -52484,7 +52484,7 @@
       </c>
       <c r="P664" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q664" s="4" t="n"/>
@@ -52563,7 +52563,7 @@
       </c>
       <c r="P665" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q665" s="4" t="n"/>
@@ -52642,7 +52642,7 @@
       </c>
       <c r="P666" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q666" s="4" t="n"/>
@@ -52727,7 +52727,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_macroeconomia.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_macroeconomia.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5931,7 +5931,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -6010,7 +6010,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6405,7 +6405,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7669,7 +7669,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8064,7 +8064,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8459,7 +8459,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8617,7 +8617,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8775,7 +8775,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -9012,7 +9012,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9091,7 +9091,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9249,7 +9249,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9486,7 +9486,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9565,7 +9565,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9644,7 +9644,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9802,7 +9802,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9881,7 +9881,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10276,7 +10276,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10355,7 +10355,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10592,7 +10592,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10671,7 +10671,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10829,7 +10829,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10908,7 +10908,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11066,7 +11066,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11143,7 +11143,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11220,7 +11220,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11451,7 +11451,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11605,7 +11605,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11682,7 +11682,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11761,7 +11761,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11840,7 +11840,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11919,7 +11919,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11998,7 +11998,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12077,7 +12077,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12156,7 +12156,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12235,7 +12235,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12314,7 +12314,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12393,7 +12393,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12472,7 +12472,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12551,7 +12551,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12709,7 +12709,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12788,7 +12788,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12867,7 +12867,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12946,7 +12946,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -13025,7 +13025,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13104,7 +13104,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13183,7 +13183,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13262,7 +13262,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13341,7 +13341,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13420,7 +13420,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13499,7 +13499,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13578,7 +13578,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13657,7 +13657,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13736,7 +13736,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13815,7 +13815,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13973,7 +13973,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -14052,7 +14052,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14131,7 +14131,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14368,7 +14368,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14447,7 +14447,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14526,7 +14526,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14605,7 +14605,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14684,7 +14684,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14763,7 +14763,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14842,7 +14842,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14921,7 +14921,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -15000,7 +15000,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -15079,7 +15079,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15235,7 +15235,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15312,7 +15312,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15389,7 +15389,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15466,7 +15466,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15543,7 +15543,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15620,7 +15620,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15697,7 +15697,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15774,7 +15774,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15851,7 +15851,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15928,7 +15928,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -16005,7 +16005,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16159,7 +16159,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16236,7 +16236,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16313,7 +16313,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16390,7 +16390,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16467,7 +16467,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16544,7 +16544,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16621,7 +16621,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16698,7 +16698,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16775,7 +16775,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16852,7 +16852,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16931,7 +16931,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -17010,7 +17010,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -17089,7 +17089,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17168,7 +17168,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17247,7 +17247,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17326,7 +17326,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17405,7 +17405,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17484,7 +17484,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17563,7 +17563,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17642,7 +17642,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17721,7 +17721,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17800,7 +17800,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17879,7 +17879,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17958,7 +17958,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -18037,7 +18037,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18195,7 +18195,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18274,7 +18274,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18353,7 +18353,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18432,7 +18432,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18511,7 +18511,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18590,7 +18590,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18748,7 +18748,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18827,7 +18827,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18985,7 +18985,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -19064,7 +19064,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19143,7 +19143,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19222,7 +19222,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19301,7 +19301,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19380,7 +19380,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19459,7 +19459,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19538,7 +19538,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19617,7 +19617,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19696,7 +19696,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19775,7 +19775,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19854,7 +19854,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19933,7 +19933,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -20012,7 +20012,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -20091,7 +20091,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20170,7 +20170,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20249,7 +20249,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20328,7 +20328,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20405,7 +20405,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20482,7 +20482,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20559,7 +20559,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20636,7 +20636,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20713,7 +20713,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20790,7 +20790,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20867,7 +20867,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20944,7 +20944,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -21021,7 +21021,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -21098,7 +21098,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21252,7 +21252,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21406,7 +21406,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21483,7 +21483,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21560,7 +21560,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21637,7 +21637,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21714,7 +21714,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21791,7 +21791,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21868,7 +21868,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21945,7 +21945,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -22022,7 +22022,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -22101,7 +22101,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22180,7 +22180,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22259,7 +22259,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22338,7 +22338,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22417,7 +22417,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22496,7 +22496,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22575,7 +22575,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22654,7 +22654,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22733,7 +22733,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22812,7 +22812,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22891,7 +22891,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22970,7 +22970,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -23049,7 +23049,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -23128,7 +23128,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23207,7 +23207,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23286,7 +23286,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23365,7 +23365,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23444,7 +23444,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23523,7 +23523,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23602,7 +23602,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23681,7 +23681,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23760,7 +23760,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23839,7 +23839,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23918,7 +23918,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23997,7 +23997,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -24076,7 +24076,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -24155,7 +24155,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24234,7 +24234,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24313,7 +24313,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24392,7 +24392,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24471,7 +24471,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24550,7 +24550,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24629,7 +24629,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24708,7 +24708,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24866,7 +24866,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24945,7 +24945,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -25024,7 +25024,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -25103,7 +25103,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -25182,7 +25182,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25261,7 +25261,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25340,7 +25340,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25498,7 +25498,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25652,7 +25652,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25729,7 +25729,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25806,7 +25806,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25883,7 +25883,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25960,7 +25960,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -26037,7 +26037,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -26114,7 +26114,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -26191,7 +26191,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26268,7 +26268,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26345,7 +26345,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26422,7 +26422,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26576,7 +26576,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26655,7 +26655,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26734,7 +26734,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26813,7 +26813,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -26892,7 +26892,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -26971,7 +26971,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -27050,7 +27050,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -27129,7 +27129,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -27208,7 +27208,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27287,7 +27287,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27366,7 +27366,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27445,7 +27445,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27524,7 +27524,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27603,7 +27603,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27682,7 +27682,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27761,7 +27761,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27840,7 +27840,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -27919,7 +27919,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -27998,7 +27998,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -28077,7 +28077,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -28156,7 +28156,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -28235,7 +28235,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28393,7 +28393,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28472,7 +28472,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28551,7 +28551,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28630,7 +28630,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28709,7 +28709,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28788,7 +28788,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28867,7 +28867,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -28946,7 +28946,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -29025,7 +29025,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -29104,7 +29104,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -29183,7 +29183,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -29262,7 +29262,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29341,7 +29341,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29420,7 +29420,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29499,7 +29499,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29578,7 +29578,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29657,7 +29657,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29736,7 +29736,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29815,7 +29815,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -29894,7 +29894,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -29973,7 +29973,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -30052,7 +30052,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -30131,7 +30131,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -30210,7 +30210,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -30289,7 +30289,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30368,7 +30368,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30447,7 +30447,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30526,7 +30526,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30605,7 +30605,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30684,7 +30684,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30763,7 +30763,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30842,7 +30842,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -30921,7 +30921,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -31000,7 +31000,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -31079,7 +31079,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -31158,7 +31158,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -31237,7 +31237,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -31316,7 +31316,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31395,7 +31395,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31474,7 +31474,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31553,7 +31553,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31632,7 +31632,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31711,7 +31711,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31790,7 +31790,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31867,7 +31867,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -31946,7 +31946,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -32025,7 +32025,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -32104,7 +32104,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -32183,7 +32183,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32262,7 +32262,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32341,7 +32341,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32420,7 +32420,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32499,7 +32499,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32578,7 +32578,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32657,7 +32657,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32736,7 +32736,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32815,7 +32815,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -32894,7 +32894,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -32973,7 +32973,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -33052,7 +33052,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -33131,7 +33131,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -33210,7 +33210,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33289,7 +33289,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33368,7 +33368,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33447,7 +33447,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33526,7 +33526,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33605,7 +33605,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33684,7 +33684,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33763,7 +33763,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33842,7 +33842,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -33921,7 +33921,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -34000,7 +34000,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -34079,7 +34079,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -34158,7 +34158,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -34237,7 +34237,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34316,7 +34316,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34395,7 +34395,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34474,7 +34474,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34553,7 +34553,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34632,7 +34632,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34711,7 +34711,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34790,7 +34790,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34869,7 +34869,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -34948,7 +34948,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -35027,7 +35027,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -35106,7 +35106,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -35185,7 +35185,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -35264,7 +35264,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35343,7 +35343,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35422,7 +35422,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35501,7 +35501,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35580,7 +35580,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35659,7 +35659,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35738,7 +35738,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35817,7 +35817,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -35896,7 +35896,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -35975,7 +35975,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -36054,7 +36054,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -36133,7 +36133,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -36212,7 +36212,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -36291,7 +36291,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36370,7 +36370,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36449,7 +36449,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36528,7 +36528,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36607,7 +36607,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36686,7 +36686,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36765,7 +36765,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36844,7 +36844,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -36923,7 +36923,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -37002,7 +37002,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -37081,7 +37081,7 @@
       </c>
       <c r="P469" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q469" s="4" t="n"/>
@@ -37160,7 +37160,7 @@
       </c>
       <c r="P470" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q470" s="4" t="n"/>
@@ -37239,7 +37239,7 @@
       </c>
       <c r="P471" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q471" s="4" t="n"/>
@@ -37318,7 +37318,7 @@
       </c>
       <c r="P472" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q472" s="4" t="n"/>
@@ -37397,7 +37397,7 @@
       </c>
       <c r="P473" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q473" s="4" t="n"/>
@@ -37476,7 +37476,7 @@
       </c>
       <c r="P474" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q474" s="4" t="n"/>
@@ -37555,7 +37555,7 @@
       </c>
       <c r="P475" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q475" s="4" t="n"/>
@@ -37634,7 +37634,7 @@
       </c>
       <c r="P476" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q476" s="4" t="n"/>
@@ -37713,7 +37713,7 @@
       </c>
       <c r="P477" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q477" s="4" t="n"/>
@@ -37792,7 +37792,7 @@
       </c>
       <c r="P478" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q478" s="4" t="n"/>
@@ -37871,7 +37871,7 @@
       </c>
       <c r="P479" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q479" s="4" t="n"/>
@@ -37950,7 +37950,7 @@
       </c>
       <c r="P480" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q480" s="4" t="n"/>
@@ -38029,7 +38029,7 @@
       </c>
       <c r="P481" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q481" s="4" t="n"/>
@@ -38108,7 +38108,7 @@
       </c>
       <c r="P482" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q482" s="4" t="n"/>
@@ -38187,7 +38187,7 @@
       </c>
       <c r="P483" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q483" s="4" t="n"/>
@@ -38266,7 +38266,7 @@
       </c>
       <c r="P484" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q484" s="4" t="n"/>
@@ -38345,7 +38345,7 @@
       </c>
       <c r="P485" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q485" s="4" t="n"/>
@@ -38424,7 +38424,7 @@
       </c>
       <c r="P486" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q486" s="4" t="n"/>
@@ -38503,7 +38503,7 @@
       </c>
       <c r="P487" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q487" s="4" t="n"/>
@@ -38582,7 +38582,7 @@
       </c>
       <c r="P488" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q488" s="4" t="n"/>
@@ -38661,7 +38661,7 @@
       </c>
       <c r="P489" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q489" s="4" t="n"/>
@@ -38740,7 +38740,7 @@
       </c>
       <c r="P490" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q490" s="4" t="n"/>
@@ -38819,7 +38819,7 @@
       </c>
       <c r="P491" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q491" s="4" t="n"/>
@@ -38898,7 +38898,7 @@
       </c>
       <c r="P492" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q492" s="4" t="n"/>
@@ -38977,7 +38977,7 @@
       </c>
       <c r="P493" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q493" s="4" t="n"/>
@@ -39056,7 +39056,7 @@
       </c>
       <c r="P494" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q494" s="4" t="n"/>
@@ -39135,7 +39135,7 @@
       </c>
       <c r="P495" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q495" s="4" t="n"/>
@@ -39214,7 +39214,7 @@
       </c>
       <c r="P496" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q496" s="4" t="n"/>
@@ -39293,7 +39293,7 @@
       </c>
       <c r="P497" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q497" s="4" t="n"/>
@@ -39372,7 +39372,7 @@
       </c>
       <c r="P498" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q498" s="4" t="n"/>
@@ -39451,7 +39451,7 @@
       </c>
       <c r="P499" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q499" s="4" t="n"/>
@@ -39530,7 +39530,7 @@
       </c>
       <c r="P500" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q500" s="4" t="n"/>
@@ -39609,7 +39609,7 @@
       </c>
       <c r="P501" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q501" s="4" t="n"/>
@@ -39688,7 +39688,7 @@
       </c>
       <c r="P502" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q502" s="4" t="n"/>
@@ -39767,7 +39767,7 @@
       </c>
       <c r="P503" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q503" s="4" t="n"/>
@@ -39846,7 +39846,7 @@
       </c>
       <c r="P504" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q504" s="4" t="n"/>
@@ -39925,7 +39925,7 @@
       </c>
       <c r="P505" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q505" s="4" t="n"/>
@@ -40004,7 +40004,7 @@
       </c>
       <c r="P506" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q506" s="4" t="n"/>
@@ -40083,7 +40083,7 @@
       </c>
       <c r="P507" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q507" s="4" t="n"/>
@@ -40162,7 +40162,7 @@
       </c>
       <c r="P508" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q508" s="4" t="n"/>
@@ -40241,7 +40241,7 @@
       </c>
       <c r="P509" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q509" s="4" t="n"/>
@@ -40320,7 +40320,7 @@
       </c>
       <c r="P510" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q510" s="4" t="n"/>
@@ -40399,7 +40399,7 @@
       </c>
       <c r="P511" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q511" s="4" t="n"/>
@@ -40478,7 +40478,7 @@
       </c>
       <c r="P512" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q512" s="4" t="n"/>
@@ -40557,7 +40557,7 @@
       </c>
       <c r="P513" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q513" s="4" t="n"/>
@@ -40636,7 +40636,7 @@
       </c>
       <c r="P514" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q514" s="4" t="n"/>
@@ -40715,7 +40715,7 @@
       </c>
       <c r="P515" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q515" s="4" t="n"/>
@@ -40794,7 +40794,7 @@
       </c>
       <c r="P516" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q516" s="4" t="n"/>
@@ -40873,7 +40873,7 @@
       </c>
       <c r="P517" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q517" s="4" t="n"/>
@@ -40952,7 +40952,7 @@
       </c>
       <c r="P518" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q518" s="4" t="n"/>
@@ -41031,7 +41031,7 @@
       </c>
       <c r="P519" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q519" s="4" t="n"/>
@@ -41110,7 +41110,7 @@
       </c>
       <c r="P520" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q520" s="4" t="n"/>
@@ -41189,7 +41189,7 @@
       </c>
       <c r="P521" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q521" s="4" t="n"/>
@@ -41268,7 +41268,7 @@
       </c>
       <c r="P522" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q522" s="4" t="n"/>
@@ -41347,7 +41347,7 @@
       </c>
       <c r="P523" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q523" s="4" t="n"/>
@@ -41426,7 +41426,7 @@
       </c>
       <c r="P524" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q524" s="4" t="n"/>
@@ -41505,7 +41505,7 @@
       </c>
       <c r="P525" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q525" s="4" t="n"/>
@@ -41584,7 +41584,7 @@
       </c>
       <c r="P526" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q526" s="4" t="n"/>
@@ -41663,7 +41663,7 @@
       </c>
       <c r="P527" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q527" s="4" t="n"/>
@@ -41742,7 +41742,7 @@
       </c>
       <c r="P528" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q528" s="4" t="n"/>
@@ -41821,7 +41821,7 @@
       </c>
       <c r="P529" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q529" s="4" t="n"/>
@@ -41900,7 +41900,7 @@
       </c>
       <c r="P530" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q530" s="4" t="n"/>
@@ -41979,7 +41979,7 @@
       </c>
       <c r="P531" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q531" s="4" t="n"/>
@@ -42058,7 +42058,7 @@
       </c>
       <c r="P532" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q532" s="4" t="n"/>
@@ -42137,7 +42137,7 @@
       </c>
       <c r="P533" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q533" s="4" t="n"/>
@@ -42216,7 +42216,7 @@
       </c>
       <c r="P534" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q534" s="4" t="n"/>
@@ -42293,7 +42293,7 @@
       </c>
       <c r="P535" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q535" s="4" t="n"/>
@@ -42372,7 +42372,7 @@
       </c>
       <c r="P536" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q536" s="4" t="n"/>
@@ -42451,7 +42451,7 @@
       </c>
       <c r="P537" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q537" s="4" t="n"/>
@@ -42530,7 +42530,7 @@
       </c>
       <c r="P538" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q538" s="4" t="n"/>
@@ -42609,7 +42609,7 @@
       </c>
       <c r="P539" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q539" s="4" t="n"/>
@@ -42688,7 +42688,7 @@
       </c>
       <c r="P540" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q540" s="4" t="n"/>
@@ -42767,7 +42767,7 @@
       </c>
       <c r="P541" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q541" s="4" t="n"/>
@@ -42846,7 +42846,7 @@
       </c>
       <c r="P542" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q542" s="4" t="n"/>
@@ -42925,7 +42925,7 @@
       </c>
       <c r="P543" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q543" s="4" t="n"/>
@@ -43004,7 +43004,7 @@
       </c>
       <c r="P544" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q544" s="4" t="n"/>
@@ -43083,7 +43083,7 @@
       </c>
       <c r="P545" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q545" s="4" t="n"/>
@@ -43162,7 +43162,7 @@
       </c>
       <c r="P546" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q546" s="4" t="n"/>
@@ -43241,7 +43241,7 @@
       </c>
       <c r="P547" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q547" s="4" t="n"/>
@@ -43320,7 +43320,7 @@
       </c>
       <c r="P548" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q548" s="4" t="n"/>
@@ -43399,7 +43399,7 @@
       </c>
       <c r="P549" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q549" s="4" t="n"/>
@@ -43478,7 +43478,7 @@
       </c>
       <c r="P550" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q550" s="4" t="n"/>
@@ -43557,7 +43557,7 @@
       </c>
       <c r="P551" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q551" s="4" t="n"/>
@@ -43636,7 +43636,7 @@
       </c>
       <c r="P552" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q552" s="4" t="n"/>
@@ -43715,7 +43715,7 @@
       </c>
       <c r="P553" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q553" s="4" t="n"/>
@@ -43794,7 +43794,7 @@
       </c>
       <c r="P554" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q554" s="4" t="n"/>
@@ -43873,7 +43873,7 @@
       </c>
       <c r="P555" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q555" s="4" t="n"/>
@@ -43952,7 +43952,7 @@
       </c>
       <c r="P556" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q556" s="4" t="n"/>
@@ -44031,7 +44031,7 @@
       </c>
       <c r="P557" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q557" s="4" t="n"/>
@@ -44110,7 +44110,7 @@
       </c>
       <c r="P558" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q558" s="4" t="n"/>
@@ -44189,7 +44189,7 @@
       </c>
       <c r="P559" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q559" s="4" t="n"/>
@@ -44268,7 +44268,7 @@
       </c>
       <c r="P560" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q560" s="4" t="n"/>
@@ -44347,7 +44347,7 @@
       </c>
       <c r="P561" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q561" s="4" t="n"/>
@@ -44426,7 +44426,7 @@
       </c>
       <c r="P562" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q562" s="4" t="n"/>
@@ -44505,7 +44505,7 @@
       </c>
       <c r="P563" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q563" s="4" t="n"/>
@@ -44584,7 +44584,7 @@
       </c>
       <c r="P564" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q564" s="4" t="n"/>
@@ -44663,7 +44663,7 @@
       </c>
       <c r="P565" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q565" s="4" t="n"/>
@@ -44742,7 +44742,7 @@
       </c>
       <c r="P566" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q566" s="4" t="n"/>
@@ -44821,7 +44821,7 @@
       </c>
       <c r="P567" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q567" s="4" t="n"/>
@@ -44900,7 +44900,7 @@
       </c>
       <c r="P568" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q568" s="4" t="n"/>
@@ -44979,7 +44979,7 @@
       </c>
       <c r="P569" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q569" s="4" t="n"/>
@@ -45058,7 +45058,7 @@
       </c>
       <c r="P570" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q570" s="4" t="n"/>
@@ -45137,7 +45137,7 @@
       </c>
       <c r="P571" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q571" s="4" t="n"/>
@@ -45216,7 +45216,7 @@
       </c>
       <c r="P572" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q572" s="4" t="n"/>
@@ -45295,7 +45295,7 @@
       </c>
       <c r="P573" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q573" s="4" t="n"/>
@@ -45374,7 +45374,7 @@
       </c>
       <c r="P574" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q574" s="4" t="n"/>
@@ -45453,7 +45453,7 @@
       </c>
       <c r="P575" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q575" s="4" t="n"/>
@@ -45532,7 +45532,7 @@
       </c>
       <c r="P576" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q576" s="4" t="n"/>
@@ -45611,7 +45611,7 @@
       </c>
       <c r="P577" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q577" s="4" t="n"/>
@@ -45690,7 +45690,7 @@
       </c>
       <c r="P578" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q578" s="4" t="n"/>
@@ -45769,7 +45769,7 @@
       </c>
       <c r="P579" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q579" s="4" t="n"/>
@@ -45848,7 +45848,7 @@
       </c>
       <c r="P580" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q580" s="4" t="n"/>
@@ -45927,7 +45927,7 @@
       </c>
       <c r="P581" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q581" s="4" t="n"/>
@@ -46006,7 +46006,7 @@
       </c>
       <c r="P582" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q582" s="4" t="n"/>
@@ -46085,7 +46085,7 @@
       </c>
       <c r="P583" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q583" s="4" t="n"/>
@@ -46164,7 +46164,7 @@
       </c>
       <c r="P584" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q584" s="4" t="n"/>
@@ -46243,7 +46243,7 @@
       </c>
       <c r="P585" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q585" s="4" t="n"/>
@@ -46322,7 +46322,7 @@
       </c>
       <c r="P586" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q586" s="4" t="n"/>
@@ -46401,7 +46401,7 @@
       </c>
       <c r="P587" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q587" s="4" t="n"/>
@@ -46480,7 +46480,7 @@
       </c>
       <c r="P588" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q588" s="4" t="n"/>
@@ -46559,7 +46559,7 @@
       </c>
       <c r="P589" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q589" s="4" t="n"/>
@@ -46638,7 +46638,7 @@
       </c>
       <c r="P590" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q590" s="4" t="n"/>
@@ -46717,7 +46717,7 @@
       </c>
       <c r="P591" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q591" s="4" t="n"/>
@@ -46796,7 +46796,7 @@
       </c>
       <c r="P592" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q592" s="4" t="n"/>
@@ -46875,7 +46875,7 @@
       </c>
       <c r="P593" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q593" s="4" t="n"/>
@@ -46954,7 +46954,7 @@
       </c>
       <c r="P594" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q594" s="4" t="n"/>
@@ -47033,7 +47033,7 @@
       </c>
       <c r="P595" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q595" s="4" t="n"/>
@@ -47112,7 +47112,7 @@
       </c>
       <c r="P596" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q596" s="4" t="n"/>
@@ -47191,7 +47191,7 @@
       </c>
       <c r="P597" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q597" s="4" t="n"/>
@@ -47270,7 +47270,7 @@
       </c>
       <c r="P598" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q598" s="4" t="n"/>
@@ -47349,7 +47349,7 @@
       </c>
       <c r="P599" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q599" s="4" t="n"/>
@@ -47428,7 +47428,7 @@
       </c>
       <c r="P600" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q600" s="4" t="n"/>
@@ -47507,7 +47507,7 @@
       </c>
       <c r="P601" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q601" s="4" t="n"/>
@@ -47586,7 +47586,7 @@
       </c>
       <c r="P602" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q602" s="4" t="n"/>
@@ -47665,7 +47665,7 @@
       </c>
       <c r="P603" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q603" s="4" t="n"/>
@@ -47744,7 +47744,7 @@
       </c>
       <c r="P604" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q604" s="4" t="n"/>
@@ -47823,7 +47823,7 @@
       </c>
       <c r="P605" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q605" s="4" t="n"/>
@@ -47902,7 +47902,7 @@
       </c>
       <c r="P606" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q606" s="4" t="n"/>
@@ -47981,7 +47981,7 @@
       </c>
       <c r="P607" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q607" s="4" t="n"/>
@@ -48060,7 +48060,7 @@
       </c>
       <c r="P608" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q608" s="4" t="n"/>
@@ -48139,7 +48139,7 @@
       </c>
       <c r="P609" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q609" s="4" t="n"/>
@@ -48218,7 +48218,7 @@
       </c>
       <c r="P610" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q610" s="4" t="n"/>
@@ -48297,7 +48297,7 @@
       </c>
       <c r="P611" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q611" s="4" t="n"/>
@@ -48376,7 +48376,7 @@
       </c>
       <c r="P612" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q612" s="4" t="n"/>
@@ -48455,7 +48455,7 @@
       </c>
       <c r="P613" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q613" s="4" t="n"/>
@@ -48534,7 +48534,7 @@
       </c>
       <c r="P614" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q614" s="4" t="n"/>
@@ -48613,7 +48613,7 @@
       </c>
       <c r="P615" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q615" s="4" t="n"/>
@@ -48692,7 +48692,7 @@
       </c>
       <c r="P616" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q616" s="4" t="n"/>
@@ -48771,7 +48771,7 @@
       </c>
       <c r="P617" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q617" s="4" t="n"/>
@@ -48850,7 +48850,7 @@
       </c>
       <c r="P618" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q618" s="4" t="n"/>
@@ -48929,7 +48929,7 @@
       </c>
       <c r="P619" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q619" s="4" t="n"/>
@@ -49008,7 +49008,7 @@
       </c>
       <c r="P620" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q620" s="4" t="n"/>
@@ -49087,7 +49087,7 @@
       </c>
       <c r="P621" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q621" s="4" t="n"/>
@@ -49166,7 +49166,7 @@
       </c>
       <c r="P622" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q622" s="4" t="n"/>
@@ -49245,7 +49245,7 @@
       </c>
       <c r="P623" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q623" s="4" t="n"/>
@@ -49324,7 +49324,7 @@
       </c>
       <c r="P624" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q624" s="4" t="n"/>
@@ -49403,7 +49403,7 @@
       </c>
       <c r="P625" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q625" s="4" t="n"/>
@@ -49482,7 +49482,7 @@
       </c>
       <c r="P626" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q626" s="4" t="n"/>
@@ -49561,7 +49561,7 @@
       </c>
       <c r="P627" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q627" s="4" t="n"/>
@@ -49640,7 +49640,7 @@
       </c>
       <c r="P628" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q628" s="4" t="n"/>
@@ -49719,7 +49719,7 @@
       </c>
       <c r="P629" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q629" s="4" t="n"/>
@@ -49798,7 +49798,7 @@
       </c>
       <c r="P630" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q630" s="4" t="n"/>
@@ -49877,7 +49877,7 @@
       </c>
       <c r="P631" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q631" s="4" t="n"/>
@@ -49956,7 +49956,7 @@
       </c>
       <c r="P632" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q632" s="4" t="n"/>
@@ -50035,7 +50035,7 @@
       </c>
       <c r="P633" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q633" s="4" t="n"/>
@@ -50114,7 +50114,7 @@
       </c>
       <c r="P634" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q634" s="4" t="n"/>
@@ -50193,7 +50193,7 @@
       </c>
       <c r="P635" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q635" s="4" t="n"/>
@@ -50272,7 +50272,7 @@
       </c>
       <c r="P636" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q636" s="4" t="n"/>
@@ -50351,7 +50351,7 @@
       </c>
       <c r="P637" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q637" s="4" t="n"/>
@@ -50430,7 +50430,7 @@
       </c>
       <c r="P638" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q638" s="4" t="n"/>
@@ -50509,7 +50509,7 @@
       </c>
       <c r="P639" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q639" s="4" t="n"/>
@@ -50588,7 +50588,7 @@
       </c>
       <c r="P640" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q640" s="4" t="n"/>
@@ -50667,7 +50667,7 @@
       </c>
       <c r="P641" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q641" s="4" t="n"/>
@@ -50746,7 +50746,7 @@
       </c>
       <c r="P642" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q642" s="4" t="n"/>
@@ -50825,7 +50825,7 @@
       </c>
       <c r="P643" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q643" s="4" t="n"/>
@@ -50904,7 +50904,7 @@
       </c>
       <c r="P644" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q644" s="4" t="n"/>
@@ -50983,7 +50983,7 @@
       </c>
       <c r="P645" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q645" s="4" t="n"/>
@@ -51062,7 +51062,7 @@
       </c>
       <c r="P646" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q646" s="4" t="n"/>
@@ -51141,7 +51141,7 @@
       </c>
       <c r="P647" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q647" s="4" t="n"/>
@@ -51220,7 +51220,7 @@
       </c>
       <c r="P648" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q648" s="4" t="n"/>
@@ -51299,7 +51299,7 @@
       </c>
       <c r="P649" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q649" s="4" t="n"/>
@@ -51378,7 +51378,7 @@
       </c>
       <c r="P650" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q650" s="4" t="n"/>
@@ -51457,7 +51457,7 @@
       </c>
       <c r="P651" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q651" s="4" t="n"/>
@@ -51536,7 +51536,7 @@
       </c>
       <c r="P652" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q652" s="4" t="n"/>
@@ -51615,7 +51615,7 @@
       </c>
       <c r="P653" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q653" s="4" t="n"/>
@@ -51694,7 +51694,7 @@
       </c>
       <c r="P654" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q654" s="4" t="n"/>
@@ -51773,7 +51773,7 @@
       </c>
       <c r="P655" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q655" s="4" t="n"/>
@@ -51852,7 +51852,7 @@
       </c>
       <c r="P656" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q656" s="4" t="n"/>
@@ -51931,7 +51931,7 @@
       </c>
       <c r="P657" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q657" s="4" t="n"/>
@@ -52010,7 +52010,7 @@
       </c>
       <c r="P658" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q658" s="4" t="n"/>
@@ -52089,7 +52089,7 @@
       </c>
       <c r="P659" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q659" s="4" t="n"/>
@@ -52168,7 +52168,7 @@
       </c>
       <c r="P660" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q660" s="4" t="n"/>
@@ -52247,7 +52247,7 @@
       </c>
       <c r="P661" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q661" s="4" t="n"/>
@@ -52326,7 +52326,7 @@
       </c>
       <c r="P662" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q662" s="4" t="n"/>
@@ -52405,7 +52405,7 @@
       </c>
       <c r="P663" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q663" s="4" t="n"/>
@@ -52484,7 +52484,7 @@
       </c>
       <c r="P664" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q664" s="4" t="n"/>
@@ -52563,7 +52563,7 @@
       </c>
       <c r="P665" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q665" s="4" t="n"/>
@@ -52642,7 +52642,7 @@
       </c>
       <c r="P666" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q666" s="4" t="n"/>
@@ -52727,7 +52727,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_macroeconomia.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_macroeconomia.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5931,7 +5931,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -6010,7 +6010,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6405,7 +6405,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7669,7 +7669,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8064,7 +8064,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8459,7 +8459,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8617,7 +8617,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8775,7 +8775,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -9012,7 +9012,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9091,7 +9091,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9249,7 +9249,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9486,7 +9486,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9565,7 +9565,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9644,7 +9644,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9802,7 +9802,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9881,7 +9881,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10276,7 +10276,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10355,7 +10355,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10592,7 +10592,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10671,7 +10671,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10829,7 +10829,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10908,7 +10908,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11066,7 +11066,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11143,7 +11143,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11220,7 +11220,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11451,7 +11451,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11605,7 +11605,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11682,7 +11682,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11761,7 +11761,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11840,7 +11840,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11919,7 +11919,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11998,7 +11998,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12077,7 +12077,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12156,7 +12156,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12235,7 +12235,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12314,7 +12314,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12393,7 +12393,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12472,7 +12472,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12551,7 +12551,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12709,7 +12709,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12788,7 +12788,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12867,7 +12867,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12946,7 +12946,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -13025,7 +13025,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13104,7 +13104,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13183,7 +13183,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13262,7 +13262,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13341,7 +13341,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13420,7 +13420,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13499,7 +13499,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13578,7 +13578,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13657,7 +13657,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13736,7 +13736,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13815,7 +13815,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13973,7 +13973,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -14052,7 +14052,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14131,7 +14131,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14368,7 +14368,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14447,7 +14447,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14526,7 +14526,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14605,7 +14605,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14684,7 +14684,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14763,7 +14763,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14842,7 +14842,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14921,7 +14921,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -15000,7 +15000,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -15079,7 +15079,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15235,7 +15235,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15312,7 +15312,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15389,7 +15389,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15466,7 +15466,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15543,7 +15543,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15620,7 +15620,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15697,7 +15697,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15774,7 +15774,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15851,7 +15851,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15928,7 +15928,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -16005,7 +16005,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16159,7 +16159,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16236,7 +16236,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16313,7 +16313,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16390,7 +16390,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16467,7 +16467,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16544,7 +16544,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16621,7 +16621,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16698,7 +16698,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16775,7 +16775,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16852,7 +16852,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16931,7 +16931,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -17010,7 +17010,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -17089,7 +17089,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17168,7 +17168,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17247,7 +17247,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17326,7 +17326,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17405,7 +17405,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17484,7 +17484,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17563,7 +17563,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17642,7 +17642,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17721,7 +17721,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17800,7 +17800,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17879,7 +17879,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17958,7 +17958,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -18037,7 +18037,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18195,7 +18195,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18274,7 +18274,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18353,7 +18353,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18432,7 +18432,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18511,7 +18511,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18590,7 +18590,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18748,7 +18748,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18827,7 +18827,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18985,7 +18985,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -19064,7 +19064,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19143,7 +19143,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19222,7 +19222,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19301,7 +19301,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19380,7 +19380,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19459,7 +19459,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19538,7 +19538,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19617,7 +19617,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19696,7 +19696,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19775,7 +19775,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19854,7 +19854,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19933,7 +19933,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -20012,7 +20012,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -20091,7 +20091,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20170,7 +20170,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20249,7 +20249,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20328,7 +20328,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20405,7 +20405,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20482,7 +20482,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20559,7 +20559,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20636,7 +20636,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20713,7 +20713,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20790,7 +20790,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20867,7 +20867,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20944,7 +20944,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -21021,7 +21021,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -21098,7 +21098,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21252,7 +21252,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21406,7 +21406,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21483,7 +21483,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21560,7 +21560,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21637,7 +21637,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21714,7 +21714,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21791,7 +21791,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21868,7 +21868,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21945,7 +21945,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -22022,7 +22022,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -22101,7 +22101,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22180,7 +22180,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22259,7 +22259,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22338,7 +22338,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22417,7 +22417,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22496,7 +22496,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22575,7 +22575,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22654,7 +22654,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22733,7 +22733,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22812,7 +22812,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22891,7 +22891,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22970,7 +22970,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -23049,7 +23049,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -23128,7 +23128,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23207,7 +23207,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23286,7 +23286,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23365,7 +23365,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23444,7 +23444,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23523,7 +23523,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23602,7 +23602,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23681,7 +23681,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23760,7 +23760,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23839,7 +23839,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23918,7 +23918,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23997,7 +23997,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -24076,7 +24076,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -24155,7 +24155,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24234,7 +24234,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24313,7 +24313,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24392,7 +24392,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24471,7 +24471,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24550,7 +24550,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24629,7 +24629,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24708,7 +24708,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24866,7 +24866,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24945,7 +24945,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -25024,7 +25024,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -25103,7 +25103,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -25182,7 +25182,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25261,7 +25261,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25340,7 +25340,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25498,7 +25498,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25652,7 +25652,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25729,7 +25729,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25806,7 +25806,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25883,7 +25883,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25960,7 +25960,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -26037,7 +26037,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -26114,7 +26114,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -26191,7 +26191,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26268,7 +26268,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26345,7 +26345,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26422,7 +26422,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26576,7 +26576,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26655,7 +26655,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26734,7 +26734,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26813,7 +26813,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -26892,7 +26892,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -26971,7 +26971,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -27050,7 +27050,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -27129,7 +27129,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -27208,7 +27208,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27287,7 +27287,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27366,7 +27366,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27445,7 +27445,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27524,7 +27524,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27603,7 +27603,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27682,7 +27682,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27761,7 +27761,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27840,7 +27840,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -27919,7 +27919,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -27998,7 +27998,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -28077,7 +28077,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -28156,7 +28156,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -28235,7 +28235,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28393,7 +28393,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28472,7 +28472,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28551,7 +28551,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28630,7 +28630,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28709,7 +28709,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28788,7 +28788,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28867,7 +28867,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -28946,7 +28946,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -29025,7 +29025,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -29104,7 +29104,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -29183,7 +29183,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -29262,7 +29262,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29341,7 +29341,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29420,7 +29420,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29499,7 +29499,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29578,7 +29578,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29657,7 +29657,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29736,7 +29736,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29815,7 +29815,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -29894,7 +29894,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -29973,7 +29973,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -30052,7 +30052,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -30131,7 +30131,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -30210,7 +30210,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -30289,7 +30289,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30368,7 +30368,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30447,7 +30447,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30526,7 +30526,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30605,7 +30605,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30684,7 +30684,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30763,7 +30763,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30842,7 +30842,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -30921,7 +30921,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -31000,7 +31000,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -31079,7 +31079,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -31158,7 +31158,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -31237,7 +31237,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -31316,7 +31316,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31395,7 +31395,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31474,7 +31474,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31553,7 +31553,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31632,7 +31632,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31711,7 +31711,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31790,7 +31790,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31867,7 +31867,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -31946,7 +31946,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -32025,7 +32025,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -32104,7 +32104,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -32183,7 +32183,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32262,7 +32262,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32341,7 +32341,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32420,7 +32420,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32499,7 +32499,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32578,7 +32578,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32657,7 +32657,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32736,7 +32736,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32815,7 +32815,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -32894,7 +32894,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -32973,7 +32973,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -33052,7 +33052,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -33131,7 +33131,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -33210,7 +33210,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33289,7 +33289,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33368,7 +33368,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33447,7 +33447,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33526,7 +33526,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33605,7 +33605,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33684,7 +33684,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33763,7 +33763,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33842,7 +33842,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -33921,7 +33921,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -34000,7 +34000,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -34079,7 +34079,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -34158,7 +34158,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -34237,7 +34237,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34316,7 +34316,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34395,7 +34395,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34474,7 +34474,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34553,7 +34553,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34632,7 +34632,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34711,7 +34711,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34790,7 +34790,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34869,7 +34869,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -34948,7 +34948,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -35027,7 +35027,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -35106,7 +35106,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -35185,7 +35185,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -35264,7 +35264,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35343,7 +35343,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35422,7 +35422,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35501,7 +35501,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35580,7 +35580,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35659,7 +35659,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35738,7 +35738,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35817,7 +35817,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -35896,7 +35896,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -35975,7 +35975,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -36054,7 +36054,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -36133,7 +36133,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -36212,7 +36212,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -36291,7 +36291,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36370,7 +36370,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36449,7 +36449,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36528,7 +36528,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36607,7 +36607,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36686,7 +36686,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36765,7 +36765,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36844,7 +36844,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -36923,7 +36923,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -37002,7 +37002,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -37081,7 +37081,7 @@
       </c>
       <c r="P469" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q469" s="4" t="n"/>
@@ -37160,7 +37160,7 @@
       </c>
       <c r="P470" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q470" s="4" t="n"/>
@@ -37239,7 +37239,7 @@
       </c>
       <c r="P471" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q471" s="4" t="n"/>
@@ -37318,7 +37318,7 @@
       </c>
       <c r="P472" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q472" s="4" t="n"/>
@@ -37397,7 +37397,7 @@
       </c>
       <c r="P473" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q473" s="4" t="n"/>
@@ -37476,7 +37476,7 @@
       </c>
       <c r="P474" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q474" s="4" t="n"/>
@@ -37555,7 +37555,7 @@
       </c>
       <c r="P475" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q475" s="4" t="n"/>
@@ -37634,7 +37634,7 @@
       </c>
       <c r="P476" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q476" s="4" t="n"/>
@@ -37713,7 +37713,7 @@
       </c>
       <c r="P477" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q477" s="4" t="n"/>
@@ -37792,7 +37792,7 @@
       </c>
       <c r="P478" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q478" s="4" t="n"/>
@@ -37871,7 +37871,7 @@
       </c>
       <c r="P479" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q479" s="4" t="n"/>
@@ -37950,7 +37950,7 @@
       </c>
       <c r="P480" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q480" s="4" t="n"/>
@@ -38029,7 +38029,7 @@
       </c>
       <c r="P481" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q481" s="4" t="n"/>
@@ -38108,7 +38108,7 @@
       </c>
       <c r="P482" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q482" s="4" t="n"/>
@@ -38187,7 +38187,7 @@
       </c>
       <c r="P483" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q483" s="4" t="n"/>
@@ -38266,7 +38266,7 @@
       </c>
       <c r="P484" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q484" s="4" t="n"/>
@@ -38345,7 +38345,7 @@
       </c>
       <c r="P485" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q485" s="4" t="n"/>
@@ -38424,7 +38424,7 @@
       </c>
       <c r="P486" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q486" s="4" t="n"/>
@@ -38503,7 +38503,7 @@
       </c>
       <c r="P487" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q487" s="4" t="n"/>
@@ -38582,7 +38582,7 @@
       </c>
       <c r="P488" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q488" s="4" t="n"/>
@@ -38661,7 +38661,7 @@
       </c>
       <c r="P489" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q489" s="4" t="n"/>
@@ -38740,7 +38740,7 @@
       </c>
       <c r="P490" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q490" s="4" t="n"/>
@@ -38819,7 +38819,7 @@
       </c>
       <c r="P491" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q491" s="4" t="n"/>
@@ -38898,7 +38898,7 @@
       </c>
       <c r="P492" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q492" s="4" t="n"/>
@@ -38977,7 +38977,7 @@
       </c>
       <c r="P493" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q493" s="4" t="n"/>
@@ -39056,7 +39056,7 @@
       </c>
       <c r="P494" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q494" s="4" t="n"/>
@@ -39135,7 +39135,7 @@
       </c>
       <c r="P495" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q495" s="4" t="n"/>
@@ -39214,7 +39214,7 @@
       </c>
       <c r="P496" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q496" s="4" t="n"/>
@@ -39293,7 +39293,7 @@
       </c>
       <c r="P497" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q497" s="4" t="n"/>
@@ -39372,7 +39372,7 @@
       </c>
       <c r="P498" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q498" s="4" t="n"/>
@@ -39451,7 +39451,7 @@
       </c>
       <c r="P499" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q499" s="4" t="n"/>
@@ -39530,7 +39530,7 @@
       </c>
       <c r="P500" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q500" s="4" t="n"/>
@@ -39609,7 +39609,7 @@
       </c>
       <c r="P501" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q501" s="4" t="n"/>
@@ -39688,7 +39688,7 @@
       </c>
       <c r="P502" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q502" s="4" t="n"/>
@@ -39767,7 +39767,7 @@
       </c>
       <c r="P503" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q503" s="4" t="n"/>
@@ -39846,7 +39846,7 @@
       </c>
       <c r="P504" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q504" s="4" t="n"/>
@@ -39925,7 +39925,7 @@
       </c>
       <c r="P505" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q505" s="4" t="n"/>
@@ -40004,7 +40004,7 @@
       </c>
       <c r="P506" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q506" s="4" t="n"/>
@@ -40083,7 +40083,7 @@
       </c>
       <c r="P507" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q507" s="4" t="n"/>
@@ -40162,7 +40162,7 @@
       </c>
       <c r="P508" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q508" s="4" t="n"/>
@@ -40241,7 +40241,7 @@
       </c>
       <c r="P509" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q509" s="4" t="n"/>
@@ -40320,7 +40320,7 @@
       </c>
       <c r="P510" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q510" s="4" t="n"/>
@@ -40399,7 +40399,7 @@
       </c>
       <c r="P511" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q511" s="4" t="n"/>
@@ -40478,7 +40478,7 @@
       </c>
       <c r="P512" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q512" s="4" t="n"/>
@@ -40557,7 +40557,7 @@
       </c>
       <c r="P513" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q513" s="4" t="n"/>
@@ -40636,7 +40636,7 @@
       </c>
       <c r="P514" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q514" s="4" t="n"/>
@@ -40715,7 +40715,7 @@
       </c>
       <c r="P515" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q515" s="4" t="n"/>
@@ -40794,7 +40794,7 @@
       </c>
       <c r="P516" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q516" s="4" t="n"/>
@@ -40873,7 +40873,7 @@
       </c>
       <c r="P517" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q517" s="4" t="n"/>
@@ -40952,7 +40952,7 @@
       </c>
       <c r="P518" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q518" s="4" t="n"/>
@@ -41031,7 +41031,7 @@
       </c>
       <c r="P519" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q519" s="4" t="n"/>
@@ -41110,7 +41110,7 @@
       </c>
       <c r="P520" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q520" s="4" t="n"/>
@@ -41189,7 +41189,7 @@
       </c>
       <c r="P521" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q521" s="4" t="n"/>
@@ -41268,7 +41268,7 @@
       </c>
       <c r="P522" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q522" s="4" t="n"/>
@@ -41347,7 +41347,7 @@
       </c>
       <c r="P523" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q523" s="4" t="n"/>
@@ -41426,7 +41426,7 @@
       </c>
       <c r="P524" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q524" s="4" t="n"/>
@@ -41505,7 +41505,7 @@
       </c>
       <c r="P525" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q525" s="4" t="n"/>
@@ -41584,7 +41584,7 @@
       </c>
       <c r="P526" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q526" s="4" t="n"/>
@@ -41663,7 +41663,7 @@
       </c>
       <c r="P527" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q527" s="4" t="n"/>
@@ -41742,7 +41742,7 @@
       </c>
       <c r="P528" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q528" s="4" t="n"/>
@@ -41821,7 +41821,7 @@
       </c>
       <c r="P529" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q529" s="4" t="n"/>
@@ -41900,7 +41900,7 @@
       </c>
       <c r="P530" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q530" s="4" t="n"/>
@@ -41979,7 +41979,7 @@
       </c>
       <c r="P531" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q531" s="4" t="n"/>
@@ -42058,7 +42058,7 @@
       </c>
       <c r="P532" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q532" s="4" t="n"/>
@@ -42137,7 +42137,7 @@
       </c>
       <c r="P533" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q533" s="4" t="n"/>
@@ -42216,7 +42216,7 @@
       </c>
       <c r="P534" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q534" s="4" t="n"/>
@@ -42293,7 +42293,7 @@
       </c>
       <c r="P535" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q535" s="4" t="n"/>
@@ -42372,7 +42372,7 @@
       </c>
       <c r="P536" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q536" s="4" t="n"/>
@@ -42451,7 +42451,7 @@
       </c>
       <c r="P537" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q537" s="4" t="n"/>
@@ -42530,7 +42530,7 @@
       </c>
       <c r="P538" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q538" s="4" t="n"/>
@@ -42609,7 +42609,7 @@
       </c>
       <c r="P539" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q539" s="4" t="n"/>
@@ -42688,7 +42688,7 @@
       </c>
       <c r="P540" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q540" s="4" t="n"/>
@@ -42767,7 +42767,7 @@
       </c>
       <c r="P541" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q541" s="4" t="n"/>
@@ -42846,7 +42846,7 @@
       </c>
       <c r="P542" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q542" s="4" t="n"/>
@@ -42925,7 +42925,7 @@
       </c>
       <c r="P543" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q543" s="4" t="n"/>
@@ -43004,7 +43004,7 @@
       </c>
       <c r="P544" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q544" s="4" t="n"/>
@@ -43083,7 +43083,7 @@
       </c>
       <c r="P545" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q545" s="4" t="n"/>
@@ -43162,7 +43162,7 @@
       </c>
       <c r="P546" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q546" s="4" t="n"/>
@@ -43241,7 +43241,7 @@
       </c>
       <c r="P547" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q547" s="4" t="n"/>
@@ -43320,7 +43320,7 @@
       </c>
       <c r="P548" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q548" s="4" t="n"/>
@@ -43399,7 +43399,7 @@
       </c>
       <c r="P549" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q549" s="4" t="n"/>
@@ -43478,7 +43478,7 @@
       </c>
       <c r="P550" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q550" s="4" t="n"/>
@@ -43557,7 +43557,7 @@
       </c>
       <c r="P551" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q551" s="4" t="n"/>
@@ -43636,7 +43636,7 @@
       </c>
       <c r="P552" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q552" s="4" t="n"/>
@@ -43715,7 +43715,7 @@
       </c>
       <c r="P553" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q553" s="4" t="n"/>
@@ -43794,7 +43794,7 @@
       </c>
       <c r="P554" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q554" s="4" t="n"/>
@@ -43873,7 +43873,7 @@
       </c>
       <c r="P555" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q555" s="4" t="n"/>
@@ -43952,7 +43952,7 @@
       </c>
       <c r="P556" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q556" s="4" t="n"/>
@@ -44031,7 +44031,7 @@
       </c>
       <c r="P557" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q557" s="4" t="n"/>
@@ -44110,7 +44110,7 @@
       </c>
       <c r="P558" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q558" s="4" t="n"/>
@@ -44189,7 +44189,7 @@
       </c>
       <c r="P559" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q559" s="4" t="n"/>
@@ -44268,7 +44268,7 @@
       </c>
       <c r="P560" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q560" s="4" t="n"/>
@@ -44347,7 +44347,7 @@
       </c>
       <c r="P561" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q561" s="4" t="n"/>
@@ -44426,7 +44426,7 @@
       </c>
       <c r="P562" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q562" s="4" t="n"/>
@@ -44505,7 +44505,7 @@
       </c>
       <c r="P563" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q563" s="4" t="n"/>
@@ -44584,7 +44584,7 @@
       </c>
       <c r="P564" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q564" s="4" t="n"/>
@@ -44663,7 +44663,7 @@
       </c>
       <c r="P565" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q565" s="4" t="n"/>
@@ -44742,7 +44742,7 @@
       </c>
       <c r="P566" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q566" s="4" t="n"/>
@@ -44821,7 +44821,7 @@
       </c>
       <c r="P567" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q567" s="4" t="n"/>
@@ -44900,7 +44900,7 @@
       </c>
       <c r="P568" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q568" s="4" t="n"/>
@@ -44979,7 +44979,7 @@
       </c>
       <c r="P569" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q569" s="4" t="n"/>
@@ -45058,7 +45058,7 @@
       </c>
       <c r="P570" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q570" s="4" t="n"/>
@@ -45137,7 +45137,7 @@
       </c>
       <c r="P571" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q571" s="4" t="n"/>
@@ -45216,7 +45216,7 @@
       </c>
       <c r="P572" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q572" s="4" t="n"/>
@@ -45295,7 +45295,7 @@
       </c>
       <c r="P573" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q573" s="4" t="n"/>
@@ -45374,7 +45374,7 @@
       </c>
       <c r="P574" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q574" s="4" t="n"/>
@@ -45453,7 +45453,7 @@
       </c>
       <c r="P575" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q575" s="4" t="n"/>
@@ -45532,7 +45532,7 @@
       </c>
       <c r="P576" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q576" s="4" t="n"/>
@@ -45611,7 +45611,7 @@
       </c>
       <c r="P577" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q577" s="4" t="n"/>
@@ -45690,7 +45690,7 @@
       </c>
       <c r="P578" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q578" s="4" t="n"/>
@@ -45769,7 +45769,7 @@
       </c>
       <c r="P579" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q579" s="4" t="n"/>
@@ -45848,7 +45848,7 @@
       </c>
       <c r="P580" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q580" s="4" t="n"/>
@@ -45927,7 +45927,7 @@
       </c>
       <c r="P581" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q581" s="4" t="n"/>
@@ -46006,7 +46006,7 @@
       </c>
       <c r="P582" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q582" s="4" t="n"/>
@@ -46085,7 +46085,7 @@
       </c>
       <c r="P583" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q583" s="4" t="n"/>
@@ -46164,7 +46164,7 @@
       </c>
       <c r="P584" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q584" s="4" t="n"/>
@@ -46243,7 +46243,7 @@
       </c>
       <c r="P585" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q585" s="4" t="n"/>
@@ -46322,7 +46322,7 @@
       </c>
       <c r="P586" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q586" s="4" t="n"/>
@@ -46401,7 +46401,7 @@
       </c>
       <c r="P587" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q587" s="4" t="n"/>
@@ -46480,7 +46480,7 @@
       </c>
       <c r="P588" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q588" s="4" t="n"/>
@@ -46559,7 +46559,7 @@
       </c>
       <c r="P589" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q589" s="4" t="n"/>
@@ -46638,7 +46638,7 @@
       </c>
       <c r="P590" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q590" s="4" t="n"/>
@@ -46717,7 +46717,7 @@
       </c>
       <c r="P591" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q591" s="4" t="n"/>
@@ -46796,7 +46796,7 @@
       </c>
       <c r="P592" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q592" s="4" t="n"/>
@@ -46875,7 +46875,7 @@
       </c>
       <c r="P593" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q593" s="4" t="n"/>
@@ -46954,7 +46954,7 @@
       </c>
       <c r="P594" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q594" s="4" t="n"/>
@@ -47033,7 +47033,7 @@
       </c>
       <c r="P595" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q595" s="4" t="n"/>
@@ -47112,7 +47112,7 @@
       </c>
       <c r="P596" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q596" s="4" t="n"/>
@@ -47191,7 +47191,7 @@
       </c>
       <c r="P597" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q597" s="4" t="n"/>
@@ -47270,7 +47270,7 @@
       </c>
       <c r="P598" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q598" s="4" t="n"/>
@@ -47349,7 +47349,7 @@
       </c>
       <c r="P599" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q599" s="4" t="n"/>
@@ -47428,7 +47428,7 @@
       </c>
       <c r="P600" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q600" s="4" t="n"/>
@@ -47507,7 +47507,7 @@
       </c>
       <c r="P601" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q601" s="4" t="n"/>
@@ -47586,7 +47586,7 @@
       </c>
       <c r="P602" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q602" s="4" t="n"/>
@@ -47665,7 +47665,7 @@
       </c>
       <c r="P603" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q603" s="4" t="n"/>
@@ -47744,7 +47744,7 @@
       </c>
       <c r="P604" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q604" s="4" t="n"/>
@@ -47823,7 +47823,7 @@
       </c>
       <c r="P605" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q605" s="4" t="n"/>
@@ -47902,7 +47902,7 @@
       </c>
       <c r="P606" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q606" s="4" t="n"/>
@@ -47981,7 +47981,7 @@
       </c>
       <c r="P607" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q607" s="4" t="n"/>
@@ -48060,7 +48060,7 @@
       </c>
       <c r="P608" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q608" s="4" t="n"/>
@@ -48139,7 +48139,7 @@
       </c>
       <c r="P609" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q609" s="4" t="n"/>
@@ -48218,7 +48218,7 @@
       </c>
       <c r="P610" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q610" s="4" t="n"/>
@@ -48297,7 +48297,7 @@
       </c>
       <c r="P611" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q611" s="4" t="n"/>
@@ -48376,7 +48376,7 @@
       </c>
       <c r="P612" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q612" s="4" t="n"/>
@@ -48455,7 +48455,7 @@
       </c>
       <c r="P613" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q613" s="4" t="n"/>
@@ -48534,7 +48534,7 @@
       </c>
       <c r="P614" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q614" s="4" t="n"/>
@@ -48613,7 +48613,7 @@
       </c>
       <c r="P615" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q615" s="4" t="n"/>
@@ -48692,7 +48692,7 @@
       </c>
       <c r="P616" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q616" s="4" t="n"/>
@@ -48771,7 +48771,7 @@
       </c>
       <c r="P617" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q617" s="4" t="n"/>
@@ -48850,7 +48850,7 @@
       </c>
       <c r="P618" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q618" s="4" t="n"/>
@@ -48929,7 +48929,7 @@
       </c>
       <c r="P619" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q619" s="4" t="n"/>
@@ -49008,7 +49008,7 @@
       </c>
       <c r="P620" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q620" s="4" t="n"/>
@@ -49087,7 +49087,7 @@
       </c>
       <c r="P621" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q621" s="4" t="n"/>
@@ -49166,7 +49166,7 @@
       </c>
       <c r="P622" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q622" s="4" t="n"/>
@@ -49245,7 +49245,7 @@
       </c>
       <c r="P623" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q623" s="4" t="n"/>
@@ -49324,7 +49324,7 @@
       </c>
       <c r="P624" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q624" s="4" t="n"/>
@@ -49403,7 +49403,7 @@
       </c>
       <c r="P625" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q625" s="4" t="n"/>
@@ -49482,7 +49482,7 @@
       </c>
       <c r="P626" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q626" s="4" t="n"/>
@@ -49561,7 +49561,7 @@
       </c>
       <c r="P627" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q627" s="4" t="n"/>
@@ -49640,7 +49640,7 @@
       </c>
       <c r="P628" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q628" s="4" t="n"/>
@@ -49719,7 +49719,7 @@
       </c>
       <c r="P629" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q629" s="4" t="n"/>
@@ -49798,7 +49798,7 @@
       </c>
       <c r="P630" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q630" s="4" t="n"/>
@@ -49877,7 +49877,7 @@
       </c>
       <c r="P631" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q631" s="4" t="n"/>
@@ -49956,7 +49956,7 @@
       </c>
       <c r="P632" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q632" s="4" t="n"/>
@@ -50035,7 +50035,7 @@
       </c>
       <c r="P633" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q633" s="4" t="n"/>
@@ -50114,7 +50114,7 @@
       </c>
       <c r="P634" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q634" s="4" t="n"/>
@@ -50193,7 +50193,7 @@
       </c>
       <c r="P635" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q635" s="4" t="n"/>
@@ -50272,7 +50272,7 @@
       </c>
       <c r="P636" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q636" s="4" t="n"/>
@@ -50351,7 +50351,7 @@
       </c>
       <c r="P637" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q637" s="4" t="n"/>
@@ -50430,7 +50430,7 @@
       </c>
       <c r="P638" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q638" s="4" t="n"/>
@@ -50509,7 +50509,7 @@
       </c>
       <c r="P639" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q639" s="4" t="n"/>
@@ -50588,7 +50588,7 @@
       </c>
       <c r="P640" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q640" s="4" t="n"/>
@@ -50667,7 +50667,7 @@
       </c>
       <c r="P641" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q641" s="4" t="n"/>
@@ -50746,7 +50746,7 @@
       </c>
       <c r="P642" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q642" s="4" t="n"/>
@@ -50825,7 +50825,7 @@
       </c>
       <c r="P643" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q643" s="4" t="n"/>
@@ -50904,7 +50904,7 @@
       </c>
       <c r="P644" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q644" s="4" t="n"/>
@@ -50983,7 +50983,7 @@
       </c>
       <c r="P645" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q645" s="4" t="n"/>
@@ -51062,7 +51062,7 @@
       </c>
       <c r="P646" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q646" s="4" t="n"/>
@@ -51141,7 +51141,7 @@
       </c>
       <c r="P647" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q647" s="4" t="n"/>
@@ -51220,7 +51220,7 @@
       </c>
       <c r="P648" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q648" s="4" t="n"/>
@@ -51299,7 +51299,7 @@
       </c>
       <c r="P649" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q649" s="4" t="n"/>
@@ -51378,7 +51378,7 @@
       </c>
       <c r="P650" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q650" s="4" t="n"/>
@@ -51457,7 +51457,7 @@
       </c>
       <c r="P651" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q651" s="4" t="n"/>
@@ -51536,7 +51536,7 @@
       </c>
       <c r="P652" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q652" s="4" t="n"/>
@@ -51615,7 +51615,7 @@
       </c>
       <c r="P653" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q653" s="4" t="n"/>
@@ -51694,7 +51694,7 @@
       </c>
       <c r="P654" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q654" s="4" t="n"/>
@@ -51773,7 +51773,7 @@
       </c>
       <c r="P655" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q655" s="4" t="n"/>
@@ -51852,7 +51852,7 @@
       </c>
       <c r="P656" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q656" s="4" t="n"/>
@@ -51931,7 +51931,7 @@
       </c>
       <c r="P657" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q657" s="4" t="n"/>
@@ -52010,7 +52010,7 @@
       </c>
       <c r="P658" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q658" s="4" t="n"/>
@@ -52089,7 +52089,7 @@
       </c>
       <c r="P659" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q659" s="4" t="n"/>
@@ -52168,7 +52168,7 @@
       </c>
       <c r="P660" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q660" s="4" t="n"/>
@@ -52247,7 +52247,7 @@
       </c>
       <c r="P661" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q661" s="4" t="n"/>
@@ -52326,7 +52326,7 @@
       </c>
       <c r="P662" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q662" s="4" t="n"/>
@@ -52405,7 +52405,7 @@
       </c>
       <c r="P663" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q663" s="4" t="n"/>
@@ -52484,7 +52484,7 @@
       </c>
       <c r="P664" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q664" s="4" t="n"/>
@@ -52563,7 +52563,7 @@
       </c>
       <c r="P665" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q665" s="4" t="n"/>
@@ -52642,7 +52642,7 @@
       </c>
       <c r="P666" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q666" s="4" t="n"/>
@@ -52727,7 +52727,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
